--- a/src/attributions/attributions_saliency_traj_58.xlsx
+++ b/src/attributions/attributions_saliency_traj_58.xlsx
@@ -2137,2278 +2137,2278 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.0001032056898111477</v>
+        <v>3.165209636790678e-05</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0004736364644486457</v>
+        <v>9.393806067237165e-06</v>
       </c>
       <c r="C4" t="n">
-        <v>4.581400571623817e-05</v>
+        <v>4.033411187265301e-06</v>
       </c>
       <c r="D4" t="n">
-        <v>7.516136975027621e-05</v>
+        <v>1.304767647525296e-05</v>
       </c>
       <c r="E4" t="n">
-        <v>3.210578506696038e-05</v>
+        <v>1.004589648800902e-06</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0004774776461999863</v>
+        <v>5.085285374661908e-05</v>
       </c>
       <c r="G4" t="n">
-        <v>1.397839878336526e-05</v>
+        <v>2.165001569665037e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>3.424815440666862e-05</v>
+        <v>2.394846524111927e-05</v>
       </c>
       <c r="I4" t="n">
-        <v>7.689392987231258e-06</v>
+        <v>1.502615191384393e-06</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0001819420576794073</v>
+        <v>2.258416679978836e-05</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0003368885663803667</v>
+        <v>3.516705692163669e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>4.309833457227796e-06</v>
+        <v>5.856858479091898e-06</v>
       </c>
       <c r="M4" t="n">
-        <v>5.762500586570241e-05</v>
+        <v>5.664353011525236e-06</v>
       </c>
       <c r="N4" t="n">
-        <v>3.940699389204383e-05</v>
+        <v>7.563696271972731e-06</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0003509256639517844</v>
+        <v>4.964082108926959e-05</v>
       </c>
       <c r="P4" t="n">
-        <v>2.306486931047402e-05</v>
+        <v>3.565392034943216e-05</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0001033785665640607</v>
+        <v>2.10713260457851e-05</v>
       </c>
       <c r="R4" t="n">
-        <v>8.913558849599212e-05</v>
+        <v>1.361261274723802e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>2.433382360322867e-05</v>
+        <v>9.506231435807422e-06</v>
       </c>
       <c r="T4" t="n">
-        <v>3.492906398605555e-05</v>
+        <v>3.067610305151902e-05</v>
       </c>
       <c r="U4" t="n">
-        <v>1.370700192637742e-05</v>
+        <v>1.400743985868758e-05</v>
       </c>
       <c r="V4" t="n">
-        <v>5.822734237881377e-05</v>
+        <v>1.834655631682836e-05</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0001170918258139864</v>
+        <v>4.149474989390001e-05</v>
       </c>
       <c r="X4" t="n">
-        <v>4.862246714765206e-05</v>
+        <v>3.152446879539639e-05</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.154918886139058e-05</v>
+        <v>1.091251397156157e-05</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.52835668309126e-05</v>
+        <v>3.748055860341992e-06</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.138211468467489e-06</v>
+        <v>2.439578565827105e-06</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.716483479365706e-05</v>
+        <v>1.835344846767839e-06</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.428549684438622e-06</v>
+        <v>8.573829290980939e-07</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.920259976235684e-05</v>
+        <v>1.298825827689143e-05</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.0001057108238455839</v>
+        <v>3.540565103321569e-06</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.0001078994246199727</v>
+        <v>7.445313713105861e-06</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.650009966804646e-05</v>
+        <v>3.349669441377046e-06</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.677412001299672e-06</v>
+        <v>5.789974238723516e-06</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.776746830728371e-05</v>
+        <v>1.990458804357331e-05</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.317807891609846e-05</v>
+        <v>6.234102784219431e-06</v>
       </c>
       <c r="AK4" t="n">
-        <v>8.891058769222582e-07</v>
+        <v>2.821837369992863e-06</v>
       </c>
       <c r="AL4" t="n">
-        <v>3.419652421143837e-05</v>
+        <v>7.106956218194682e-06</v>
       </c>
       <c r="AM4" t="n">
-        <v>5.261503611109219e-05</v>
+        <v>1.553530637465883e-06</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.269540997687727e-05</v>
+        <v>1.559457450639457e-05</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.917677582241595e-05</v>
+        <v>2.274302642035764e-05</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.0001100377849070355</v>
+        <v>6.307473086053506e-06</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6.919454608578235e-05</v>
+        <v>4.075519882462686e-06</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.777533078799024e-05</v>
+        <v>6.340515028568916e-06</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.0001196264129248448</v>
+        <v>5.815818894916447e-06</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.311846037628129e-05</v>
+        <v>1.128598569266615e-06</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.0002251311670988798</v>
+        <v>5.138562846696004e-05</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.981602488551289e-05</v>
+        <v>4.537591848929878e-06</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.891895564971492e-05</v>
+        <v>5.157122814125614e-06</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.407907257089391e-05</v>
+        <v>2.118975316989236e-06</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.0001351090904790908</v>
+        <v>2.282823697896674e-05</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.0001111968085751869</v>
+        <v>1.449229603167623e-05</v>
       </c>
       <c r="BA4" t="n">
-        <v>4.537483619060367e-05</v>
+        <v>2.326111280126497e-05</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.000187309313332662</v>
+        <v>1.166450829259702e-06</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001545083214296028</v>
+        <v>2.28221106226556e-05</v>
       </c>
       <c r="BD4" t="n">
-        <v>8.338040061062202e-05</v>
+        <v>3.757842023333069e-06</v>
       </c>
       <c r="BE4" t="n">
-        <v>4.996686766389757e-05</v>
+        <v>6.174269856273895e-06</v>
       </c>
       <c r="BF4" t="n">
-        <v>2.655880962265655e-05</v>
+        <v>9.638379196985625e-06</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0001064742536982521</v>
+        <v>9.118301022681408e-06</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.0002154640096705407</v>
+        <v>1.108572905650362e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>9.896514529827982e-05</v>
+        <v>7.881915735197254e-06</v>
       </c>
       <c r="BJ4" t="n">
-        <v>6.303399277385324e-05</v>
+        <v>3.529225432430394e-05</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0001199843391077593</v>
+        <v>3.300885282442323e-06</v>
       </c>
       <c r="BL4" t="n">
-        <v>7.919761628727429e-06</v>
+        <v>1.083834013115847e-05</v>
       </c>
       <c r="BM4" t="n">
-        <v>3.488186848699115e-05</v>
+        <v>1.747507485561073e-05</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.770021405420266e-06</v>
+        <v>3.959075456805294e-06</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.03834019380156e-06</v>
+        <v>6.473115263361251e-06</v>
       </c>
       <c r="BP4" t="n">
-        <v>6.456416303990409e-05</v>
+        <v>9.676819900050759e-06</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.050644980045035e-06</v>
+        <v>8.908115887606982e-06</v>
       </c>
       <c r="BR4" t="n">
-        <v>5.565693572862074e-05</v>
+        <v>1.119389344239607e-05</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.941740083566401e-05</v>
+        <v>1.458121550967917e-05</v>
       </c>
       <c r="BT4" t="n">
-        <v>3.439092688495293e-05</v>
+        <v>8.97668633115245e-06</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.286968032829463e-05</v>
+        <v>5.783421784144593e-06</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.0001265278551727533</v>
+        <v>4.313221779739251e-06</v>
       </c>
       <c r="BW4" t="n">
-        <v>4.490174615057185e-05</v>
+        <v>1.684160088188946e-05</v>
       </c>
       <c r="BX4" t="n">
-        <v>3.159738480462693e-05</v>
+        <v>3.413280137465335e-05</v>
       </c>
       <c r="BY4" t="n">
-        <v>9.140544716501608e-05</v>
+        <v>3.135645965812728e-05</v>
       </c>
       <c r="BZ4" t="n">
-        <v>5.096838140161708e-05</v>
+        <v>3.705472408910282e-05</v>
       </c>
       <c r="CA4" t="n">
-        <v>5.0080661821994e-06</v>
+        <v>1.780577576937503e-06</v>
       </c>
       <c r="CB4" t="n">
-        <v>7.17482907930389e-06</v>
+        <v>6.428331289498601e-07</v>
       </c>
       <c r="CC4" t="n">
-        <v>6.786684389226139e-05</v>
+        <v>7.225673016364453e-06</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.497916284482926e-05</v>
+        <v>6.10100187259377e-06</v>
       </c>
       <c r="CE4" t="n">
-        <v>6.46273183519952e-05</v>
+        <v>4.661353159463033e-06</v>
       </c>
       <c r="CF4" t="n">
-        <v>3.748339804587886e-05</v>
+        <v>3.448834149821778e-06</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.622895251784939e-05</v>
+        <v>6.263926934479969e-06</v>
       </c>
       <c r="CH4" t="n">
-        <v>4.407183951116167e-05</v>
+        <v>2.380919340794208e-06</v>
       </c>
       <c r="CI4" t="n">
-        <v>8.490172331221402e-05</v>
+        <v>1.449555657018209e-05</v>
       </c>
       <c r="CJ4" t="n">
-        <v>2.639475860632956e-05</v>
+        <v>2.828987817338202e-06</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.601640178705566e-06</v>
+        <v>4.6119607759465e-06</v>
       </c>
       <c r="CL4" t="n">
-        <v>5.170628355699591e-05</v>
+        <v>4.854493454331532e-06</v>
       </c>
       <c r="CM4" t="n">
-        <v>4.889072442892939e-05</v>
+        <v>2.887020400521578e-07</v>
       </c>
       <c r="CN4" t="n">
-        <v>7.526374974986538e-05</v>
+        <v>2.789979407680221e-05</v>
       </c>
       <c r="CO4" t="n">
-        <v>5.581996447290294e-05</v>
+        <v>4.259923116478603e-06</v>
       </c>
       <c r="CP4" t="n">
-        <v>5.406991840573028e-05</v>
+        <v>4.727304713014746e-06</v>
       </c>
       <c r="CQ4" t="n">
-        <v>3.33458483510185e-05</v>
+        <v>1.824951141315978e-06</v>
       </c>
       <c r="CR4" t="n">
-        <v>1.696695471764542e-05</v>
+        <v>1.903299198602326e-05</v>
       </c>
       <c r="CS4" t="n">
-        <v>3.674473191495053e-05</v>
+        <v>1.656570566410664e-05</v>
       </c>
       <c r="CT4" t="n">
-        <v>4.835805157199502e-06</v>
+        <v>7.142718459363095e-06</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0001062214651028626</v>
+        <v>4.641360646928661e-06</v>
       </c>
       <c r="CV4" t="n">
-        <v>1.573460576764774e-05</v>
+        <v>7.344201549130958e-06</v>
       </c>
       <c r="CW4" t="n">
-        <v>7.498884224332869e-05</v>
+        <v>2.619643510115566e-06</v>
       </c>
       <c r="CX4" t="n">
-        <v>2.592790042399429e-05</v>
+        <v>9.776853175935685e-07</v>
       </c>
       <c r="CY4" t="n">
-        <v>2.741217031143606e-05</v>
+        <v>6.076062618376454e-06</v>
       </c>
       <c r="CZ4" t="n">
-        <v>4.595885548042133e-05</v>
+        <v>2.012670165640884e-06</v>
       </c>
       <c r="DA4" t="n">
-        <v>8.669972157804295e-05</v>
+        <v>1.103004069591407e-05</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.099843211704865e-05</v>
+        <v>2.566563125583343e-06</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.162784064945299e-05</v>
+        <v>5.680490744452982e-07</v>
       </c>
       <c r="DD4" t="n">
-        <v>5.067224628874101e-05</v>
+        <v>2.459988536429591e-06</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.337538353458513e-05</v>
+        <v>8.852201062836684e-06</v>
       </c>
       <c r="DF4" t="n">
-        <v>5.835721094626933e-05</v>
+        <v>2.030546238529496e-05</v>
       </c>
       <c r="DG4" t="n">
-        <v>3.389347330085002e-05</v>
+        <v>1.963560862350278e-06</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.0001129528172896244</v>
+        <v>5.987075383018237e-06</v>
       </c>
       <c r="DI4" t="n">
-        <v>6.499660958070308e-05</v>
+        <v>5.889279236725997e-06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.0002037460799328983</v>
+        <v>5.668358426191844e-06</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.0001104745315387845</v>
+        <v>4.89958938487689e-06</v>
       </c>
       <c r="DL4" t="n">
-        <v>2.26080373977311e-05</v>
+        <v>2.867072339540755e-07</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.0001542231329949573</v>
+        <v>6.108986781327985e-06</v>
       </c>
       <c r="DN4" t="n">
-        <v>7.123823161236942e-05</v>
+        <v>1.588103259564377e-06</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.449272844591178e-05</v>
+        <v>5.968522600596771e-07</v>
       </c>
       <c r="DP4" t="n">
-        <v>1.548427098896354e-05</v>
+        <v>1.209427864523605e-05</v>
       </c>
       <c r="DQ4" t="n">
-        <v>7.194792124209926e-05</v>
+        <v>2.133360976586118e-05</v>
       </c>
       <c r="DR4" t="n">
-        <v>3.671969898277894e-05</v>
+        <v>1.216914097312838e-05</v>
       </c>
       <c r="DS4" t="n">
-        <v>4.402053946250817e-06</v>
+        <v>1.914892345666885e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>8.342081127921119e-05</v>
+        <v>6.748795385647099e-06</v>
       </c>
       <c r="DU4" t="n">
-        <v>2.163795761589427e-05</v>
+        <v>8.981200153357349e-06</v>
       </c>
       <c r="DV4" t="n">
-        <v>2.448331360938028e-05</v>
+        <v>5.38579115527682e-06</v>
       </c>
       <c r="DW4" t="n">
-        <v>3.933743937523104e-05</v>
+        <v>1.113901089411229e-05</v>
       </c>
       <c r="DX4" t="n">
-        <v>1.355906442768173e-05</v>
+        <v>6.834007308498258e-06</v>
       </c>
       <c r="DY4" t="n">
-        <v>1.715423240966629e-05</v>
+        <v>9.394674634677358e-06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>3.041233685507905e-05</v>
+        <v>7.663519681955222e-06</v>
       </c>
       <c r="EA4" t="n">
-        <v>2.767614387266804e-05</v>
+        <v>1.135732691182056e-05</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.264538241230184e-05</v>
+        <v>6.43659495835891e-06</v>
       </c>
       <c r="EC4" t="n">
-        <v>2.51303099503275e-05</v>
+        <v>5.869529104529647e-06</v>
       </c>
       <c r="ED4" t="n">
-        <v>5.291131674312055e-05</v>
+        <v>9.817883437790442e-06</v>
       </c>
       <c r="EE4" t="n">
-        <v>4.240875568939373e-05</v>
+        <v>9.539434358885046e-06</v>
       </c>
       <c r="EF4" t="n">
-        <v>2.117636904586107e-05</v>
+        <v>1.112379959522514e-05</v>
       </c>
       <c r="EG4" t="n">
-        <v>4.231355705996975e-05</v>
+        <v>8.770552994974423e-06</v>
       </c>
       <c r="EH4" t="n">
-        <v>6.443852726079058e-06</v>
+        <v>7.646577614650596e-06</v>
       </c>
       <c r="EI4" t="n">
-        <v>8.491994958603755e-05</v>
+        <v>6.408865374396555e-06</v>
       </c>
       <c r="EJ4" t="n">
-        <v>5.538334153243341e-05</v>
+        <v>1.201701343234163e-05</v>
       </c>
       <c r="EK4" t="n">
-        <v>1.180427534563933e-05</v>
+        <v>1.393071761413012e-05</v>
       </c>
       <c r="EL4" t="n">
-        <v>4.878386971540749e-05</v>
+        <v>5.752116294388543e-07</v>
       </c>
       <c r="EM4" t="n">
-        <v>4.789160811924376e-06</v>
+        <v>1.506521812189021e-06</v>
       </c>
       <c r="EN4" t="n">
-        <v>1.869548032118473e-05</v>
+        <v>6.277095053519588e-06</v>
       </c>
       <c r="EO4" t="n">
-        <v>4.594508573063649e-05</v>
+        <v>3.464010887910263e-06</v>
       </c>
       <c r="EP4" t="n">
-        <v>2.832132850016933e-05</v>
+        <v>5.286651230562711e-06</v>
       </c>
       <c r="EQ4" t="n">
-        <v>1.204397449328098e-05</v>
+        <v>1.693080957920756e-05</v>
       </c>
       <c r="ER4" t="n">
-        <v>3.15625402436126e-05</v>
+        <v>5.519020305655431e-06</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0001289171341340989</v>
+        <v>7.472489869542187e-06</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0001889664999907836</v>
+        <v>2.154138746846002e-05</v>
       </c>
       <c r="EU4" t="n">
-        <v>7.052146247588098e-05</v>
+        <v>8.329618140123785e-06</v>
       </c>
       <c r="EV4" t="n">
-        <v>6.541590846609324e-05</v>
+        <v>4.287201136321528e-06</v>
       </c>
       <c r="EW4" t="n">
-        <v>9.849597699940205e-05</v>
+        <v>5.333978947419382e-07</v>
       </c>
       <c r="EX4" t="n">
-        <v>1.918046109494753e-05</v>
+        <v>9.841014616540633e-06</v>
       </c>
       <c r="EY4" t="n">
-        <v>7.423492934321985e-05</v>
+        <v>5.365243850974366e-06</v>
       </c>
       <c r="EZ4" t="n">
-        <v>4.015904778498225e-06</v>
+        <v>6.026523351465585e-07</v>
       </c>
       <c r="FA4" t="n">
-        <v>1.98968882614281e-06</v>
+        <v>7.139763511077035e-06</v>
       </c>
       <c r="FB4" t="n">
-        <v>5.881017204956152e-05</v>
+        <v>1.456548943679081e-06</v>
       </c>
       <c r="FC4" t="n">
-        <v>6.895980186527595e-05</v>
+        <v>1.419018917658832e-05</v>
       </c>
       <c r="FD4" t="n">
-        <v>4.109555084141903e-05</v>
+        <v>2.701647645153571e-06</v>
       </c>
       <c r="FE4" t="n">
-        <v>1.684970993665047e-05</v>
+        <v>3.090578502451535e-06</v>
       </c>
       <c r="FF4" t="n">
-        <v>7.155432831496e-05</v>
+        <v>1.779926947165222e-06</v>
       </c>
       <c r="FG4" t="n">
-        <v>1.692976547928993e-05</v>
+        <v>1.998313928197604e-05</v>
       </c>
       <c r="FH4" t="n">
-        <v>5.058652823208831e-05</v>
+        <v>1.098376856134564e-08</v>
       </c>
       <c r="FI4" t="n">
-        <v>3.470664159976877e-05</v>
+        <v>5.38250287718256e-06</v>
       </c>
       <c r="FJ4" t="n">
-        <v>5.241814506007358e-05</v>
+        <v>3.928353180526756e-07</v>
       </c>
       <c r="FK4" t="n">
-        <v>2.499171023373492e-05</v>
+        <v>1.927740959217772e-05</v>
       </c>
       <c r="FL4" t="n">
-        <v>6.888442294439301e-05</v>
+        <v>1.468966365791857e-05</v>
       </c>
       <c r="FM4" t="n">
-        <v>2.066842716885731e-05</v>
+        <v>8.843901468935655e-07</v>
       </c>
       <c r="FN4" t="n">
-        <v>2.380399018875323e-05</v>
+        <v>9.138404493569396e-06</v>
       </c>
       <c r="FO4" t="n">
-        <v>4.328368959249929e-05</v>
+        <v>1.918465613925946e-06</v>
       </c>
       <c r="FP4" t="n">
-        <v>1.833621354307979e-05</v>
+        <v>2.028941707976628e-05</v>
       </c>
       <c r="FQ4" t="n">
-        <v>5.866526771569625e-05</v>
+        <v>9.643931662139948e-06</v>
       </c>
       <c r="FR4" t="n">
-        <v>6.397836114047095e-05</v>
+        <v>1.17925646918593e-05</v>
       </c>
       <c r="FS4" t="n">
-        <v>8.777999028097838e-06</v>
+        <v>6.320468855847139e-06</v>
       </c>
       <c r="FT4" t="n">
-        <v>1.28212132040062e-05</v>
+        <v>5.112087455927394e-05</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0001395415019942448</v>
+        <v>1.230474845215213e-05</v>
       </c>
       <c r="FV4" t="n">
-        <v>2.450157444400247e-05</v>
+        <v>2.443882840452716e-05</v>
       </c>
       <c r="FW4" t="n">
-        <v>4.687174077844247e-05</v>
+        <v>6.901531378389336e-06</v>
       </c>
       <c r="FX4" t="n">
-        <v>5.489516479428858e-05</v>
+        <v>6.62503680359805e-06</v>
       </c>
       <c r="FY4" t="n">
-        <v>6.185386155266315e-05</v>
+        <v>3.6541314329952e-07</v>
       </c>
       <c r="FZ4" t="n">
-        <v>8.203944162232801e-05</v>
+        <v>1.826617153710686e-05</v>
       </c>
       <c r="GA4" t="n">
-        <v>2.491029772500042e-05</v>
+        <v>1.132019588112598e-05</v>
       </c>
       <c r="GB4" t="n">
-        <v>2.243832022941206e-05</v>
+        <v>5.760187832493102e-06</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.0001193700663861819</v>
+        <v>1.639484980842099e-05</v>
       </c>
       <c r="GD4" t="n">
-        <v>1.311405958404066e-05</v>
+        <v>1.242953567270888e-05</v>
       </c>
       <c r="GE4" t="n">
-        <v>4.137541691306978e-05</v>
+        <v>7.193805686256383e-06</v>
       </c>
       <c r="GF4" t="n">
-        <v>2.378983481321484e-07</v>
+        <v>1.108361993829021e-05</v>
       </c>
       <c r="GG4" t="n">
-        <v>4.319639629102312e-05</v>
+        <v>1.575484589011467e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.0001213495415868238</v>
+        <v>4.388537945487769e-06</v>
       </c>
       <c r="B5" t="n">
-        <v>0.00388789176940918</v>
+        <v>0.0001299802970606834</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0004451247805263847</v>
+        <v>2.972553920699283e-05</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004024953581392765</v>
+        <v>5.542808503378183e-05</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003403973765671253</v>
+        <v>1.427942379450542e-06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001648789271712303</v>
+        <v>4.884459485765547e-05</v>
       </c>
       <c r="G5" t="n">
-        <v>2.849125303328037e-05</v>
+        <v>4.403094499139115e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001649264595471323</v>
+        <v>4.148959123995155e-05</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001574285561218858</v>
+        <v>2.296646016475279e-06</v>
       </c>
       <c r="J5" t="n">
-        <v>7.172371260821819e-05</v>
+        <v>5.603086719929706e-06</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003471605479717255</v>
+        <v>0.0001307345664827153</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0004477448237594217</v>
+        <v>4.889551928499714e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>0.003600012511014938</v>
+        <v>8.724255894776434e-05</v>
       </c>
       <c r="N5" t="n">
-        <v>0.003718617372214794</v>
+        <v>3.081518661929294e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0.002458123955875635</v>
+        <v>4.178394010523334e-05</v>
       </c>
       <c r="P5" t="n">
-        <v>0.001026759040541947</v>
+        <v>3.768371971091256e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.001152673154138029</v>
+        <v>1.789785346772987e-05</v>
       </c>
       <c r="R5" t="n">
-        <v>0.001969023142009974</v>
+        <v>1.161974887509132e-05</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0001184897701023147</v>
+        <v>4.858072315983009e-06</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0002731098502408713</v>
+        <v>4.350978088041302e-06</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0001497880148235708</v>
+        <v>2.668158003871213e-06</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0005525145679712296</v>
+        <v>2.833344296959694e-06</v>
       </c>
       <c r="W5" t="n">
-        <v>0.00253545050509274</v>
+        <v>4.923257165501127e-06</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0003440824802964926</v>
+        <v>1.632218663871754e-05</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.001485746586695313</v>
+        <v>1.512437393103028e-05</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.0002088444744003937</v>
+        <v>2.245775431219954e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.0004573029582388699</v>
+        <v>2.334320197405759e-05</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0001840692857513204</v>
+        <v>6.116759777796688e-06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.0004578206571750343</v>
+        <v>4.704001185018569e-06</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0004112917231395841</v>
+        <v>2.06349250220228e-05</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.001342881703749299</v>
+        <v>2.792686063912697e-05</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.002975857350975275</v>
+        <v>2.297252649441361e-06</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.001346097560599446</v>
+        <v>4.96428256155923e-05</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.00040630460716784</v>
+        <v>8.796504516794812e-06</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.0003903688048012555</v>
+        <v>2.441202377667651e-05</v>
       </c>
       <c r="AJ5" t="n">
-        <v>8.803427044767886e-05</v>
+        <v>1.363383489660919e-05</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0002143486490240321</v>
+        <v>1.988100393646164e-06</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.000457858550362289</v>
+        <v>3.731159813469276e-05</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.689026587177068e-06</v>
+        <v>2.260240580653772e-05</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.0007839684258215129</v>
+        <v>1.525806510471739e-05</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.001760233077220619</v>
+        <v>1.803400664357468e-05</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.001012836582958698</v>
+        <v>1.898242589959409e-05</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0003639352507889271</v>
+        <v>7.425227977364557e-06</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.0008559463312849402</v>
+        <v>7.957793968671467e-06</v>
       </c>
       <c r="AS5" t="n">
-        <v>0.00050880026537925</v>
+        <v>2.995533577632159e-06</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.0001889494596980512</v>
+        <v>2.996684997924604e-06</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.002079619094729424</v>
+        <v>5.647673242492601e-05</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.0001927300472743809</v>
+        <v>1.966815761988983e-05</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.001831382047384977</v>
+        <v>2.283535286551341e-05</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.001964900409802794</v>
+        <v>7.168688898673281e-05</v>
       </c>
       <c r="AY5" t="n">
-        <v>0.001656297361478209</v>
+        <v>4.696561882155947e-05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.002170221880078316</v>
+        <v>8.925630936573725e-07</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.002797680906951427</v>
+        <v>1.398144604536355e-06</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.001069760764949024</v>
+        <v>5.051106654718751e-06</v>
       </c>
       <c r="BC5" t="n">
-        <v>8.314706792589277e-05</v>
+        <v>1.36100406962214e-05</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.001281182165257633</v>
+        <v>1.398588665324496e-05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0007881924393586814</v>
+        <v>2.450339525239542e-05</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0003442728193476796</v>
+        <v>1.378447996103205e-05</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.002043362706899643</v>
+        <v>3.227656270610169e-05</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.001639310037717223</v>
+        <v>1.390148190694163e-05</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.001190526760183275</v>
+        <v>2.413479160168208e-05</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.001459113555029035</v>
+        <v>4.784433622262441e-05</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.001978109590709209</v>
+        <v>1.382893515256001e-06</v>
       </c>
       <c r="BL5" t="n">
-        <v>2.3745495127514e-05</v>
+        <v>8.150311714416603e-08</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0001818353193812072</v>
+        <v>2.062495877908077e-05</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0004648882313631475</v>
+        <v>6.284423761826474e-06</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.001638597226701677</v>
+        <v>2.173257416870911e-05</v>
       </c>
       <c r="BP5" t="n">
-        <v>1.814396819099784e-05</v>
+        <v>3.651213319244562e-06</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0.001007178099825978</v>
+        <v>1.795841626517358e-07</v>
       </c>
       <c r="BR5" t="n">
-        <v>0.0004280958673916757</v>
+        <v>8.521938070771284e-06</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.000816333806142211</v>
+        <v>7.266502962011145e-06</v>
       </c>
       <c r="BT5" t="n">
-        <v>1.019376213662326e-05</v>
+        <v>1.00019715318922e-05</v>
       </c>
       <c r="BU5" t="n">
-        <v>0.0004947802517563105</v>
+        <v>5.615750524157193e-06</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.001278143026866019</v>
+        <v>4.074894241057336e-05</v>
       </c>
       <c r="BW5" t="n">
-        <v>0.0003392861108295619</v>
+        <v>1.413110203429824e-05</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.002410839078947902</v>
+        <v>4.490239371079952e-05</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.001231864560395479</v>
+        <v>5.461579348775558e-06</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0.0001023482764139771</v>
+        <v>2.260878864035476e-05</v>
       </c>
       <c r="CA5" t="n">
-        <v>0.0008955525700002909</v>
+        <v>1.187837369798217e-05</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.001306696562096477</v>
+        <v>2.500423306628363e-06</v>
       </c>
       <c r="CC5" t="n">
-        <v>0.0002542157890275121</v>
+        <v>1.343144867860246e-05</v>
       </c>
       <c r="CD5" t="n">
-        <v>0.000140933771035634</v>
+        <v>4.123721282667248e-06</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.0005036602960899472</v>
+        <v>4.191853804513812e-05</v>
       </c>
       <c r="CF5" t="n">
-        <v>0.0001619544927962124</v>
+        <v>5.08648190589156e-06</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.0006019182619638741</v>
+        <v>2.528629920561798e-05</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.000500737049151212</v>
+        <v>1.120548859034898e-06</v>
       </c>
       <c r="CI5" t="n">
-        <v>0.00025710224872455</v>
+        <v>6.843024493718985e-06</v>
       </c>
       <c r="CJ5" t="n">
-        <v>0.0002909044269472361</v>
+        <v>3.373326762812212e-06</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0003534553397912532</v>
+        <v>1.012521011034551e-06</v>
       </c>
       <c r="CL5" t="n">
-        <v>0.0002525463351048529</v>
+        <v>2.490273345756577e-06</v>
       </c>
       <c r="CM5" t="n">
-        <v>0.0005665093194693327</v>
+        <v>1.647970202611759e-05</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.887121809180826e-05</v>
+        <v>1.841604171204381e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>8.181991142919287e-05</v>
+        <v>4.456049282453023e-05</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.0001881813805084676</v>
+        <v>4.867382085649297e-05</v>
       </c>
       <c r="CQ5" t="n">
-        <v>0.001117272768169641</v>
+        <v>1.629063990549184e-05</v>
       </c>
       <c r="CR5" t="n">
-        <v>0.0009454411920160055</v>
+        <v>1.73073112819111e-05</v>
       </c>
       <c r="CS5" t="n">
-        <v>0.001480127219110727</v>
+        <v>1.656706444919109e-05</v>
       </c>
       <c r="CT5" t="n">
-        <v>0.002467144746333361</v>
+        <v>1.728286952129565e-05</v>
       </c>
       <c r="CU5" t="n">
-        <v>8.320523193106055e-06</v>
+        <v>1.024043058350799e-06</v>
       </c>
       <c r="CV5" t="n">
-        <v>0.0001037515030475333</v>
+        <v>3.84726718039019e-06</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.0004772347747348249</v>
+        <v>4.149966116528958e-05</v>
       </c>
       <c r="CX5" t="n">
-        <v>0.0002722365316003561</v>
+        <v>8.96268647920806e-06</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.0005211828392930329</v>
+        <v>2.666692307684571e-05</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0007790948147885501</v>
+        <v>6.358549399010371e-06</v>
       </c>
       <c r="DA5" t="n">
-        <v>0.0001493650197517127</v>
+        <v>8.342003638972528e-06</v>
       </c>
       <c r="DB5" t="n">
-        <v>0.0001940346555784345</v>
+        <v>4.702766091213562e-06</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.0002059503021882847</v>
+        <v>9.671496172813931e-07</v>
       </c>
       <c r="DD5" t="n">
-        <v>7.034384179860353e-05</v>
+        <v>3.304126948933117e-06</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.000931575836148113</v>
+        <v>1.553639958729036e-05</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.000730794679839164</v>
+        <v>2.922775456681848e-05</v>
       </c>
       <c r="DG5" t="n">
-        <v>0.0008515756344422698</v>
+        <v>6.739041964465287e-06</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.002360604703426361</v>
+        <v>2.423833211651072e-05</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.001181342639029026</v>
+        <v>9.117120498558506e-06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0.0006032479577697814</v>
+        <v>7.914450543466955e-05</v>
       </c>
       <c r="DK5" t="n">
-        <v>0.001299316762015224</v>
+        <v>1.27615021483507e-05</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.0005969135672785342</v>
+        <v>4.788939259015024e-05</v>
       </c>
       <c r="DM5" t="n">
-        <v>0.0004329100484028459</v>
+        <v>3.2013149393606e-06</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.0002623529289849102</v>
+        <v>1.55388306666282e-06</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.0003908403450623155</v>
+        <v>2.288731957378332e-05</v>
       </c>
       <c r="DP5" t="n">
-        <v>0.0001815650030039251</v>
+        <v>3.437184204813093e-06</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.0008917183149605989</v>
+        <v>1.891519605123904e-05</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.0004021185450255871</v>
+        <v>4.362138042779407e-06</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.0004137730284128338</v>
+        <v>6.625887181144208e-06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.000772219558712095</v>
+        <v>2.172193126170896e-05</v>
       </c>
       <c r="DU5" t="n">
-        <v>0.0004094521573279053</v>
+        <v>8.724122380954213e-06</v>
       </c>
       <c r="DV5" t="n">
-        <v>0.0002726875536609441</v>
+        <v>3.983722854172811e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.0004553788166958839</v>
+        <v>1.035196419252316e-06</v>
       </c>
       <c r="DX5" t="n">
-        <v>2.397370553808287e-05</v>
+        <v>7.708700650255196e-06</v>
       </c>
       <c r="DY5" t="n">
-        <v>3.641577495727688e-05</v>
+        <v>2.489056714694016e-05</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.0002860124805010855</v>
+        <v>1.143349618359935e-05</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.00171428662724793</v>
+        <v>7.375663699349388e-06</v>
       </c>
       <c r="EB5" t="n">
-        <v>0.0006633121520280838</v>
+        <v>3.14929275191389e-05</v>
       </c>
       <c r="EC5" t="n">
-        <v>0.0001127132709370926</v>
+        <v>8.725057796254987e-07</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.0007139142253436148</v>
+        <v>5.941413473919965e-05</v>
       </c>
       <c r="EE5" t="n">
-        <v>0.000405164115363732</v>
+        <v>4.909564086119644e-05</v>
       </c>
       <c r="EF5" t="n">
-        <v>0.0003824111190624535</v>
+        <v>1.578897899889853e-05</v>
       </c>
       <c r="EG5" t="n">
-        <v>9.653030429035425e-05</v>
+        <v>2.93347766273655e-05</v>
       </c>
       <c r="EH5" t="n">
-        <v>0.0003389001067262143</v>
+        <v>1.76130542968167e-05</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.0005762877990491688</v>
+        <v>3.682986425701529e-05</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.001030571525916457</v>
+        <v>9.123872587224469e-06</v>
       </c>
       <c r="EK5" t="n">
-        <v>0.0003430577926337719</v>
+        <v>6.560742349392967e-06</v>
       </c>
       <c r="EL5" t="n">
-        <v>0.0005625617923215032</v>
+        <v>9.567002052790485e-06</v>
       </c>
       <c r="EM5" t="n">
-        <v>0.0001239966368302703</v>
+        <v>3.583264060580404e-06</v>
       </c>
       <c r="EN5" t="n">
-        <v>1.26724480651319e-05</v>
+        <v>7.775179255986586e-06</v>
       </c>
       <c r="EO5" t="n">
-        <v>0.0002000795066123828</v>
+        <v>7.483971785404719e-06</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.0005089222686365247</v>
+        <v>3.903231845470145e-05</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0.0003175165038555861</v>
+        <v>2.267283889523242e-07</v>
       </c>
       <c r="ER5" t="n">
-        <v>0.0003788121393881738</v>
+        <v>2.75770162261324e-06</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.001341438153758645</v>
+        <v>4.406972038850654e-06</v>
       </c>
       <c r="ET5" t="n">
-        <v>0.001023539109155536</v>
+        <v>8.462111509288661e-06</v>
       </c>
       <c r="EU5" t="n">
-        <v>0.001303594443015754</v>
+        <v>1.206633987749228e-05</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.0003498237056192011</v>
+        <v>6.222338924999349e-06</v>
       </c>
       <c r="EW5" t="n">
-        <v>0.0003379767294973135</v>
+        <v>2.624805711093359e-05</v>
       </c>
       <c r="EX5" t="n">
-        <v>0.0002062737621599808</v>
+        <v>3.981777354056248e-06</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.0004731577937491238</v>
+        <v>4.277451807865873e-05</v>
       </c>
       <c r="EZ5" t="n">
-        <v>0.0001092200400307775</v>
+        <v>6.558365839737235e-06</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.0006921514868736267</v>
+        <v>3.161024505971e-05</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0006231438019312918</v>
+        <v>1.218206534758792e-06</v>
       </c>
       <c r="FC5" t="n">
-        <v>0.000465325458208099</v>
+        <v>7.622577868460212e-06</v>
       </c>
       <c r="FD5" t="n">
-        <v>0.0004249604535289109</v>
+        <v>1.66464417361567e-06</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.0004251644422765821</v>
+        <v>2.629375103424536e-06</v>
       </c>
       <c r="FF5" t="n">
-        <v>0.0001273097441298887</v>
+        <v>7.909226042102091e-06</v>
       </c>
       <c r="FG5" t="n">
-        <v>0.0001557021168991923</v>
+        <v>1.013251676340587e-06</v>
       </c>
       <c r="FH5" t="n">
-        <v>3.891796950483695e-05</v>
+        <v>1.413306199538056e-05</v>
       </c>
       <c r="FI5" t="n">
-        <v>0.0001759883743943647</v>
+        <v>4.482094027480343e-06</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.0006192529108375311</v>
+        <v>2.092871000058949e-05</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.0007051026332192123</v>
+        <v>1.136706941906596e-05</v>
       </c>
       <c r="FL5" t="n">
-        <v>0.0003192581643816084</v>
+        <v>9.329864951723721e-07</v>
       </c>
       <c r="FM5" t="n">
-        <v>0.0004902886576019228</v>
+        <v>7.203435870906105e-06</v>
       </c>
       <c r="FN5" t="n">
-        <v>0.0004281081492081285</v>
+        <v>2.126333129126579e-05</v>
       </c>
       <c r="FO5" t="n">
-        <v>0.0002044397406280041</v>
+        <v>2.057658275589347e-05</v>
       </c>
       <c r="FP5" t="n">
-        <v>0.0004939615027979016</v>
+        <v>2.783213130896911e-05</v>
       </c>
       <c r="FQ5" t="n">
-        <v>0.0006648400449194014</v>
+        <v>5.018973752157763e-05</v>
       </c>
       <c r="FR5" t="n">
-        <v>6.772120832465589e-05</v>
+        <v>1.78278423845768e-05</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.0006842926959507167</v>
+        <v>1.346334920526715e-05</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.002937791403383017</v>
+        <v>5.667346704285592e-05</v>
       </c>
       <c r="FU5" t="n">
-        <v>0.0004104433464817703</v>
+        <v>2.795004184008576e-05</v>
       </c>
       <c r="FV5" t="n">
-        <v>0.0003127719974145293</v>
+        <v>2.220102032879367e-06</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.0002288417454110458</v>
+        <v>3.518852463457733e-05</v>
       </c>
       <c r="FX5" t="n">
-        <v>0.001073895720764995</v>
+        <v>3.551363624865189e-05</v>
       </c>
       <c r="FY5" t="n">
-        <v>6.889121141284704e-05</v>
+        <v>8.032564437598921e-06</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.0001217747922055423</v>
+        <v>8.84161090652924e-06</v>
       </c>
       <c r="GA5" t="n">
-        <v>0.000376954470993951</v>
+        <v>1.230109955940861e-05</v>
       </c>
       <c r="GB5" t="n">
-        <v>9.860089630819857e-05</v>
+        <v>3.109393946942873e-05</v>
       </c>
       <c r="GC5" t="n">
-        <v>0.0008086348534561694</v>
+        <v>4.451041490938223e-08</v>
       </c>
       <c r="GD5" t="n">
-        <v>0.0006656625191681087</v>
+        <v>1.501839051343268e-05</v>
       </c>
       <c r="GE5" t="n">
-        <v>0.0007150995079427958</v>
+        <v>2.371489972574636e-05</v>
       </c>
       <c r="GF5" t="n">
-        <v>0.0005375211476348341</v>
+        <v>3.003971642101533e-06</v>
       </c>
       <c r="GG5" t="n">
-        <v>0.000753184431232512</v>
+        <v>1.638768844713923e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0002353085728827864</v>
+        <v>2.956767317964515e-13</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0002295315352967009</v>
+        <v>5.34316839904958e-13</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0002028826420428231</v>
+        <v>1.861768253669585e-13</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0001360244059469551</v>
+        <v>3.662287978439685e-15</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009085029596462846</v>
+        <v>2.731971278976258e-13</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000750405655708164</v>
+        <v>8.593920388690057e-13</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0005042768898420036</v>
+        <v>6.313926161419237e-13</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0003141497145406902</v>
+        <v>1.432405734823339e-12</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0005511846975423396</v>
+        <v>3.537666562009002e-15</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0003474598343018442</v>
+        <v>3.427989229282113e-13</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0005184505134820938</v>
+        <v>2.513786433785276e-13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001805376814445481</v>
+        <v>4.098379621786385e-13</v>
       </c>
       <c r="M6" t="n">
-        <v>9.17999423108995e-05</v>
+        <v>2.452534161000164e-13</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001062033697962761</v>
+        <v>6.331134618300926e-13</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0008253343985415995</v>
+        <v>9.736957334166574e-13</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001609863829798996</v>
+        <v>1.093856342310184e-12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.570217136759311e-05</v>
+        <v>1.297466908217748e-12</v>
       </c>
       <c r="R6" t="n">
-        <v>0.0001667698234086856</v>
+        <v>1.72796781224005e-13</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0001867173559730873</v>
+        <v>9.18236027578484e-14</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0001473206066293642</v>
+        <v>3.789074360261574e-13</v>
       </c>
       <c r="U6" t="n">
-        <v>8.401306695304811e-05</v>
+        <v>2.604563971182056e-14</v>
       </c>
       <c r="V6" t="n">
-        <v>2.202796895289794e-05</v>
+        <v>2.015440223566978e-13</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002146378828911111</v>
+        <v>7.308958126228671e-13</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0003021386219188571</v>
+        <v>4.891842952849806e-14</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0001438736799173057</v>
+        <v>2.500311156033996e-13</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.886750922305509e-05</v>
+        <v>8.870462957916159e-13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.0002805936092045158</v>
+        <v>3.22033896673745e-14</v>
       </c>
       <c r="AB6" t="n">
-        <v>7.259473204612732e-05</v>
+        <v>2.469364502374199e-13</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0004042570653837174</v>
+        <v>2.887506585832339e-13</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0002096716780215502</v>
+        <v>2.552640173889009e-14</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0002273573190905154</v>
+        <v>1.207564457499435e-13</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0008401447557844222</v>
+        <v>2.889269769615344e-13</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0005395878688432276</v>
+        <v>5.705544543765928e-13</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0005237238947302103</v>
+        <v>1.646676095175617e-13</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0003068856312893331</v>
+        <v>3.076941370964981e-13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0004329434596002102</v>
+        <v>4.436013188724441e-14</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0001410448749084026</v>
+        <v>8.599663272072441e-14</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0001886684622149915</v>
+        <v>1.204195841349523e-13</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.392901322105899e-05</v>
+        <v>6.585042163246776e-14</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.0004099036450497806</v>
+        <v>1.16826158664575e-13</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0003152414865326136</v>
+        <v>2.996300039678768e-13</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0001436627935618162</v>
+        <v>1.044465349712281e-13</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.000364461011486128</v>
+        <v>1.649698579781964e-13</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0002215661661466584</v>
+        <v>2.380502208115115e-13</v>
       </c>
       <c r="AS6" t="n">
-        <v>6.744421261828393e-05</v>
+        <v>1.543266111691394e-13</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.327727219788358e-05</v>
+        <v>5.46875709322471e-14</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.000296454963972792</v>
+        <v>7.524983240692062e-13</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.1796233340865e-05</v>
+        <v>4.555637009122371e-13</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.0003643974487204105</v>
+        <v>3.765819849965019e-13</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0006339274113997817</v>
+        <v>3.359571464339045e-13</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0002684500650502741</v>
+        <v>9.576308929865052e-13</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.000864292960613966</v>
+        <v>1.889033769903251e-13</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0004344651242718101</v>
+        <v>4.7193114216873e-13</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.302966645918787e-05</v>
+        <v>4.172667934917648e-14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0003233444294892251</v>
+        <v>2.588396077335409e-13</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0001919512869790196</v>
+        <v>7.159416831083176e-13</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0001889333070721477</v>
+        <v>8.193016306622808e-14</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.856907566543669e-05</v>
+        <v>3.111327656016988e-13</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0008298733737319708</v>
+        <v>2.565409907076543e-13</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0008517280220985413</v>
+        <v>4.362929288681539e-13</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0001474163873353973</v>
+        <v>1.122698667973404e-13</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0003562001802492887</v>
+        <v>1.249918246161441e-12</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0002695145085453987</v>
+        <v>1.539122019937611e-13</v>
       </c>
       <c r="BL6" t="n">
-        <v>7.388446829281747e-05</v>
+        <v>2.508800187994015e-13</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0003905516059603542</v>
+        <v>1.429264557184159e-13</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0002335314929950982</v>
+        <v>9.547911235512768e-14</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.000389532302506268</v>
+        <v>1.156802789410022e-13</v>
       </c>
       <c r="BP6" t="n">
-        <v>3.629243292380124e-05</v>
+        <v>2.583578153931426e-13</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0003213523596059531</v>
+        <v>1.713348972247342e-13</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0004634697688743472</v>
+        <v>7.891894060994831e-14</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.081182851223275e-06</v>
+        <v>6.570369519721259e-14</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0002446687431074679</v>
+        <v>1.761522785276304e-13</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001066397089743987</v>
+        <v>8.391497132581582e-14</v>
       </c>
       <c r="BV6" t="n">
-        <v>7.101230585249141e-05</v>
+        <v>1.954945265999347e-15</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0001074028477887623</v>
+        <v>8.607182891764986e-15</v>
       </c>
       <c r="BX6" t="n">
-        <v>3.968073724536225e-05</v>
+        <v>5.763254457002986e-13</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0003535768482834101</v>
+        <v>5.251032898431762e-13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.494301927275956e-05</v>
+        <v>1.740210894222299e-13</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.000185456417966634</v>
+        <v>4.939642038502903e-14</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0001783736806828529</v>
+        <v>2.515282632783306e-13</v>
       </c>
       <c r="CC6" t="n">
-        <v>0.0002908254391513765</v>
+        <v>2.007414552510425e-14</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.538525096606463e-06</v>
+        <v>1.274863054749956e-13</v>
       </c>
       <c r="CE6" t="n">
-        <v>7.294514216482639e-05</v>
+        <v>8.866840502932613e-14</v>
       </c>
       <c r="CF6" t="n">
-        <v>8.041745604714379e-05</v>
+        <v>4.564804548354458e-14</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0001276532420888543</v>
+        <v>3.375424600742492e-14</v>
       </c>
       <c r="CH6" t="n">
-        <v>2.072601637337357e-05</v>
+        <v>1.969652468469113e-14</v>
       </c>
       <c r="CI6" t="n">
-        <v>3.91628491342999e-05</v>
+        <v>1.68455717040536e-13</v>
       </c>
       <c r="CJ6" t="n">
-        <v>9.396049426868558e-05</v>
+        <v>5.786240627261852e-14</v>
       </c>
       <c r="CK6" t="n">
-        <v>8.080811676336452e-05</v>
+        <v>7.469101292317815e-14</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.0001750083320075646</v>
+        <v>2.189224279289248e-13</v>
       </c>
       <c r="CM6" t="n">
-        <v>7.780479791108519e-06</v>
+        <v>3.271672212659671e-13</v>
       </c>
       <c r="CN6" t="n">
-        <v>7.53516360418871e-05</v>
+        <v>2.944771705128135e-13</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.892303771455772e-05</v>
+        <v>2.661574031916775e-13</v>
       </c>
       <c r="CP6" t="n">
-        <v>0.0002238943125121295</v>
+        <v>2.666900446139653e-13</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0004967898712493479</v>
+        <v>2.033445569045444e-13</v>
       </c>
       <c r="CR6" t="n">
-        <v>7.899380580056459e-05</v>
+        <v>3.190434299128048e-13</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.463212538510561e-05</v>
+        <v>6.733119378883601e-13</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.0002339824859518558</v>
+        <v>3.63825750126015e-13</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.0006487248465418816</v>
+        <v>4.900748860545145e-13</v>
       </c>
       <c r="CV6" t="n">
-        <v>1.841794073698111e-05</v>
+        <v>9.838741014392069e-14</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0001378910965286195</v>
+        <v>4.846775717858194e-14</v>
       </c>
       <c r="CX6" t="n">
-        <v>4.925714529235847e-05</v>
+        <v>6.377941930016742e-14</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0001189800532301888</v>
+        <v>2.399999754596101e-14</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.538205444579944e-05</v>
+        <v>1.810024433937171e-13</v>
       </c>
       <c r="DA6" t="n">
-        <v>5.699810208170675e-05</v>
+        <v>2.352001785606989e-13</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.307190152350813e-05</v>
+        <v>1.393880670608194e-13</v>
       </c>
       <c r="DC6" t="n">
-        <v>8.221388270612806e-05</v>
+        <v>7.013470072715286e-14</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.0001586856669746339</v>
+        <v>2.039843988166368e-13</v>
       </c>
       <c r="DE6" t="n">
-        <v>5.298174073686823e-05</v>
+        <v>5.623066031898438e-13</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0002956204116344452</v>
+        <v>7.99198218454783e-13</v>
       </c>
       <c r="DG6" t="n">
-        <v>9.387305908603594e-05</v>
+        <v>3.769447319383612e-13</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0005038958042860031</v>
+        <v>4.012812488980028e-13</v>
       </c>
       <c r="DI6" t="n">
-        <v>8.346172398887575e-05</v>
+        <v>9.194701207013156e-14</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0005070362240076065</v>
+        <v>1.007027902906465e-12</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0003051939711440355</v>
+        <v>1.073235331985542e-13</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.0002293440047651529</v>
+        <v>3.960684048526925e-13</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0006163899088278413</v>
+        <v>5.130458232728563e-14</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0002021896652877331</v>
+        <v>5.005104945950134e-13</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.163278557214653e-05</v>
+        <v>4.875308869719402e-14</v>
       </c>
       <c r="DP6" t="n">
-        <v>6.877630949020386e-05</v>
+        <v>2.99091806009455e-14</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0001354677660856396</v>
+        <v>7.98672597241562e-13</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.0005031282780691981</v>
+        <v>5.374468773668151e-13</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.0002287641982547939</v>
+        <v>2.465943302418921e-13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.0004020859487354755</v>
+        <v>4.004891307907849e-13</v>
       </c>
       <c r="DU6" t="n">
-        <v>2.28436038014479e-05</v>
+        <v>2.355473400963287e-13</v>
       </c>
       <c r="DV6" t="n">
-        <v>0.0006267474964261055</v>
+        <v>2.460143159609303e-14</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.0001689675846137106</v>
+        <v>1.378920171405881e-13</v>
       </c>
       <c r="DX6" t="n">
-        <v>7.008977991063148e-05</v>
+        <v>2.99494560011479e-13</v>
       </c>
       <c r="DY6" t="n">
-        <v>2.058866084553301e-05</v>
+        <v>3.625179583605087e-13</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.0003007215855177492</v>
+        <v>3.865188334326031e-13</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0002528757904656231</v>
+        <v>5.171631894430873e-13</v>
       </c>
       <c r="EB6" t="n">
-        <v>0.0002626730129122734</v>
+        <v>3.483399820761873e-13</v>
       </c>
       <c r="EC6" t="n">
-        <v>7.545908738393337e-05</v>
+        <v>2.151137612222548e-13</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0002156879345420748</v>
+        <v>1.514598722048704e-13</v>
       </c>
       <c r="EE6" t="n">
-        <v>0.0001036958856275305</v>
+        <v>1.348644096789767e-13</v>
       </c>
       <c r="EF6" t="n">
-        <v>4.200396506348625e-05</v>
+        <v>9.983448800727351e-15</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.0001032969303196296</v>
+        <v>3.595302495388447e-14</v>
       </c>
       <c r="EH6" t="n">
-        <v>0.0001080158399417996</v>
+        <v>2.400508177652361e-13</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0007136555504985154</v>
+        <v>3.114375077273301e-13</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.0001241475401911885</v>
+        <v>3.312798711567477e-13</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.0003461192827671766</v>
+        <v>2.024391125652475e-13</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0004192275227978826</v>
+        <v>6.89596627414038e-14</v>
       </c>
       <c r="EM6" t="n">
-        <v>9.832305659074336e-05</v>
+        <v>5.860530160120558e-14</v>
       </c>
       <c r="EN6" t="n">
-        <v>8.08403710834682e-05</v>
+        <v>2.571631872293895e-13</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0002012384356930852</v>
+        <v>1.569369905297241e-13</v>
       </c>
       <c r="EP6" t="n">
-        <v>2.233124905615114e-05</v>
+        <v>3.538637753045665e-13</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0.0001231679780175909</v>
+        <v>5.019883502475377e-14</v>
       </c>
       <c r="ER6" t="n">
-        <v>3.315590947750024e-05</v>
+        <v>9.10757200992679e-14</v>
       </c>
       <c r="ES6" t="n">
-        <v>3.858532727463171e-05</v>
+        <v>3.176234232224462e-13</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0002954125229734927</v>
+        <v>9.656446649242145e-14</v>
       </c>
       <c r="EU6" t="n">
-        <v>0.0001918051711982116</v>
+        <v>1.81237498424712e-13</v>
       </c>
       <c r="EV6" t="n">
-        <v>6.147997919470072e-05</v>
+        <v>2.895437795774614e-14</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001830282708397135</v>
+        <v>5.558830576835733e-14</v>
       </c>
       <c r="EX6" t="n">
-        <v>9.733324986882508e-06</v>
+        <v>1.203675288781458e-13</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.0001156888029072434</v>
+        <v>4.963737076533678e-14</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001106065901694819</v>
+        <v>3.363174471446122e-14</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.0001735420373734087</v>
+        <v>3.875384442606628e-14</v>
       </c>
       <c r="FB6" t="n">
-        <v>3.547090454958379e-05</v>
+        <v>1.437418977248694e-13</v>
       </c>
       <c r="FC6" t="n">
-        <v>4.47874772362411e-05</v>
+        <v>2.198460055495566e-13</v>
       </c>
       <c r="FD6" t="n">
-        <v>6.382774881785735e-05</v>
+        <v>9.3130940513695e-14</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.995722413994372e-05</v>
+        <v>9.812567696321911e-14</v>
       </c>
       <c r="FF6" t="n">
-        <v>6.572429265361279e-05</v>
+        <v>1.805402344550594e-13</v>
       </c>
       <c r="FG6" t="n">
-        <v>1.552962203277275e-06</v>
+        <v>5.749710603464298e-13</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0002209401282016188</v>
+        <v>1.925967930060599e-13</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0002198643196607009</v>
+        <v>2.112760650024165e-13</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0003743405977729708</v>
+        <v>1.089141594295441e-13</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0002737551985774189</v>
+        <v>3.430700276814413e-14</v>
       </c>
       <c r="FL6" t="n">
-        <v>5.193539254833013e-05</v>
+        <v>2.993912897545498e-13</v>
       </c>
       <c r="FM6" t="n">
-        <v>0.0001163759152404964</v>
+        <v>9.528775744794757e-14</v>
       </c>
       <c r="FN6" t="n">
-        <v>0.0001607865269761533</v>
+        <v>6.268715472927677e-13</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.000396751391235739</v>
+        <v>4.247963200816607e-13</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0004071700968779624</v>
+        <v>1.943664413445179e-13</v>
       </c>
       <c r="FQ6" t="n">
-        <v>8.003757830010727e-05</v>
+        <v>6.07337097280336e-13</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.000346920860465616</v>
+        <v>7.675775163043519e-13</v>
       </c>
       <c r="FS6" t="n">
-        <v>2.509190380806103e-05</v>
+        <v>1.075573007394692e-13</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.0005848652217537165</v>
+        <v>3.224074110984299e-13</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0007756901322863996</v>
+        <v>4.159999371345334e-14</v>
       </c>
       <c r="FV6" t="n">
-        <v>0.0001653112703934312</v>
+        <v>8.672056128755656e-13</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0003641304210759699</v>
+        <v>6.200941995125608e-13</v>
       </c>
       <c r="FX6" t="n">
-        <v>0.000133002846268937</v>
+        <v>2.867339612272479e-13</v>
       </c>
       <c r="FY6" t="n">
-        <v>8.017494110390544e-05</v>
+        <v>7.755497361938007e-14</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0003117637243121862</v>
+        <v>4.417507890519187e-14</v>
       </c>
       <c r="GA6" t="n">
-        <v>9.893549577100202e-05</v>
+        <v>2.250977046902233e-13</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0001035485838656314</v>
+        <v>1.274613688250284e-13</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0003398983972147107</v>
+        <v>4.66162481879695e-13</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0002615581615827978</v>
+        <v>2.537657041966346e-13</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.000659806770272553</v>
+        <v>1.312429270892545e-14</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0001482363586546853</v>
+        <v>4.398995816050355e-13</v>
       </c>
       <c r="GG6" t="n">
-        <v>0.0009156715823337436</v>
+        <v>8.97585093273881e-14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4.077234105892558e-09</v>
+        <v>3.839369533425617e-16</v>
       </c>
       <c r="B7" t="n">
-        <v>1.627692869377029e-09</v>
+        <v>4.165847795032946e-16</v>
       </c>
       <c r="C7" t="n">
-        <v>3.074924315171756e-09</v>
+        <v>2.008619414526247e-15</v>
       </c>
       <c r="D7" t="n">
-        <v>8.814159957459822e-10</v>
+        <v>1.944730472171934e-15</v>
       </c>
       <c r="E7" t="n">
-        <v>2.794886988510825e-09</v>
+        <v>9.191298506257446e-16</v>
       </c>
       <c r="F7" t="n">
-        <v>2.388008901732519e-09</v>
+        <v>3.927369056865287e-15</v>
       </c>
       <c r="G7" t="n">
-        <v>7.832890780434809e-09</v>
+        <v>4.941464218130684e-16</v>
       </c>
       <c r="H7" t="n">
-        <v>4.937348307976208e-10</v>
+        <v>2.983379742149694e-17</v>
       </c>
       <c r="I7" t="n">
-        <v>3.981135421327053e-10</v>
+        <v>3.212372875978408e-15</v>
       </c>
       <c r="J7" t="n">
-        <v>1.205161970219137e-09</v>
+        <v>3.358125646860718e-16</v>
       </c>
       <c r="K7" t="n">
-        <v>2.829995793263151e-09</v>
+        <v>2.898604979019339e-15</v>
       </c>
       <c r="L7" t="n">
-        <v>4.13569400947722e-09</v>
+        <v>1.765303694713292e-15</v>
       </c>
       <c r="M7" t="n">
-        <v>2.063082371606129e-09</v>
+        <v>3.850200543722157e-15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.406300942363714e-08</v>
+        <v>3.467938174516317e-16</v>
       </c>
       <c r="O7" t="n">
-        <v>3.138619364406736e-10</v>
+        <v>3.401109180802084e-15</v>
       </c>
       <c r="P7" t="n">
-        <v>3.300309581177885e-09</v>
+        <v>1.41180910549505e-15</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.829006527984347e-09</v>
+        <v>1.687195292636066e-15</v>
       </c>
       <c r="R7" t="n">
-        <v>3.883353194567007e-09</v>
+        <v>2.109316173603496e-15</v>
       </c>
       <c r="S7" t="n">
-        <v>3.228709521962969e-10</v>
+        <v>7.113302752307217e-16</v>
       </c>
       <c r="T7" t="n">
-        <v>4.035195511065126e-10</v>
+        <v>2.008304741786342e-15</v>
       </c>
       <c r="U7" t="n">
-        <v>7.539284196944607e-10</v>
+        <v>5.575954364304015e-16</v>
       </c>
       <c r="V7" t="n">
-        <v>2.099872720151552e-09</v>
+        <v>1.938359302100924e-15</v>
       </c>
       <c r="W7" t="n">
-        <v>7.122403777870545e-10</v>
+        <v>3.503358339513414e-15</v>
       </c>
       <c r="X7" t="n">
-        <v>4.42681269419154e-09</v>
+        <v>1.650612257281508e-15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.863012188962898e-09</v>
+        <v>7.726961711329605e-16</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.108101721492005e-09</v>
+        <v>1.169242162807468e-15</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.387600253760951e-11</v>
+        <v>6.546894996851819e-16</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.027265382815614e-10</v>
+        <v>6.470365040671801e-16</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.787993503254981e-10</v>
+        <v>6.620351282224488e-16</v>
       </c>
       <c r="AD7" t="n">
-        <v>3.709332840884372e-09</v>
+        <v>1.27076012032708e-15</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.579869899463574e-09</v>
+        <v>2.074830709463695e-15</v>
       </c>
       <c r="AF7" t="n">
-        <v>3.487091171372469e-10</v>
+        <v>9.034044457319521e-17</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.599995802514798e-09</v>
+        <v>1.637725921538455e-15</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.137614973918289e-09</v>
+        <v>5.748640030051933e-16</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.606124788722241e-09</v>
+        <v>1.809700291368916e-15</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.681262323278588e-09</v>
+        <v>4.786532892352808e-16</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.422769235759347e-09</v>
+        <v>1.066582616633194e-15</v>
       </c>
       <c r="AL7" t="n">
-        <v>3.368260947933521e-10</v>
+        <v>9.218701080892307e-16</v>
       </c>
       <c r="AM7" t="n">
-        <v>3.819973504182173e-10</v>
+        <v>4.555325190883498e-16</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.32141986242118e-09</v>
+        <v>2.104883861948751e-15</v>
       </c>
       <c r="AO7" t="n">
-        <v>4.440118051007858e-09</v>
+        <v>1.202543898403481e-15</v>
       </c>
       <c r="AP7" t="n">
-        <v>9.882131779548331e-10</v>
+        <v>7.48816300646612e-17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.2298037033176e-09</v>
+        <v>2.703492263108291e-16</v>
       </c>
       <c r="AR7" t="n">
-        <v>2.273337962321875e-09</v>
+        <v>8.918818595037578e-16</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.906393931605521e-10</v>
+        <v>7.521034237566691e-16</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.274892413860584e-10</v>
+        <v>2.645518416522451e-16</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.027290749306303e-09</v>
+        <v>4.350883836426542e-15</v>
       </c>
       <c r="AV7" t="n">
-        <v>8.800048467705324e-10</v>
+        <v>3.801106672917976e-16</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.041489530872468e-10</v>
+        <v>8.056923925328109e-16</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.70388325670956e-09</v>
+        <v>1.536568482417018e-15</v>
       </c>
       <c r="AY7" t="n">
-        <v>3.793760861015016e-09</v>
+        <v>5.094353929807881e-17</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.493835386616297e-10</v>
+        <v>3.640066916101416e-16</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.169629726405219e-09</v>
+        <v>1.201727676279683e-15</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.85183085427343e-09</v>
+        <v>9.369955754283507e-16</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.933590842995159e-09</v>
+        <v>1.231889990135817e-15</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.035454110289493e-10</v>
+        <v>1.566347937380992e-15</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.404159316071741e-09</v>
+        <v>5.795725003403024e-17</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.534991994096458e-09</v>
+        <v>1.441469975846409e-15</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.806294390784615e-09</v>
+        <v>3.460370464528192e-16</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.278334353458035e-10</v>
+        <v>1.914079102667879e-15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.014399202998618e-10</v>
+        <v>9.963271628890807e-16</v>
       </c>
       <c r="BJ7" t="n">
-        <v>1.611834665737888e-09</v>
+        <v>1.178552325447214e-15</v>
       </c>
       <c r="BK7" t="n">
-        <v>4.492941130251893e-09</v>
+        <v>9.597824557753859e-16</v>
       </c>
       <c r="BL7" t="n">
-        <v>7.768118925888245e-10</v>
+        <v>1.277531195828312e-15</v>
       </c>
       <c r="BM7" t="n">
-        <v>5.299731320462797e-09</v>
+        <v>1.47529951884768e-15</v>
       </c>
       <c r="BN7" t="n">
-        <v>4.606709458343516e-10</v>
+        <v>1.460390415487025e-16</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.035592722686829e-09</v>
+        <v>3.359450724027579e-16</v>
       </c>
       <c r="BP7" t="n">
-        <v>1.209682842784332e-08</v>
+        <v>2.018093478041287e-15</v>
       </c>
       <c r="BQ7" t="n">
-        <v>3.227013989359762e-09</v>
+        <v>1.688391303157589e-15</v>
       </c>
       <c r="BR7" t="n">
-        <v>3.05182656923364e-09</v>
+        <v>1.862597498924947e-15</v>
       </c>
       <c r="BS7" t="n">
-        <v>4.868522474055226e-09</v>
+        <v>2.601620404635405e-16</v>
       </c>
       <c r="BT7" t="n">
-        <v>6.48685549720085e-10</v>
+        <v>3.019189648181646e-16</v>
       </c>
       <c r="BU7" t="n">
-        <v>8.622747516007223e-10</v>
+        <v>1.72588256958984e-17</v>
       </c>
       <c r="BV7" t="n">
-        <v>3.556628103140724e-09</v>
+        <v>4.423337605366577e-16</v>
       </c>
       <c r="BW7" t="n">
-        <v>9.904400632976262e-10</v>
+        <v>1.026012703075029e-15</v>
       </c>
       <c r="BX7" t="n">
-        <v>1.959389539507583e-09</v>
+        <v>1.964055105347067e-15</v>
       </c>
       <c r="BY7" t="n">
-        <v>4.626897087689485e-09</v>
+        <v>1.828298170275305e-15</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.67152358621081e-09</v>
+        <v>2.09509893734207e-15</v>
       </c>
       <c r="CA7" t="n">
-        <v>2.2507109509462e-09</v>
+        <v>2.108618641971432e-16</v>
       </c>
       <c r="CB7" t="n">
-        <v>5.981288797585194e-10</v>
+        <v>1.584966145078115e-15</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.254495257147937e-09</v>
+        <v>1.801036414867925e-15</v>
       </c>
       <c r="CD7" t="n">
-        <v>4.484899951417987e-10</v>
+        <v>3.610850896866043e-16</v>
       </c>
       <c r="CE7" t="n">
-        <v>8.426584985343766e-10</v>
+        <v>8.776813786128191e-17</v>
       </c>
       <c r="CF7" t="n">
-        <v>6.969647081689345e-11</v>
+        <v>2.858387325288113e-16</v>
       </c>
       <c r="CG7" t="n">
-        <v>6.464427881880397e-10</v>
+        <v>8.161088331412299e-16</v>
       </c>
       <c r="CH7" t="n">
-        <v>3.153706185088367e-10</v>
+        <v>5.565684089818557e-17</v>
       </c>
       <c r="CI7" t="n">
-        <v>8.809989404667817e-10</v>
+        <v>6.708317771379215e-16</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.572897034840537e-09</v>
+        <v>2.855922459411603e-16</v>
       </c>
       <c r="CK7" t="n">
-        <v>5.979499118069498e-10</v>
+        <v>3.808439066565442e-16</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.018993778245658e-09</v>
+        <v>8.435323189019759e-16</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.777806429321572e-09</v>
+        <v>3.939501533285284e-16</v>
       </c>
       <c r="CN7" t="n">
-        <v>4.614638005051575e-09</v>
+        <v>1.848939304408708e-15</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.222490109142882e-09</v>
+        <v>1.161841847705544e-15</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.385135006692906e-09</v>
+        <v>3.044068064633689e-16</v>
       </c>
       <c r="CQ7" t="n">
-        <v>7.529549428397786e-09</v>
+        <v>8.086003625198534e-16</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.45745815416376e-09</v>
+        <v>1.248021520858038e-16</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.604084725632561e-09</v>
+        <v>7.755258964515003e-17</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.942714155158455e-09</v>
+        <v>7.975588115963607e-16</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.857013209871639e-09</v>
+        <v>1.008762241829484e-15</v>
       </c>
       <c r="CV7" t="n">
-        <v>6.537761998437475e-11</v>
+        <v>5.455338990197371e-16</v>
       </c>
       <c r="CW7" t="n">
-        <v>9.648938315010014e-10</v>
+        <v>2.256415700402161e-17</v>
       </c>
       <c r="CX7" t="n">
-        <v>1.000472760193105e-10</v>
+        <v>1.772151744333606e-16</v>
       </c>
       <c r="CY7" t="n">
-        <v>4.316516033497919e-10</v>
+        <v>9.295084394493332e-16</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.950378469839364e-10</v>
+        <v>1.769766023098106e-16</v>
       </c>
       <c r="DA7" t="n">
-        <v>8.06191224889119e-10</v>
+        <v>6.512186233651298e-16</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.787309411582783e-09</v>
+        <v>1.326536445810388e-16</v>
       </c>
       <c r="DC7" t="n">
-        <v>5.523468349366567e-10</v>
+        <v>2.195519193101599e-16</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.941651644494669e-10</v>
+        <v>7.340094765143372e-16</v>
       </c>
       <c r="DE7" t="n">
-        <v>5.160614158228327e-09</v>
+        <v>3.654717939110955e-16</v>
       </c>
       <c r="DF7" t="n">
-        <v>7.17965686902744e-09</v>
+        <v>8.505352167329601e-16</v>
       </c>
       <c r="DG7" t="n">
-        <v>1.253815051782681e-09</v>
+        <v>6.28628360540976e-16</v>
       </c>
       <c r="DH7" t="n">
-        <v>9.532561406899731e-09</v>
+        <v>1.187586249467036e-15</v>
       </c>
       <c r="DI7" t="n">
-        <v>6.791747608758669e-09</v>
+        <v>3.414778386746638e-16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>3.430808304116795e-09</v>
+        <v>1.598565576683638e-15</v>
       </c>
       <c r="DK7" t="n">
-        <v>8.071571855339243e-09</v>
+        <v>5.028389915551473e-16</v>
       </c>
       <c r="DL7" t="n">
-        <v>5.525671920025843e-09</v>
+        <v>8.304894408823582e-16</v>
       </c>
       <c r="DM7" t="n">
-        <v>1.595918730501467e-09</v>
+        <v>6.65932115054529e-16</v>
       </c>
       <c r="DN7" t="n">
-        <v>1.16067588873392e-09</v>
+        <v>2.089295570513295e-16</v>
       </c>
       <c r="DO7" t="n">
-        <v>6.814443453961871e-10</v>
+        <v>2.296906654607775e-16</v>
       </c>
       <c r="DP7" t="n">
-        <v>1.059854648488567e-09</v>
+        <v>2.122084745297101e-16</v>
       </c>
       <c r="DQ7" t="n">
-        <v>8.000577977895773e-11</v>
+        <v>1.555512162524123e-15</v>
       </c>
       <c r="DR7" t="n">
-        <v>2.143904609397396e-09</v>
+        <v>5.303663976706095e-16</v>
       </c>
       <c r="DS7" t="n">
-        <v>2.188261238877942e-10</v>
+        <v>1.472846723190669e-15</v>
       </c>
       <c r="DT7" t="n">
-        <v>3.658703340292391e-09</v>
+        <v>1.205298237789715e-15</v>
       </c>
       <c r="DU7" t="n">
-        <v>2.314715530360445e-09</v>
+        <v>5.226490275486164e-16</v>
       </c>
       <c r="DV7" t="n">
-        <v>5.156401972072899e-10</v>
+        <v>3.983053849850732e-16</v>
       </c>
       <c r="DW7" t="n">
-        <v>5.373659850427259e-10</v>
+        <v>1.124228185012414e-15</v>
       </c>
       <c r="DX7" t="n">
-        <v>6.548410702578167e-10</v>
+        <v>3.57884972742098e-16</v>
       </c>
       <c r="DY7" t="n">
-        <v>1.450341735598215e-09</v>
+        <v>4.392276642492966e-16</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.901281881406703e-09</v>
+        <v>5.920795241416634e-16</v>
       </c>
       <c r="EA7" t="n">
-        <v>1.901732660236632e-10</v>
+        <v>3.102463574808584e-16</v>
       </c>
       <c r="EB7" t="n">
-        <v>2.201241411370347e-10</v>
+        <v>2.647565589276846e-17</v>
       </c>
       <c r="EC7" t="n">
-        <v>1.833682206076048e-09</v>
+        <v>1.238931586784579e-15</v>
       </c>
       <c r="ED7" t="n">
-        <v>4.191352598326148e-09</v>
+        <v>2.582638925683028e-16</v>
       </c>
       <c r="EE7" t="n">
-        <v>1.360402235306424e-09</v>
+        <v>5.300819534190097e-16</v>
       </c>
       <c r="EF7" t="n">
-        <v>7.703478410725495e-10</v>
+        <v>2.484447690063757e-16</v>
       </c>
       <c r="EG7" t="n">
-        <v>2.376263630310405e-09</v>
+        <v>5.905648704132951e-16</v>
       </c>
       <c r="EH7" t="n">
-        <v>1.232480006940762e-09</v>
+        <v>5.446369970077132e-16</v>
       </c>
       <c r="EI7" t="n">
-        <v>3.480971066949223e-09</v>
+        <v>1.600151751756491e-15</v>
       </c>
       <c r="EJ7" t="n">
-        <v>7.23547333159047e-10</v>
+        <v>2.698195395512196e-16</v>
       </c>
       <c r="EK7" t="n">
-        <v>2.093454964935404e-09</v>
+        <v>4.426439069442508e-16</v>
       </c>
       <c r="EL7" t="n">
-        <v>2.00752678369831e-10</v>
+        <v>3.305615956878056e-16</v>
       </c>
       <c r="EM7" t="n">
-        <v>9.403915424144316e-10</v>
+        <v>6.124102736394571e-16</v>
       </c>
       <c r="EN7" t="n">
-        <v>6.984694489453602e-10</v>
+        <v>1.005512070531751e-15</v>
       </c>
       <c r="EO7" t="n">
-        <v>3.141438775777772e-10</v>
+        <v>6.956588951570963e-16</v>
       </c>
       <c r="EP7" t="n">
-        <v>8.750118407618857e-10</v>
+        <v>1.634020575910691e-15</v>
       </c>
       <c r="EQ7" t="n">
-        <v>2.633546436481282e-10</v>
+        <v>1.386373764880188e-15</v>
       </c>
       <c r="ER7" t="n">
-        <v>2.619897854216902e-09</v>
+        <v>3.56478686291419e-16</v>
       </c>
       <c r="ES7" t="n">
-        <v>1.022946172213324e-10</v>
+        <v>3.022759627356527e-16</v>
       </c>
       <c r="ET7" t="n">
-        <v>7.076847996501101e-10</v>
+        <v>1.385757124894586e-15</v>
       </c>
       <c r="EU7" t="n">
-        <v>1.498894564022635e-09</v>
+        <v>1.044291144681184e-15</v>
       </c>
       <c r="EV7" t="n">
-        <v>8.454268396462794e-10</v>
+        <v>6.004068109252388e-16</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.822364703585322e-09</v>
+        <v>6.314571329474501e-16</v>
       </c>
       <c r="EX7" t="n">
-        <v>2.251155512000835e-10</v>
+        <v>7.888588832555526e-16</v>
       </c>
       <c r="EY7" t="n">
-        <v>3.412084503828794e-10</v>
+        <v>1.619507804560011e-16</v>
       </c>
       <c r="EZ7" t="n">
-        <v>1.543659644553941e-10</v>
+        <v>4.384814546925451e-16</v>
       </c>
       <c r="FA7" t="n">
-        <v>2.610997529295389e-10</v>
+        <v>9.042165650399118e-16</v>
       </c>
       <c r="FB7" t="n">
-        <v>3.790412428372747e-10</v>
+        <v>5.732312014155729e-17</v>
       </c>
       <c r="FC7" t="n">
-        <v>1.822210826674109e-09</v>
+        <v>7.87594792460894e-16</v>
       </c>
       <c r="FD7" t="n">
-        <v>1.998434751016021e-09</v>
+        <v>4.738713647315566e-16</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.269305993645276e-09</v>
+        <v>3.258859208794026e-16</v>
       </c>
       <c r="FF7" t="n">
-        <v>2.156731182534344e-10</v>
+        <v>8.782885688871024e-16</v>
       </c>
       <c r="FG7" t="n">
-        <v>8.845785770539294e-10</v>
+        <v>2.30046440474448e-15</v>
       </c>
       <c r="FH7" t="n">
-        <v>1.307574937214895e-09</v>
+        <v>5.054551586918606e-16</v>
       </c>
       <c r="FI7" t="n">
-        <v>4.125934871535009e-10</v>
+        <v>1.0419109820994e-15</v>
       </c>
       <c r="FJ7" t="n">
-        <v>1.357994383610617e-09</v>
+        <v>3.375716403592821e-16</v>
       </c>
       <c r="FK7" t="n">
-        <v>9.946385937098512e-10</v>
+        <v>1.1564870377619e-16</v>
       </c>
       <c r="FL7" t="n">
-        <v>3.075009136210838e-10</v>
+        <v>9.659845368943003e-16</v>
       </c>
       <c r="FM7" t="n">
-        <v>1.27498012147953e-10</v>
+        <v>1.462430547280046e-15</v>
       </c>
       <c r="FN7" t="n">
-        <v>2.311833391388518e-09</v>
+        <v>1.204294371398321e-16</v>
       </c>
       <c r="FO7" t="n">
-        <v>2.379559660425912e-09</v>
+        <v>8.379631302133381e-16</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.172108048981158e-09</v>
+        <v>5.16468810467653e-17</v>
       </c>
       <c r="FQ7" t="n">
-        <v>5.835575578316821e-09</v>
+        <v>4.384275357514965e-16</v>
       </c>
       <c r="FR7" t="n">
-        <v>1.494821044722983e-09</v>
+        <v>3.279640632759318e-16</v>
       </c>
       <c r="FS7" t="n">
-        <v>2.240208907267061e-09</v>
+        <v>1.280652088722471e-15</v>
       </c>
       <c r="FT7" t="n">
-        <v>4.779138196298049e-11</v>
+        <v>1.849635141974878e-15</v>
       </c>
       <c r="FU7" t="n">
-        <v>3.601333897762515e-09</v>
+        <v>1.333297833372286e-15</v>
       </c>
       <c r="FV7" t="n">
-        <v>7.166762738819443e-10</v>
+        <v>1.901571178894012e-15</v>
       </c>
       <c r="FW7" t="n">
-        <v>1.207006716796855e-09</v>
+        <v>9.147714425956476e-16</v>
       </c>
       <c r="FX7" t="n">
-        <v>1.147959949321375e-09</v>
+        <v>1.179547483281119e-15</v>
       </c>
       <c r="FY7" t="n">
-        <v>1.417128497882558e-10</v>
+        <v>5.397088005019101e-16</v>
       </c>
       <c r="FZ7" t="n">
-        <v>2.619521044522344e-09</v>
+        <v>5.599961925007162e-16</v>
       </c>
       <c r="GA7" t="n">
-        <v>3.759723199436849e-09</v>
+        <v>3.03860390803051e-16</v>
       </c>
       <c r="GB7" t="n">
-        <v>1.9128851835859e-09</v>
+        <v>8.016845502637588e-16</v>
       </c>
       <c r="GC7" t="n">
-        <v>5.431930905075433e-09</v>
+        <v>6.261871057078707e-16</v>
       </c>
       <c r="GD7" t="n">
-        <v>4.06117539597517e-09</v>
+        <v>1.260191266727714e-15</v>
       </c>
       <c r="GE7" t="n">
-        <v>1.896371726317625e-09</v>
+        <v>1.691027428508122e-16</v>
       </c>
       <c r="GF7" t="n">
-        <v>2.226286488493656e-09</v>
+        <v>4.612199218126888e-16</v>
       </c>
       <c r="GG7" t="n">
-        <v>1.669785421043457e-09</v>
+        <v>5.222443575580657e-16</v>
       </c>
     </row>
     <row r="8">
@@ -4982,4554 +4982,4554 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.0004667385946959257</v>
+        <v>9.905016806754929e-10</v>
       </c>
       <c r="B9" t="n">
-        <v>0.005443087313324213</v>
+        <v>1.012681671852533e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000149565443280153</v>
+        <v>1.949840289228177e-10</v>
       </c>
       <c r="D9" t="n">
-        <v>0.006341524422168732</v>
+        <v>4.286289545518684e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003005605889484286</v>
+        <v>6.374484939897229e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002420359989628196</v>
+        <v>1.34963666909016e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001042213873006403</v>
+        <v>7.592918294108131e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001486436347477138</v>
+        <v>8.958688013649407e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001218240475282073</v>
+        <v>1.073079403113297e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0003548212116584182</v>
+        <v>3.809720094949398e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004250815603882074</v>
+        <v>1.320977460750328e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001724361442029476</v>
+        <v>1.900675616894887e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>0.005107717588543892</v>
+        <v>9.486960550475487e-09</v>
       </c>
       <c r="N9" t="n">
-        <v>0.004964519757777452</v>
+        <v>1.259490733929169e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>0.003290031105279922</v>
+        <v>1.579857666911266e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0003520383615978062</v>
+        <v>6.898998261561928e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.0001606265577720478</v>
+        <v>3.286176664119012e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>0.001909072510898113</v>
+        <v>3.260173686570056e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0005600650911219418</v>
+        <v>6.36347974314333e-10</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001079541863873601</v>
+        <v>2.3494424183923e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0005450000753626227</v>
+        <v>3.958937178083488e-09</v>
       </c>
       <c r="V9" t="n">
-        <v>0.001243163133040071</v>
+        <v>1.683825856524379e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>0.00137790129519999</v>
+        <v>4.45989600805774e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0009870132198557258</v>
+        <v>2.042964020176896e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001537920674309134</v>
+        <v>2.143401456322636e-09</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0004649166949093342</v>
+        <v>7.095714571470069e-10</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.0006600775523111224</v>
+        <v>2.88363732892094e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.191871706396341e-05</v>
+        <v>7.362878640115866e-10</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0007444618386216462</v>
+        <v>2.461440828938066e-09</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.000107640640635509</v>
+        <v>3.320091090941446e-09</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.001030178158544004</v>
+        <v>2.129123544136746e-09</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.001654905965551734</v>
+        <v>5.558161930707683e-09</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0007521640509366989</v>
+        <v>8.528105333027725e-09</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.0004556706117000431</v>
+        <v>5.78073200419027e-10</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.0001092228194465861</v>
+        <v>9.656047517125899e-09</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.133407052606344e-05</v>
+        <v>1.308769204122484e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0004018832114525139</v>
+        <v>5.288494087096751e-10</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0003587728133425117</v>
+        <v>1.640817925974147e-09</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0002249883837066591</v>
+        <v>5.439941830331918e-09</v>
       </c>
       <c r="AN9" t="n">
-        <v>6.108806701377034e-05</v>
+        <v>2.215897465518424e-09</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001786262029781938</v>
+        <v>4.112321150273601e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.001157869701273739</v>
+        <v>1.855297027120173e-09</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9.217369370162487e-05</v>
+        <v>1.857234366298144e-10</v>
       </c>
       <c r="AR9" t="n">
-        <v>6.865931209176779e-05</v>
+        <v>1.370545454904004e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.0006868946948088706</v>
+        <v>4.363640004889646e-10</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.001172066549770534</v>
+        <v>1.445524366872064e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.005230034235864878</v>
+        <v>8.230367498640589e-09</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.0006196141475811601</v>
+        <v>7.274458813100182e-09</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.002372078131884336</v>
+        <v>7.182156536167383e-10</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.0002554180682636797</v>
+        <v>1.253779657872656e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.0003952333354391158</v>
+        <v>1.23950734121081e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.001520748250186443</v>
+        <v>3.372555568148528e-10</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.00186778255738318</v>
+        <v>1.116118530930521e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.92676268145442e-05</v>
+        <v>1.979236552429597e-09</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0003596517199184746</v>
+        <v>2.375736940507522e-09</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0005031275795772672</v>
+        <v>2.824028122461186e-09</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0008107285830192268</v>
+        <v>2.204817883821875e-09</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0005777464248239994</v>
+        <v>3.811631010819383e-10</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.002717131748795509</v>
+        <v>5.576789252614844e-09</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.003218764439225197</v>
+        <v>2.750113026195322e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.001790870213881135</v>
+        <v>1.506096358738773e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>6.061200110707432e-06</v>
+        <v>7.493960119120402e-09</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.001314273336902261</v>
+        <v>3.422893968263452e-09</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0007418667082674801</v>
+        <v>3.336138865162042e-10</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.002674282761290669</v>
+        <v>6.561534426907656e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0008706196094863117</v>
+        <v>1.264540028245165e-09</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.0009996260050684214</v>
+        <v>3.965633599278817e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.001775654731318355</v>
+        <v>4.198000613797603e-09</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.0009897167328745127</v>
+        <v>1.948668337803383e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.0001005601952783763</v>
+        <v>4.570684275506665e-09</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.0003294487542007118</v>
+        <v>1.713769126610032e-09</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.001047661295160651</v>
+        <v>1.118030334978926e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.001153446268290281</v>
+        <v>1.501165081130296e-09</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.002585562877357006</v>
+        <v>5.790274926198435e-09</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0004324596375226974</v>
+        <v>3.36937766576284e-09</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.001790771377272904</v>
+        <v>3.094725364860551e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.0004248102777637541</v>
+        <v>3.495131517539107e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.0008692661067470908</v>
+        <v>4.282644461284235e-09</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.0001637492096051574</v>
+        <v>3.063176157169778e-09</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.001504014013335109</v>
+        <v>1.64180136152936e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.00091634935233742</v>
+        <v>2.953252975501641e-09</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.0003314238274469972</v>
+        <v>7.466156581870109e-10</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.0007326128543354571</v>
+        <v>3.543870308320152e-09</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0004640276310965419</v>
+        <v>7.303689320004025e-10</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.0007932265871204436</v>
+        <v>1.602120547339325e-09</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.0001604751887498423</v>
+        <v>2.679366506441738e-09</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.0001822557969717309</v>
+        <v>3.869143672119435e-09</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002793273597490042</v>
+        <v>6.376957850662279e-10</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.000247842661337927</v>
+        <v>9.595950700713729e-10</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.0002144956379197538</v>
+        <v>7.50775330793374e-10</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.001302448217757046</v>
+        <v>5.826789273299937e-09</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.0009127530502155423</v>
+        <v>4.830413402601152e-09</v>
       </c>
       <c r="CO9" t="n">
-        <v>2.284843503730372e-05</v>
+        <v>1.028221952026342e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.001978406915441155</v>
+        <v>3.013090665859863e-09</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001259270589798689</v>
+        <v>2.423779510429824e-10</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.0001410884578945115</v>
+        <v>4.836750555625713e-09</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.0015031264629215</v>
+        <v>3.525379765889625e-09</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.00322405993938446</v>
+        <v>2.030664969510099e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.000107348918390926</v>
+        <v>6.893110526817736e-10</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0003682399983517826</v>
+        <v>9.518557053667109e-10</v>
       </c>
       <c r="CW9" t="n">
-        <v>0.0005559611017815769</v>
+        <v>2.935011345073235e-09</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.000648140034172684</v>
+        <v>6.397259944002087e-10</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.0009575634612701833</v>
+        <v>2.239949781213113e-09</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004329904040787369</v>
+        <v>3.721877694928821e-09</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.000270586577244103</v>
+        <v>4.230523042991763e-09</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.0003191399737261236</v>
+        <v>1.972380730963508e-10</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.000357089884346351</v>
+        <v>8.172849064180809e-10</v>
       </c>
       <c r="DD9" t="n">
-        <v>7.76375163695775e-05</v>
+        <v>6.455701528906843e-10</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.0001716398692224175</v>
+        <v>3.631698053396804e-09</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.0005853757029399276</v>
+        <v>3.540876925001157e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>7.921735232230276e-05</v>
+        <v>1.174046859730993e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.002536637708544731</v>
+        <v>1.553516426611168e-09</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0005653343396261334</v>
+        <v>1.829629781013864e-10</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.000948021886870265</v>
+        <v>7.783339306399739e-09</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.00111664819996804</v>
+        <v>9.819683954859215e-11</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.0007931066211313009</v>
+        <v>6.966323518042827e-09</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.0005060152616351843</v>
+        <v>3.19147663851993e-09</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.0004780548042617738</v>
+        <v>2.622705608246179e-09</v>
       </c>
       <c r="DO9" t="n">
-        <v>3.209074202459306e-05</v>
+        <v>4.207575621251181e-09</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.0005235241842456162</v>
+        <v>1.038039321166195e-09</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.0005427561700344086</v>
+        <v>3.261126479969789e-09</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0002640521270222962</v>
+        <v>4.074793835684432e-09</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001008630642900243</v>
+        <v>1.841551133807684e-09</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.001175103592686355</v>
+        <v>1.159456641808276e-09</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.0001478179765399545</v>
+        <v>2.990323322293875e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>0.0001654692459851503</v>
+        <v>2.756569861261937e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>8.992468065116554e-05</v>
+        <v>3.36255856492329e-10</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.0003310571773909032</v>
+        <v>6.14048978331283e-10</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.0009190621203742921</v>
+        <v>4.460298796971074e-09</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.046761023346335e-05</v>
+        <v>1.603782440184887e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.0003201560175511986</v>
+        <v>4.126505359636212e-09</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.001369915553368628</v>
+        <v>5.286118653913263e-09</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.0005202855099923909</v>
+        <v>3.076006338531556e-09</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.0006033008685335517</v>
+        <v>3.108012069930055e-09</v>
       </c>
       <c r="EE9" t="n">
-        <v>2.071302151307464e-05</v>
+        <v>5.451917584053945e-09</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0001704675087239593</v>
+        <v>1.026930984693308e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>1.297499693464488e-05</v>
+        <v>2.863128845120855e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.0004011935961898416</v>
+        <v>5.199993324822572e-09</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.001236312906257808</v>
+        <v>3.92487109479589e-09</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.0009459832217544317</v>
+        <v>8.915722049529506e-10</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0002916414814535528</v>
+        <v>4.54306459118925e-09</v>
       </c>
       <c r="EL9" t="n">
-        <v>0.0004811454855371267</v>
+        <v>5.734369645793436e-10</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.778973455657251e-05</v>
+        <v>3.562630052078575e-11</v>
       </c>
       <c r="EN9" t="n">
-        <v>0.0004985093837603927</v>
+        <v>2.436146839812636e-09</v>
       </c>
       <c r="EO9" t="n">
-        <v>3.054249100387096e-05</v>
+        <v>5.994871266068458e-10</v>
       </c>
       <c r="EP9" t="n">
-        <v>0.0008681351901032031</v>
+        <v>4.07026812254685e-09</v>
       </c>
       <c r="EQ9" t="n">
-        <v>7.02693869243376e-05</v>
+        <v>3.413471727498063e-09</v>
       </c>
       <c r="ER9" t="n">
-        <v>8.366993279196322e-05</v>
+        <v>2.895183204287832e-09</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0004713318194262683</v>
+        <v>4.008308129854754e-10</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.001446884591132402</v>
+        <v>2.54958876233502e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.001250849105417728</v>
+        <v>1.262452808958869e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0007897078758105636</v>
+        <v>4.74534300742846e-11</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0003364784934092313</v>
+        <v>5.352796428326201e-09</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.0001210626869578846</v>
+        <v>5.450077056323721e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.0005485400906763971</v>
+        <v>3.508569879073775e-09</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.0003200508945155889</v>
+        <v>3.992334240976447e-10</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.0009184966329485178</v>
+        <v>2.05971728561849e-09</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.0005411127931438386</v>
+        <v>2.518225183933964e-09</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.0004086867847945541</v>
+        <v>3.938191994734552e-09</v>
       </c>
       <c r="FD9" t="n">
-        <v>0.0004201305564492941</v>
+        <v>1.513685843335111e-09</v>
       </c>
       <c r="FE9" t="n">
-        <v>0.0004258734697941691</v>
+        <v>4.622261462472466e-10</v>
       </c>
       <c r="FF9" t="n">
-        <v>0.0001807054941309616</v>
+        <v>7.687635528164094e-10</v>
       </c>
       <c r="FG9" t="n">
-        <v>5.249372043181211e-05</v>
+        <v>1.774860258763056e-09</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.0003451696247793734</v>
+        <v>1.956360629051801e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>0.0003514894633553922</v>
+        <v>4.092468586236464e-09</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.0007854964351281524</v>
+        <v>4.076740278691204e-09</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.0008026529685594141</v>
+        <v>1.027679885634569e-10</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.0002073114446830004</v>
+        <v>2.863749237747015e-09</v>
       </c>
       <c r="FM9" t="n">
-        <v>0.0005875201313756406</v>
+        <v>9.488553276426615e-10</v>
       </c>
       <c r="FN9" t="n">
-        <v>2.23122478928417e-05</v>
+        <v>4.53959758672795e-09</v>
       </c>
       <c r="FO9" t="n">
-        <v>0.0001858690084191039</v>
+        <v>8.569263520996628e-09</v>
       </c>
       <c r="FP9" t="n">
-        <v>9.600348130334169e-05</v>
+        <v>7.796204570809095e-09</v>
       </c>
       <c r="FQ9" t="n">
-        <v>0.001274461508728564</v>
+        <v>5.845830930439888e-09</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0002370479196542874</v>
+        <v>7.501416376953784e-09</v>
       </c>
       <c r="FS9" t="n">
-        <v>0.0009757519001141191</v>
+        <v>5.123956814401254e-11</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.002883289009332657</v>
+        <v>1.296012897000764e-08</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.0007871423731558025</v>
+        <v>1.758763357173621e-09</v>
       </c>
       <c r="FV9" t="n">
-        <v>0.0003689320292323828</v>
+        <v>3.469980525139249e-09</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.788779627531767e-06</v>
+        <v>1.413677352957166e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>0.0001641337003093213</v>
+        <v>2.706622481696286e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>0.0009531675605103374</v>
+        <v>3.212044852318741e-09</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0003499632584862411</v>
+        <v>3.764185407817422e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.0006015406106598675</v>
+        <v>2.758409944902951e-09</v>
       </c>
       <c r="GB9" t="n">
-        <v>0.0005972652579657733</v>
+        <v>2.531462595101175e-09</v>
       </c>
       <c r="GC9" t="n">
-        <v>0.0004064585373271257</v>
+        <v>3.711480456303207e-09</v>
       </c>
       <c r="GD9" t="n">
-        <v>0.001163253909908235</v>
+        <v>6.874957492186695e-09</v>
       </c>
       <c r="GE9" t="n">
-        <v>0.002481547649949789</v>
+        <v>2.806521237630477e-09</v>
       </c>
       <c r="GF9" t="n">
-        <v>2.286076778545976e-05</v>
+        <v>5.677254222291594e-10</v>
       </c>
       <c r="GG9" t="n">
-        <v>0.0004311094235163182</v>
+        <v>9.218672492039559e-10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.128519207239151</v>
+        <v>0.01229790970683098</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7436598539352417</v>
+        <v>0.001559206051751971</v>
       </c>
       <c r="C10" t="n">
-        <v>0.07350741326808929</v>
+        <v>0.03231516107916832</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09058762341737747</v>
+        <v>0.1323436945676804</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0134404394775629</v>
+        <v>0.1048911362886429</v>
       </c>
       <c r="F10" t="n">
-        <v>0.07720474898815155</v>
+        <v>0.06305941194295883</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02484503760933876</v>
+        <v>0.1228617131710052</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03159103915095329</v>
+        <v>0.07147806882858276</v>
       </c>
       <c r="I10" t="n">
-        <v>0.04009589925408363</v>
+        <v>0.08173862844705582</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1467465907335281</v>
+        <v>0.0300821028649807</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5232400298118591</v>
+        <v>0.1004580184817314</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02025913819670677</v>
+        <v>0.01209383457899094</v>
       </c>
       <c r="M10" t="n">
-        <v>0.112152136862278</v>
+        <v>0.2345497906208038</v>
       </c>
       <c r="N10" t="n">
-        <v>0.02101554721593857</v>
+        <v>0.1800397038459778</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0722113773226738</v>
+        <v>0.07630859315395355</v>
       </c>
       <c r="P10" t="n">
-        <v>0.06768958270549774</v>
+        <v>0.1610995382070541</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.02764587290585041</v>
+        <v>0.07244959473609924</v>
       </c>
       <c r="R10" t="n">
-        <v>0.04216187447309494</v>
+        <v>0.0943523570895195</v>
       </c>
       <c r="S10" t="n">
-        <v>0.04957713931798935</v>
+        <v>0.01551673468202353</v>
       </c>
       <c r="T10" t="n">
-        <v>0.06526788324117661</v>
+        <v>0.02445936761796474</v>
       </c>
       <c r="U10" t="n">
-        <v>0.02809531986713409</v>
+        <v>0.01028916891664267</v>
       </c>
       <c r="V10" t="n">
-        <v>0.08927049487829208</v>
+        <v>0.05939500033855438</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1204081624746323</v>
+        <v>0.04575568810105324</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04419530928134918</v>
+        <v>0.02790205180644989</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.002444682642817497</v>
+        <v>0.001286688027903438</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.1102385967969894</v>
+        <v>0.02521838434040546</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.02090801112353802</v>
+        <v>0.004701430909335613</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.012127585709095</v>
+        <v>0.02376058325171471</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.03515562042593956</v>
+        <v>0.02491024509072304</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.1836777329444885</v>
+        <v>0.01703022792935371</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.03095181286334991</v>
+        <v>0.02115847170352936</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1665323376655579</v>
+        <v>0.002577463164925575</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.06548888981342316</v>
+        <v>0.033411905169487</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.03089161217212677</v>
+        <v>0.02833464369177818</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.100322961807251</v>
+        <v>0.04121800139546394</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.03045311011373997</v>
+        <v>0.01518856454640627</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.1106810867786407</v>
+        <v>0.02251358516514301</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.01526895444840193</v>
+        <v>0.1047423034906387</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.05790353938937187</v>
+        <v>0.006723605096340179</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.07404899597167969</v>
+        <v>0.001755468547344208</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.1306459158658981</v>
+        <v>0.02661491185426712</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.07046578824520111</v>
+        <v>0.003830629400908947</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.02913060411810875</v>
+        <v>0.03968031704425812</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.03366295620799065</v>
+        <v>0.006477738730609417</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.01649064943194389</v>
+        <v>0.009116986766457558</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.007192522753030062</v>
+        <v>0.1265313625335693</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5244219303131104</v>
+        <v>0.06782648712396622</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0006872238591313362</v>
+        <v>0.03636977076530457</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.08878185600042343</v>
+        <v>0.02953808568418026</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.04078778252005577</v>
+        <v>0.1196317374706268</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.008749054744839668</v>
+        <v>0.01186555344611406</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.02687286585569382</v>
+        <v>0.04206778481602669</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.04739905148744583</v>
+        <v>0.01317133661359549</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.002753825858235359</v>
+        <v>0.000973554328083992</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.004700452089309692</v>
+        <v>0.03655297309160233</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.1957537233829498</v>
+        <v>0.05828995257616043</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.07499342411756516</v>
+        <v>0.01483091618865728</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.001859661191701889</v>
+        <v>0.06303326040506363</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.09545116126537323</v>
+        <v>0.0134012820199132</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.1026203185319901</v>
+        <v>0.07201018929481506</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.02206813916563988</v>
+        <v>0.002885559573769569</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.1113785356283188</v>
+        <v>0.004062283784151077</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.06975880265235901</v>
+        <v>0.01785857230424881</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.1449586004018784</v>
+        <v>0.01211663149297237</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.2681636214256287</v>
+        <v>0.03921399265527725</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.06418728083372116</v>
+        <v>0.0357242114841938</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.06233803927898407</v>
+        <v>0.04050122201442719</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.1137478351593018</v>
+        <v>0.02864658273756504</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01417406369000673</v>
+        <v>0.001912218518555164</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.02244561538100243</v>
+        <v>0.01470462325960398</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.09734533727169037</v>
+        <v>0.007813284173607826</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.0384213775396347</v>
+        <v>0.02166665717959404</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0366157554090023</v>
+        <v>0.02829252928495407</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.2439623475074768</v>
+        <v>0.04040780663490295</v>
       </c>
       <c r="BW10" t="n">
-        <v>0.002172742038965225</v>
+        <v>0.01849077083170414</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.03757122159004211</v>
+        <v>0.07856269180774689</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.01314448192715645</v>
+        <v>0.09427888691425323</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.1305800229310989</v>
+        <v>0.01993126980960369</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.06597436219453812</v>
+        <v>0.02813012897968292</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.001741542480885983</v>
+        <v>0.003893877845257521</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.03596251457929611</v>
+        <v>0.010905671864748</v>
       </c>
       <c r="CD10" t="n">
-        <v>0.04513483121991158</v>
+        <v>0.01362651772797108</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.126148134469986</v>
+        <v>0.0113742258399725</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.0003128191456198692</v>
+        <v>0.02370088174939156</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.02824376150965691</v>
+        <v>0.0379205197095871</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.05131499469280243</v>
+        <v>0.01339695043861866</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02765184827148914</v>
+        <v>0.01214662380516529</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.01407834887504578</v>
+        <v>0.01065504085272551</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.02674019150435925</v>
+        <v>0.01336347870528698</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.01299777254462242</v>
+        <v>0.006773747038096189</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.1425711214542389</v>
+        <v>0.04688062518835068</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.1212026104331017</v>
+        <v>0.003064058953896165</v>
       </c>
       <c r="CO10" t="n">
-        <v>0.05142840370535851</v>
+        <v>0.008110448718070984</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.1843511760234833</v>
+        <v>0.06701056659221649</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.1049006804823875</v>
+        <v>0.02278815396130085</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.1284926384687424</v>
+        <v>0.01953267492353916</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.03328698500990868</v>
+        <v>0.08507125079631805</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.04175771400332451</v>
+        <v>0.01063932478427887</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.01984824240207672</v>
+        <v>0.03368237614631653</v>
       </c>
       <c r="CV10" t="n">
-        <v>0.04901102930307388</v>
+        <v>0.01127610076218843</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.09569426625967026</v>
+        <v>0.01742815412580967</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.002127123065292835</v>
+        <v>0.009095947258174419</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.01233792677521706</v>
+        <v>0.05003198236227036</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.06661196053028107</v>
+        <v>0.03031124547123909</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0183744989335537</v>
+        <v>0.008361164480447769</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.02261405438184738</v>
+        <v>0.004222760908305645</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.02450508438050747</v>
+        <v>0.01802412047982216</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.02110416628420353</v>
+        <v>0.01815791614353657</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.03128169104456902</v>
+        <v>0.0617549791932106</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.04864811152219772</v>
+        <v>0.01158808544278145</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.1338179111480713</v>
+        <v>0.08093419671058655</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03175116330385208</v>
+        <v>0.09012430906295776</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.04067909717559814</v>
+        <v>0.06688595563173294</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.131108820438385</v>
+        <v>0.112079069018364</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.02086927928030491</v>
+        <v>0.01298690959811211</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.02033494971692562</v>
+        <v>0.04596230015158653</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.07766157388687134</v>
+        <v>0.04688350111246109</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.09576622396707535</v>
+        <v>0.06341938674449921</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.01974113285541534</v>
+        <v>0.01346644200384617</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.1246226280927658</v>
+        <v>0.02055463939905167</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.05441905930638313</v>
+        <v>0.006338946986943483</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.01992902904748917</v>
+        <v>0.02278653532266617</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.1602857559919357</v>
+        <v>0.005490889772772789</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.01864751428365707</v>
+        <v>0.0218182448297739</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.109252855181694</v>
+        <v>0.04107070714235306</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.05709601193666458</v>
+        <v>0.05184498801827431</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.02869654446840286</v>
+        <v>0.03535234555602074</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.004505295306444168</v>
+        <v>0.005132763646543026</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.01253582164645195</v>
+        <v>0.05465170368552208</v>
       </c>
       <c r="DZ10" t="n">
-        <v>0.01237018313258886</v>
+        <v>0.07596877962350845</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.09168165177106857</v>
+        <v>0.01264792215079069</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.00351214874535799</v>
+        <v>0.04955056309700012</v>
       </c>
       <c r="EC10" t="n">
-        <v>0.03500964120030403</v>
+        <v>0.005084880162030458</v>
       </c>
       <c r="ED10" t="n">
-        <v>0.03717777132987976</v>
+        <v>0.02542454563081264</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.06036883592605591</v>
+        <v>0.04904958233237267</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.07920262217521667</v>
+        <v>0.05268264561891556</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.1431524157524109</v>
+        <v>0.008360425941646099</v>
       </c>
       <c r="EH10" t="n">
-        <v>0.06387954950332642</v>
+        <v>0.01470640022307634</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.02270703762769699</v>
+        <v>0.04210057109594345</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03239436447620392</v>
+        <v>0.00904250331223011</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.03702347353100777</v>
+        <v>0.03492273017764091</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.01302559487521648</v>
+        <v>0.0145611185580492</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.04537773504853249</v>
+        <v>0.007557503879070282</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.02501947432756424</v>
+        <v>0.01598400063812733</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.06457103043794632</v>
+        <v>0.04950201138854027</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.04268596693873405</v>
+        <v>0.008465863764286041</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.09654486924409866</v>
+        <v>0.03501066565513611</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.003537643700838089</v>
+        <v>0.06590753048658371</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.05719196423888206</v>
+        <v>0.04802127927541733</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.1595612913370132</v>
+        <v>0.009002444334328175</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.07287684082984924</v>
+        <v>0.01521608978509903</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.001486793160438538</v>
+        <v>0.02052831277251244</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.04724329710006714</v>
+        <v>0.05879474803805351</v>
       </c>
       <c r="EX10" t="n">
-        <v>0.03389199078083038</v>
+        <v>0.01674751751124859</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.1087573543190956</v>
+        <v>0.002347956178709865</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.01437998469918966</v>
+        <v>0.007782765198498964</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.01521706953644753</v>
+        <v>0.04835351929068565</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.003569460473954678</v>
+        <v>0.01983249559998512</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.005073775071650743</v>
+        <v>0.0006801942363381386</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0187540240585804</v>
+        <v>0.007740148808807135</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.02736868336796761</v>
+        <v>0.01462006382644176</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.002371941227465868</v>
+        <v>0.01076558046042919</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.03022241033613682</v>
+        <v>0.02468145824968815</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.00630499329417944</v>
+        <v>0.04383856058120728</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.04424809291958809</v>
+        <v>0.01222314219921827</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.06679695844650269</v>
+        <v>0.03247895836830139</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0827002078294754</v>
+        <v>0.03095967881381512</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01336728036403656</v>
+        <v>0.000304473185678944</v>
       </c>
       <c r="FM10" t="n">
-        <v>0.06647214293479919</v>
+        <v>0.05068245902657509</v>
       </c>
       <c r="FN10" t="n">
-        <v>0.00181172788143158</v>
+        <v>0.02815655246376991</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.07757678627967834</v>
+        <v>0.02198338881134987</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.06564445793628693</v>
+        <v>0.00359814940020442</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.09297066181898117</v>
+        <v>0.03017227724194527</v>
       </c>
       <c r="FR10" t="n">
-        <v>0.1083984076976776</v>
+        <v>0.03021618723869324</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.1875694394111633</v>
+        <v>0.006232112646102905</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.001315451227128506</v>
+        <v>0.02939515188336372</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.1100564002990723</v>
+        <v>0.001085869967937469</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0375930443406105</v>
+        <v>0.08487963676452637</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.06118310987949371</v>
+        <v>0.09302874654531479</v>
       </c>
       <c r="FX10" t="n">
-        <v>0.01802549883723259</v>
+        <v>0.04912260174751282</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.1465311944484711</v>
+        <v>0.001095222309231758</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.004149302840232849</v>
+        <v>0.002132277935743332</v>
       </c>
       <c r="GA10" t="n">
-        <v>0.05807756260037422</v>
+        <v>0.05221707373857498</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.03550824522972107</v>
+        <v>0.03508442640304565</v>
       </c>
       <c r="GC10" t="n">
-        <v>1.643551513552666e-05</v>
+        <v>0.02565774135291576</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.09812512993812561</v>
+        <v>0.06231825426220894</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.06976774334907532</v>
+        <v>0.0002295468002557755</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.09672759473323822</v>
+        <v>0.008410077542066574</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.06762215495109558</v>
+        <v>0.04682661965489388</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.0008055761572904885</v>
+        <v>0.0008080394472926855</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01716800779104233</v>
+        <v>0.001547241816297174</v>
       </c>
       <c r="C11" t="n">
-        <v>0.001493387389928102</v>
+        <v>0.0001798798621166497</v>
       </c>
       <c r="D11" t="n">
-        <v>0.003984377253800631</v>
+        <v>0.000928696827031672</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00828577671200037</v>
+        <v>0.0002018912928178906</v>
       </c>
       <c r="F11" t="n">
-        <v>0.002145879669114947</v>
+        <v>0.001561339944601059</v>
       </c>
       <c r="G11" t="n">
-        <v>0.00191454601008445</v>
+        <v>0.0004193004861008376</v>
       </c>
       <c r="H11" t="n">
-        <v>0.003631274681538343</v>
+        <v>0.000915810524020344</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001369797391816974</v>
+        <v>0.0002393856120761484</v>
       </c>
       <c r="J11" t="n">
-        <v>0.001209333189763129</v>
+        <v>0.0007858423050493002</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01375074964016676</v>
+        <v>0.00174150220118463</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001197445089928806</v>
+        <v>0.0004913058364763856</v>
       </c>
       <c r="M11" t="n">
-        <v>0.001600989489816129</v>
+        <v>0.0003431882942095399</v>
       </c>
       <c r="N11" t="n">
-        <v>0.005791493225842714</v>
+        <v>0.001310651889070868</v>
       </c>
       <c r="O11" t="n">
-        <v>0.003252292983233929</v>
+        <v>0.001805979292839766</v>
       </c>
       <c r="P11" t="n">
-        <v>0.001202188548631966</v>
+        <v>2.759050403255969e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0006076274439692497</v>
+        <v>0.0003044955665245652</v>
       </c>
       <c r="R11" t="n">
-        <v>0.001566605875268579</v>
+        <v>0.0003200576175004244</v>
       </c>
       <c r="S11" t="n">
-        <v>0.000341149396263063</v>
+        <v>0.0001452227152185515</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00138661137316376</v>
+        <v>0.0001952874154085293</v>
       </c>
       <c r="U11" t="n">
-        <v>4.86174103571102e-05</v>
+        <v>0.000402695091906935</v>
       </c>
       <c r="V11" t="n">
-        <v>0.001954308710992336</v>
+        <v>0.0003220632788725197</v>
       </c>
       <c r="W11" t="n">
-        <v>0.005623260512948036</v>
+        <v>0.0002408432337688282</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0007350709056481719</v>
+        <v>0.0001799010206013918</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0007347350474447012</v>
+        <v>0.0001388634846080095</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.00253899279050529</v>
+        <v>0.0003819380654022098</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.0008412100723944604</v>
+        <v>0.0001913713058456779</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0006767009035684168</v>
+        <v>0.0001503343664808199</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.00172400800511241</v>
+        <v>0.0002536605461500585</v>
       </c>
       <c r="AD11" t="n">
-        <v>0.0007628016755916178</v>
+        <v>2.988529740832746e-05</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0001443621295038611</v>
+        <v>0.0003988903481513262</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.001754602184519172</v>
+        <v>0.0004390708345454186</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.0002152136294171214</v>
+        <v>0.0006446237675845623</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0005325838574208319</v>
+        <v>0.0004973929026164114</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0004323095199652016</v>
+        <v>0.0009252964518964291</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.0004859465407207608</v>
+        <v>0.0003854880342260003</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.002690282883122563</v>
+        <v>3.152378485538065e-05</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.001554711372591555</v>
+        <v>0.0004183912242297083</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.000883593806065619</v>
+        <v>0.0004869812401011586</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.001003735233098269</v>
+        <v>0.0002265594957862049</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.002049065195024014</v>
+        <v>1.90117734746309e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.002725096652284265</v>
+        <v>0.0001257924595847726</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0004722286539617926</v>
+        <v>0.0001314552791882306</v>
       </c>
       <c r="AR11" t="n">
-        <v>8.727610111236572e-05</v>
+        <v>0.0001347396901110187</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0007352167740464211</v>
+        <v>3.276679490227252e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0002233321720268577</v>
+        <v>0.0004169787280261517</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.01203273981809616</v>
+        <v>0.001608973369002342</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.0002117875992553309</v>
+        <v>0.000437729642726481</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001666240044869483</v>
+        <v>4.811789403902367e-05</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.002482331823557615</v>
+        <v>0.0008440757519565523</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.003319693729281425</v>
+        <v>0.000976034440100193</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.003261823207139969</v>
+        <v>1.179091123049147e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0008601656882092357</v>
+        <v>0.0002991254150401801</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.002104869810864329</v>
+        <v>0.0002264821960125118</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.00232401886023581</v>
+        <v>0.0001844721846282482</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.005928180180490017</v>
+        <v>2.818423672579229e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.003060015384107828</v>
+        <v>0.0003692176833283156</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0005803385283797979</v>
+        <v>0.0007938414346426725</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.004529365338385105</v>
+        <v>0.0002820548543240875</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.003062896430492401</v>
+        <v>0.0001652551873121411</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.001124164089560509</v>
+        <v>2.494780346751213e-07</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.001174730132333934</v>
+        <v>0.0009092878899537027</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0004468718252610415</v>
+        <v>0.0004341358435340226</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.002407933352515101</v>
+        <v>5.480521940626204e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.004535647109150887</v>
+        <v>0.00055891671217978</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.002472116611897945</v>
+        <v>6.379725527949631e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.001843310310505331</v>
+        <v>3.269412991357967e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.002876427490264177</v>
+        <v>0.0004297298437450081</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.00186789536383003</v>
+        <v>0.0005825428524985909</v>
       </c>
       <c r="BR11" t="n">
-        <v>0.0002980716526508331</v>
+        <v>0.0004785417695529759</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.001080684247426689</v>
+        <v>5.384372343542054e-07</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0009573035058565438</v>
+        <v>0.0005032046465203166</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.0004984057741239667</v>
+        <v>7.822246698196977e-05</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.006831409875303507</v>
+        <v>0.001072378130629659</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.002497799461707473</v>
+        <v>0.0003451631346251816</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.001276061404496431</v>
+        <v>0.0005010155728086829</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0005889474414288998</v>
+        <v>0.0003034237306565046</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0003642882511485368</v>
+        <v>0.0005338781629689038</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0001489203423261642</v>
+        <v>0.0002019494422711432</v>
       </c>
       <c r="CB11" t="n">
-        <v>9.1274079750292e-05</v>
+        <v>0.0001838057360146195</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0008243998745456338</v>
+        <v>0.0002321287611266598</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0003488020156510174</v>
+        <v>0.0004334003024268895</v>
       </c>
       <c r="CE11" t="n">
-        <v>0.002779782982543111</v>
+        <v>0.0005178945139050484</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0009852972580119967</v>
+        <v>7.061377982608974e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0001580935931997374</v>
+        <v>0.0001671795907896012</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0009180451743304729</v>
+        <v>0.0001249590859515592</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.0004036710015498102</v>
+        <v>0.0003990313271060586</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.001361432834528387</v>
+        <v>0.0001336610876023769</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.001489372923970222</v>
+        <v>4.827115481020883e-05</v>
       </c>
       <c r="CL11" t="n">
-        <v>0.0004674478259403259</v>
+        <v>0.0001034482993418351</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.004049636889249086</v>
+        <v>0.0001532325113657862</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.003719278844073415</v>
+        <v>0.0007990255835466087</v>
       </c>
       <c r="CO11" t="n">
-        <v>0.0002788477286230773</v>
+        <v>0.0006976599688641727</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.002944792155176401</v>
+        <v>0.0004906605463474989</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.002457613358274102</v>
+        <v>0.0002400038938503712</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.001515073585323989</v>
+        <v>7.580190140288323e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.002326938323676586</v>
+        <v>0.0004090509610250592</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.0007947327103465796</v>
+        <v>0.0004236766544636339</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.001165155321359634</v>
+        <v>8.556874672649428e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.000277738377917558</v>
+        <v>0.0003453886311035603</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.002301876666024327</v>
+        <v>0.0004035147139802575</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.001286862534470856</v>
+        <v>7.99235567683354e-06</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.0008989571360871196</v>
+        <v>9.594847506377846e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0002996455586981028</v>
+        <v>1.722742308629677e-05</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.0001389674725942314</v>
+        <v>0.000424202939029783</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.001109533361159265</v>
+        <v>5.010948370909318e-05</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.001733245444484055</v>
+        <v>6.398341793101281e-05</v>
       </c>
       <c r="DD11" t="n">
-        <v>0.0005542449071072042</v>
+        <v>6.516442226711661e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.001891788677312434</v>
+        <v>6.480330193880945e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.001278548967093229</v>
+        <v>0.0004482406948227435</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.001221150858327746</v>
+        <v>0.0002674430725164711</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.007068435195833445</v>
+        <v>0.0001252252550330013</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.004336883779615164</v>
+        <v>0.0004033946897834539</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0009602254722267389</v>
+        <v>9.352699271403253e-05</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.001641663839109242</v>
+        <v>3.596444730646908e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0006367083406075835</v>
+        <v>0.0006668271962553263</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.003136689774692059</v>
+        <v>0.0006304251728579402</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.000344009546097368</v>
+        <v>0.0001425260561518371</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0008716307347640395</v>
+        <v>0.0002508307225070894</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.002907427493482828</v>
+        <v>0.0002301781205460429</v>
       </c>
       <c r="DQ11" t="n">
-        <v>0.001567053375765681</v>
+        <v>0.0002891575859393924</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.002803562209010124</v>
+        <v>0.0001819613971747458</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.0001185289584100246</v>
+        <v>0.0002349592396058142</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0008754405425861478</v>
+        <v>0.000153794841025956</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001755536795826629</v>
+        <v>0.0004089605063199997</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0009488038485869765</v>
+        <v>0.0001590320898685604</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0007104208343662322</v>
+        <v>0.0001414955477230251</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0006015453254804015</v>
+        <v>1.280339074583026e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0005373189924284816</v>
+        <v>0.0001642668794374913</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.0009597346652299166</v>
+        <v>9.615861199563369e-05</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0003592254361137748</v>
+        <v>0.0002238022279925644</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.001120704226195812</v>
+        <v>0.000473767111543566</v>
       </c>
       <c r="EC11" t="n">
-        <v>0.0001657463726587594</v>
+        <v>1.159483508672565e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0007233379292301834</v>
+        <v>0.0001831689005484805</v>
       </c>
       <c r="EE11" t="n">
-        <v>0.001725466107018292</v>
+        <v>0.0007241314742714167</v>
       </c>
       <c r="EF11" t="n">
-        <v>0.0002811847953125834</v>
+        <v>0.0003160967025905848</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.002344341017305851</v>
+        <v>8.316070307046175e-06</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0002660038589965552</v>
+        <v>0.0002832717727869749</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0007477831095457077</v>
+        <v>0.0001450998242944479</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.0003702639369294047</v>
+        <v>0.0002487320161890239</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.00125473493244499</v>
+        <v>0.0002537651744205505</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.001004817197099328</v>
+        <v>1.086016345652752e-05</v>
       </c>
       <c r="EM11" t="n">
-        <v>0.001187207992188632</v>
+        <v>1.02623698694515e-05</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0005752512952312827</v>
+        <v>2.611051604617387e-05</v>
       </c>
       <c r="EO11" t="n">
-        <v>0.001180680468678474</v>
+        <v>0.0004047928377985954</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0005004872800782323</v>
+        <v>0.0003933709231205285</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.00138898950535804</v>
+        <v>0.0001201918494189158</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0008652309188619256</v>
+        <v>0.000347748544299975</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.001653459388762712</v>
+        <v>0.0005442130495794117</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.001746318419463933</v>
+        <v>0.0002310472482349724</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.001594362314790487</v>
+        <v>2.699167816899717e-05</v>
       </c>
       <c r="EV11" t="n">
-        <v>0.003064720425754786</v>
+        <v>0.0002855242346413434</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0005255253054201603</v>
+        <v>0.0001991411845665425</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.0004928366397507489</v>
+        <v>0.0004717098199762404</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.001895998953841627</v>
+        <v>0.0005426739226095378</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0006772326887585223</v>
+        <v>1.219285695697181e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>6.625945388805121e-05</v>
+        <v>8.436082862317562e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0006650679861195385</v>
+        <v>0.0001480087667005137</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.0005394774489104748</v>
+        <v>0.0003363765717949718</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.001777366502210498</v>
+        <v>0.0001271429646294564</v>
       </c>
       <c r="FE11" t="n">
-        <v>0.001574374735355377</v>
+        <v>4.338793223723769e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0009551168186590075</v>
+        <v>0.0001085889743990265</v>
       </c>
       <c r="FG11" t="n">
-        <v>0.0005275657749734819</v>
+        <v>0.0001904475939227268</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.000592840020544827</v>
+        <v>0.000483603827888146</v>
       </c>
       <c r="FI11" t="n">
-        <v>0.0005535951931960881</v>
+        <v>0.0001646117161726579</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.003551896195858717</v>
+        <v>0.0005383342504501343</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.001405949587933719</v>
+        <v>0.0004793413681909442</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0003375484375283122</v>
+        <v>0.0005756409373134375</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.002147302031517029</v>
+        <v>0.0003021057927981019</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.000629102869424969</v>
+        <v>0.0009733005426824093</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.00131640734616667</v>
+        <v>0.000462398340459913</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.002954060211777687</v>
+        <v>0.0001053409941960126</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.003509032540023327</v>
+        <v>0.0006080910679884255</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0008201007731258869</v>
+        <v>0.0004483679367695004</v>
       </c>
       <c r="FS11" t="n">
-        <v>1.565378624945879e-06</v>
+        <v>0.0003509506641421467</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.005209749564528465</v>
+        <v>0.0003868922358378768</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.002277927938848734</v>
+        <v>5.088153557153419e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.001465316629037261</v>
+        <v>0.000341027945978567</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.001793657429516315</v>
+        <v>0.001028133789077401</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.001544762519188225</v>
+        <v>0.0002165045880246907</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.002939837984740734</v>
+        <v>0.0005004817503504455</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0003463063330855221</v>
+        <v>0.0001770203089108691</v>
       </c>
       <c r="GA11" t="n">
-        <v>0.0006431038491427898</v>
+        <v>0.000454853055998683</v>
       </c>
       <c r="GB11" t="n">
-        <v>0.0001252138754352927</v>
+        <v>8.725928637431934e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0002335893223062158</v>
+        <v>0.0005355635657906532</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.001713458681479096</v>
+        <v>0.0005044096615165472</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.002452984219416976</v>
+        <v>3.10244613501709e-05</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.000870796968229115</v>
+        <v>6.965137436054647e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>4.028391049359925e-05</v>
+        <v>0.0005172971286810935</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.008694972842931747</v>
+        <v>0.0003467857604846358</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0838066041469574</v>
+        <v>0.003475488862022758</v>
       </c>
       <c r="C12" t="n">
-        <v>0.003997073043137789</v>
+        <v>0.000102260266430676</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06458073109388351</v>
+        <v>0.005717799533158541</v>
       </c>
       <c r="E12" t="n">
-        <v>0.00560871884226799</v>
+        <v>0.001934830099344254</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01055078767240047</v>
+        <v>0.002004860434681177</v>
       </c>
       <c r="G12" t="n">
-        <v>0.005410520359873772</v>
+        <v>0.003075422486290336</v>
       </c>
       <c r="H12" t="n">
-        <v>0.008626649156212807</v>
+        <v>0.003064540447667241</v>
       </c>
       <c r="I12" t="n">
-        <v>0.002632203511893749</v>
+        <v>0.001686369068920612</v>
       </c>
       <c r="J12" t="n">
-        <v>0.01537742465734482</v>
+        <v>3.07103618979454e-05</v>
       </c>
       <c r="K12" t="n">
-        <v>0.05666615441441536</v>
+        <v>0.002298933919519186</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000764997792430222</v>
+        <v>0.0002938180696219206</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06203506886959076</v>
+        <v>0.007906492799520493</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01832455024123192</v>
+        <v>0.003999398089945316</v>
       </c>
       <c r="O12" t="n">
-        <v>0.02907241322100163</v>
+        <v>0.002134267706423998</v>
       </c>
       <c r="P12" t="n">
-        <v>0.0008526556193828583</v>
+        <v>0.003367987927049398</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.009106555953621864</v>
+        <v>0.002070183167234063</v>
       </c>
       <c r="R12" t="n">
-        <v>0.005634747911244631</v>
+        <v>0.001272882567718625</v>
       </c>
       <c r="S12" t="n">
-        <v>0.001932887593284249</v>
+        <v>0.000492266786750406</v>
       </c>
       <c r="T12" t="n">
-        <v>0.01085253618657589</v>
+        <v>7.350064697675407e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0007447048556059599</v>
+        <v>0.0003600905474741012</v>
       </c>
       <c r="V12" t="n">
-        <v>0.01055257208645344</v>
+        <v>0.0005902810953557491</v>
       </c>
       <c r="W12" t="n">
-        <v>0.003926816862076521</v>
+        <v>0.001530316658318043</v>
       </c>
       <c r="X12" t="n">
-        <v>0.004840349312871695</v>
+        <v>0.000786113494541496</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01164989545941353</v>
+        <v>0.000376973272068426</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.0001039008420775644</v>
+        <v>0.0008764503290876746</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.005646123550832272</v>
+        <v>0.0001874938898254186</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.006809172220528126</v>
+        <v>0.0002402518002782017</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.01643597520887852</v>
+        <v>6.388072506524622e-05</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.0001033806329360232</v>
+        <v>0.0005078395479358733</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.00668370770290494</v>
+        <v>0.0007385351345874369</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00495803402736783</v>
+        <v>0.0007725614123046398</v>
       </c>
       <c r="AG12" t="n">
-        <v>0.002448930172249675</v>
+        <v>0.001596673624590039</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.006876734085381031</v>
+        <v>0.0007141870446503162</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.0001759356819093227</v>
+        <v>0.001329351216554642</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.00177113909740001</v>
+        <v>0.0004083456005901098</v>
       </c>
       <c r="AK12" t="n">
-        <v>0.003998089581727982</v>
+        <v>0.0004421410558279604</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.008293386548757553</v>
+        <v>0.001276570837944746</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.002018181141465902</v>
+        <v>0.0007946796831674874</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.003181652165949345</v>
+        <v>0.001405425369739532</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.009803034365177155</v>
+        <v>0.0004513915919233114</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.008417370729148388</v>
+        <v>0.0007496414473280311</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.00553430337458849</v>
+        <v>0.001261078752577305</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.003794882912188768</v>
+        <v>2.108699845848605e-05</v>
       </c>
       <c r="AS12" t="n">
-        <v>0.002551334910094738</v>
+        <v>8.664089546073228e-05</v>
       </c>
       <c r="AT12" t="n">
-        <v>0.006903728935867548</v>
+        <v>0.001728328177705407</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.06198294460773468</v>
+        <v>0.001726019312627614</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.004281077533960342</v>
+        <v>0.001133768586441875</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.00721662724390626</v>
+        <v>0.001052243635058403</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.01087742485105991</v>
+        <v>0.004244370386004448</v>
       </c>
       <c r="AY12" t="n">
-        <v>0.006767376326024532</v>
+        <v>0.00184304965659976</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.002938007470220327</v>
+        <v>0.000580897438339889</v>
       </c>
       <c r="BA12" t="n">
-        <v>0.0005378918722271919</v>
+        <v>0.0001189526083180681</v>
       </c>
       <c r="BB12" t="n">
-        <v>0.000290034688077867</v>
+        <v>0.0006990978727117181</v>
       </c>
       <c r="BC12" t="n">
-        <v>0.001015703426674008</v>
+        <v>0.0002140039287041873</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.01461029797792435</v>
+        <v>0.001102779875509441</v>
       </c>
       <c r="BE12" t="n">
-        <v>0.01609090343117714</v>
+        <v>9.50272660702467e-05</v>
       </c>
       <c r="BF12" t="n">
-        <v>0.01564373821020126</v>
+        <v>0.001254089409485459</v>
       </c>
       <c r="BG12" t="n">
-        <v>0.01798193342983723</v>
+        <v>0.00171449373010546</v>
       </c>
       <c r="BH12" t="n">
-        <v>0.01333686988800764</v>
+        <v>8.268248348031193e-05</v>
       </c>
       <c r="BI12" t="n">
-        <v>0.009433158673346043</v>
+        <v>0.0005002058460377157</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.006047051399946213</v>
+        <v>0.001927673583850265</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.005688346456736326</v>
+        <v>0.0001383769849780947</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.01653043925762177</v>
+        <v>0.0003880820877384394</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.01010206621140242</v>
+        <v>0.001077462919056416</v>
       </c>
       <c r="BN12" t="n">
-        <v>0.005591054446995258</v>
+        <v>0.0005118519184179604</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.002332997275516391</v>
+        <v>0.002035681391134858</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.01629346609115601</v>
+        <v>0.00109813129529357</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.00416936632245779</v>
+        <v>0.0002705416991375387</v>
       </c>
       <c r="BR12" t="n">
-        <v>0.007456990890204906</v>
+        <v>0.000220923699089326</v>
       </c>
       <c r="BS12" t="n">
-        <v>0.008657733909785748</v>
+        <v>0.0006879627471789718</v>
       </c>
       <c r="BT12" t="n">
-        <v>0.0008833614992909133</v>
+        <v>0.000162382290000096</v>
       </c>
       <c r="BU12" t="n">
-        <v>0.003921291790902615</v>
+        <v>0.0007535096956416965</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.03017484955489635</v>
+        <v>0.001600109157152474</v>
       </c>
       <c r="BW12" t="n">
-        <v>0.003440540283918381</v>
+        <v>0.0006518663140013814</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.01136020570993423</v>
+        <v>0.002309826668351889</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.004199720453470945</v>
+        <v>0.00134962925221771</v>
       </c>
       <c r="BZ12" t="n">
-        <v>0.01162595488131046</v>
+        <v>0.001478808000683784</v>
       </c>
       <c r="CA12" t="n">
-        <v>0.003440272994339466</v>
+        <v>0.0007872717105783522</v>
       </c>
       <c r="CB12" t="n">
-        <v>0.004545301664620638</v>
+        <v>0.0003537125885486603</v>
       </c>
       <c r="CC12" t="n">
-        <v>0.00508602149784565</v>
+        <v>3.245379775762558e-05</v>
       </c>
       <c r="CD12" t="n">
-        <v>0.005174780264496803</v>
+        <v>0.0002043816930381581</v>
       </c>
       <c r="CE12" t="n">
-        <v>0.01431899424642324</v>
+        <v>0.0006425903411582112</v>
       </c>
       <c r="CF12" t="n">
-        <v>0.004552162252366543</v>
+        <v>0.0002033064374700189</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.004757789429277182</v>
+        <v>0.00204525189474225</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.004322489723563194</v>
+        <v>0.0004486368270590901</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.00243614218197763</v>
+        <v>0.0004500974609982222</v>
       </c>
       <c r="CJ12" t="n">
-        <v>0.004943688400089741</v>
+        <v>0.000220442729187198</v>
       </c>
       <c r="CK12" t="n">
-        <v>0.001779141137376428</v>
+        <v>0.0003972313133999705</v>
       </c>
       <c r="CL12" t="n">
-        <v>0.002453800523653626</v>
+        <v>0.0002211443788837641</v>
       </c>
       <c r="CM12" t="n">
-        <v>0.009854654781520367</v>
+        <v>0.0008618152351118624</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.006086206994950771</v>
+        <v>0.0006463018362410367</v>
       </c>
       <c r="CO12" t="n">
-        <v>0.003559929085895419</v>
+        <v>0.00148143304977566</v>
       </c>
       <c r="CP12" t="n">
-        <v>0.02457695826888084</v>
+        <v>0.002396943047642708</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.01212824508547783</v>
+        <v>0.0002584357862360775</v>
       </c>
       <c r="CR12" t="n">
-        <v>0.009351661428809166</v>
+        <v>0.0006267118733376265</v>
       </c>
       <c r="CS12" t="n">
-        <v>0.0101895472034812</v>
+        <v>0.001556700561195612</v>
       </c>
       <c r="CT12" t="n">
-        <v>0.0145100262016058</v>
+        <v>0.0005786295514553785</v>
       </c>
       <c r="CU12" t="n">
-        <v>0.001680176006630063</v>
+        <v>0.001018631621263921</v>
       </c>
       <c r="CV12" t="n">
-        <v>0.005274460185319185</v>
+        <v>0.0002190650848206133</v>
       </c>
       <c r="CW12" t="n">
-        <v>0.01067858468741179</v>
+        <v>0.0005053196800872684</v>
       </c>
       <c r="CX12" t="n">
-        <v>0.004597783088684082</v>
+        <v>0.0001775332930264995</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.007871903479099274</v>
+        <v>0.002194494474679232</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.003682759357616305</v>
+        <v>0.0009669492719694972</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.00287388451397419</v>
+        <v>0.0004566900315694511</v>
       </c>
       <c r="DB12" t="n">
-        <v>0.00631887000054121</v>
+        <v>6.281906098593026e-05</v>
       </c>
       <c r="DC12" t="n">
-        <v>0.001984408125281334</v>
+        <v>0.0004824401694349945</v>
       </c>
       <c r="DD12" t="n">
-        <v>0.00120617588981986</v>
+        <v>0.0003135836741421372</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.00578609760850668</v>
+        <v>0.001261366880498827</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.008897558785974979</v>
+        <v>0.000768063822761178</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.00642709294334054</v>
+        <v>0.0002455880166962743</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.03064708225429058</v>
+        <v>0.001926550292409956</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.004922614432871342</v>
+        <v>0.0001401645422447473</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.0008762539364397526</v>
+        <v>0.002707583364099264</v>
       </c>
       <c r="DK12" t="n">
-        <v>0.003012086497619748</v>
+        <v>8.6715750512667e-05</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.005004375707358122</v>
+        <v>0.002364568645134568</v>
       </c>
       <c r="DM12" t="n">
-        <v>0.006084812339395285</v>
+        <v>0.001405521063134074</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.009134779684245586</v>
+        <v>0.001016082358546555</v>
       </c>
       <c r="DO12" t="n">
-        <v>0.004711024463176727</v>
+        <v>0.00125707290135324</v>
       </c>
       <c r="DP12" t="n">
-        <v>0.01183854229748249</v>
+        <v>0.0001189125468954444</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.01100680138915777</v>
+        <v>0.0007337190909311175</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01173515804111958</v>
+        <v>0.0006326374132186174</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.01439435034990311</v>
+        <v>0.0007426368538290262</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.004148129373788834</v>
+        <v>0.0002202931354986504</v>
       </c>
       <c r="DU12" t="n">
-        <v>0.002162707038223743</v>
+        <v>0.001742174848914146</v>
       </c>
       <c r="DV12" t="n">
-        <v>0.007125426083803177</v>
+        <v>0.00194488896522671</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.002281869994476438</v>
+        <v>0.0003313201596029103</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.000181704293936491</v>
+        <v>0.0008956228266470134</v>
       </c>
       <c r="DY12" t="n">
-        <v>0.00829982478171587</v>
+        <v>0.0008871626341715455</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.005090046674013138</v>
+        <v>0.0009768251329660416</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.003223880659788847</v>
+        <v>0.0002227985532954335</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.007748580072075129</v>
+        <v>0.001079545123502612</v>
       </c>
       <c r="EC12" t="n">
-        <v>0.003459865693002939</v>
+        <v>0.0003415449464228004</v>
       </c>
       <c r="ED12" t="n">
-        <v>0.006410050205886364</v>
+        <v>0.002141916425898671</v>
       </c>
       <c r="EE12" t="n">
-        <v>0.00277257664129138</v>
+        <v>0.0008718690369278193</v>
       </c>
       <c r="EF12" t="n">
-        <v>0.003034968394786119</v>
+        <v>0.0005294564180076122</v>
       </c>
       <c r="EG12" t="n">
-        <v>0.006374608725309372</v>
+        <v>0.0002551792422309518</v>
       </c>
       <c r="EH12" t="n">
-        <v>0.002496637403964996</v>
+        <v>0.0004387885564938188</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.005095533560961485</v>
+        <v>0.002040893072262406</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.008158325217664242</v>
+        <v>0.0005849050940014422</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.002565910574048758</v>
+        <v>0.0003526345826685429</v>
       </c>
       <c r="EL12" t="n">
-        <v>0.009233612567186356</v>
+        <v>0.0002561250003054738</v>
       </c>
       <c r="EM12" t="n">
-        <v>0.001861002645455301</v>
+        <v>7.884568913141266e-05</v>
       </c>
       <c r="EN12" t="n">
-        <v>0.0005708812968805432</v>
+        <v>2.119148848578334e-05</v>
       </c>
       <c r="EO12" t="n">
-        <v>0.005010385997593403</v>
+        <v>0.0001400722248945385</v>
       </c>
       <c r="EP12" t="n">
-        <v>0.008564268238842487</v>
+        <v>0.001022987649776042</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0.002055835444480181</v>
+        <v>0.0001686185860307887</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.003338774666190147</v>
+        <v>0.001799894496798515</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.003342605195939541</v>
+        <v>4.120421726838686e-05</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.01747299544513226</v>
+        <v>0.0001980182423721999</v>
       </c>
       <c r="EU12" t="n">
-        <v>0.01126419752836227</v>
+        <v>0.0005579227581620216</v>
       </c>
       <c r="EV12" t="n">
-        <v>0.01114999689161777</v>
+        <v>0.0009676470654085279</v>
       </c>
       <c r="EW12" t="n">
-        <v>0.002189418766647577</v>
+        <v>0.001500323880463839</v>
       </c>
       <c r="EX12" t="n">
-        <v>0.004253569059073925</v>
+        <v>0.0002242604678031057</v>
       </c>
       <c r="EY12" t="n">
-        <v>0.01074138842523098</v>
+        <v>0.0008301414782181382</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0.001733696786686778</v>
+        <v>3.684566036099568e-05</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.006616560276597738</v>
+        <v>0.002312096301466227</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.0004084964166395366</v>
+        <v>0.0005744803347624838</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.004604948218911886</v>
+        <v>0.0006970707909204066</v>
       </c>
       <c r="FD12" t="n">
-        <v>0.006313598249107599</v>
+        <v>3.115598519798368e-05</v>
       </c>
       <c r="FE12" t="n">
-        <v>0.00181684154085815</v>
+        <v>0.0005422455142252147</v>
       </c>
       <c r="FF12" t="n">
-        <v>0.002362265717238188</v>
+        <v>5.886230064788833e-05</v>
       </c>
       <c r="FG12" t="n">
-        <v>0.00150019209831953</v>
+        <v>0.0005287834210321307</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.005097076296806335</v>
+        <v>6.766716251149774e-05</v>
       </c>
       <c r="FI12" t="n">
-        <v>0.004827479366213083</v>
+        <v>0.0005159014253877103</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.008987922221422195</v>
+        <v>0.0008029104210436344</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.002130967099219561</v>
+        <v>0.0003360310802236199</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.003391647944226861</v>
+        <v>0.0001514462492195889</v>
       </c>
       <c r="FM12" t="n">
-        <v>0.003009049920365214</v>
+        <v>0.0006458220304921269</v>
       </c>
       <c r="FN12" t="n">
-        <v>0.001729031675495207</v>
+        <v>0.0003512547700665891</v>
       </c>
       <c r="FO12" t="n">
-        <v>0.0005834102048538625</v>
+        <v>0.0002283850335516036</v>
       </c>
       <c r="FP12" t="n">
-        <v>0.001465983688831329</v>
+        <v>0.0006877383566461504</v>
       </c>
       <c r="FQ12" t="n">
-        <v>0.003255050629377365</v>
+        <v>0.0004366403154563159</v>
       </c>
       <c r="FR12" t="n">
-        <v>0.0008016679203137755</v>
+        <v>0.00180701189674437</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.01161126419901848</v>
+        <v>0.0002370328293181956</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.002659454010426998</v>
+        <v>0.001113547245040536</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.005500577390193939</v>
+        <v>0.0006062356405891478</v>
       </c>
       <c r="FV12" t="n">
-        <v>0.01214911416172981</v>
+        <v>0.001775038661435246</v>
       </c>
       <c r="FW12" t="n">
-        <v>0.00748034194111824</v>
+        <v>0.002635151613503695</v>
       </c>
       <c r="FX12" t="n">
-        <v>0.0007821787148714066</v>
+        <v>0.0006175318267196417</v>
       </c>
       <c r="FY12" t="n">
-        <v>0.01042639557272196</v>
+        <v>0.0005850354791618884</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.002027058973908424</v>
+        <v>0.0003043210599571466</v>
       </c>
       <c r="GA12" t="n">
-        <v>0.002476450521498919</v>
+        <v>0.001279200194403529</v>
       </c>
       <c r="GB12" t="n">
-        <v>0.005725644063204527</v>
+        <v>0.001135034719482064</v>
       </c>
       <c r="GC12" t="n">
-        <v>0.009775525890290737</v>
+        <v>6.069906521588564e-05</v>
       </c>
       <c r="GD12" t="n">
-        <v>0.0111289881169796</v>
+        <v>0.001893397304229438</v>
       </c>
       <c r="GE12" t="n">
-        <v>0.02021673694252968</v>
+        <v>0.00118515407666564</v>
       </c>
       <c r="GF12" t="n">
-        <v>0.008686828427016735</v>
+        <v>0.0001838258758652955</v>
       </c>
       <c r="GG12" t="n">
-        <v>0.005413228645920753</v>
+        <v>0.0004044781671836972</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.01692746020853519</v>
+        <v>0.01274144556373358</v>
       </c>
       <c r="B13" t="n">
-        <v>0.1398927718400955</v>
+        <v>0.05361321568489075</v>
       </c>
       <c r="C13" t="n">
-        <v>0.01320743747055531</v>
+        <v>0.001847693929448724</v>
       </c>
       <c r="D13" t="n">
-        <v>0.05197828263044357</v>
+        <v>0.03784498572349548</v>
       </c>
       <c r="E13" t="n">
-        <v>0.004131296649575233</v>
+        <v>0.005651626735925674</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08488455414772034</v>
+        <v>0.02835998497903347</v>
       </c>
       <c r="G13" t="n">
-        <v>0.01706771925091743</v>
+        <v>0.0195795614272356</v>
       </c>
       <c r="H13" t="n">
-        <v>0.04848878458142281</v>
+        <v>0.02894115075469017</v>
       </c>
       <c r="I13" t="n">
-        <v>0.003973508253693581</v>
+        <v>0.0002919111866503954</v>
       </c>
       <c r="J13" t="n">
-        <v>0.03205119445919991</v>
+        <v>0.02639145404100418</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1176035851240158</v>
+        <v>0.07111617177724838</v>
       </c>
       <c r="L13" t="n">
-        <v>0.003252692986279726</v>
+        <v>0.002241515554487705</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03685170412063599</v>
+        <v>0.08396684378385544</v>
       </c>
       <c r="N13" t="n">
-        <v>0.01227411720901728</v>
+        <v>0.02436660975217819</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07882920652627945</v>
+        <v>0.05144309252500534</v>
       </c>
       <c r="P13" t="n">
-        <v>0.01741099171340466</v>
+        <v>0.0223896000534296</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.005306711420416832</v>
+        <v>0.007223721593618393</v>
       </c>
       <c r="R13" t="n">
-        <v>0.01431483775377274</v>
+        <v>0.001166342524811625</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0008999544661492109</v>
+        <v>0.001194589771330357</v>
       </c>
       <c r="T13" t="n">
-        <v>0.004913906566798687</v>
+        <v>0.01346516236662865</v>
       </c>
       <c r="U13" t="n">
-        <v>0.01299036014825106</v>
+        <v>0.01949390023946762</v>
       </c>
       <c r="V13" t="n">
-        <v>0.019530164077878</v>
+        <v>0.02612082660198212</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03258831799030304</v>
+        <v>0.03907075151801109</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01111552678048611</v>
+        <v>0.01483362168073654</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01131762098520994</v>
+        <v>0.002678780816495419</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.02170904353260994</v>
+        <v>0.007297550793737173</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.01460531167685986</v>
+        <v>0.01290646661072969</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.00184435211122036</v>
+        <v>0.02952502481639385</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.006702110171318054</v>
+        <v>0.01464318670332432</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.005801121238619089</v>
+        <v>0.003730203490704298</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.001524918479844928</v>
+        <v>0.02653797343373299</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.01109636202454567</v>
+        <v>0.02285333722829819</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.01046456769108772</v>
+        <v>0.01634329184889793</v>
       </c>
       <c r="AH13" t="n">
-        <v>0.006238969974219799</v>
+        <v>0.02225666493177414</v>
       </c>
       <c r="AI13" t="n">
-        <v>0.005569361615926027</v>
+        <v>0.0338275320827961</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.006922669243067503</v>
+        <v>0.01415230426937342</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.02341775223612785</v>
+        <v>0.008806971833109856</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01011365745216608</v>
+        <v>0.001135082915425301</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.002134073991328478</v>
+        <v>0.003120994661003351</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.01133505068719387</v>
+        <v>0.02187146618962288</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.003689962672069669</v>
+        <v>0.01454552263021469</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.01515137404203415</v>
+        <v>0.02008422277867794</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.006860067136585712</v>
+        <v>0.0108303539454937</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.01081053353846073</v>
+        <v>0.022060576826334</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.01503476779907942</v>
+        <v>0.004378003533929586</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.003323693294078112</v>
+        <v>0.0007608032319694757</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.08675835281610489</v>
+        <v>0.1300268173217773</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.005612056702375412</v>
+        <v>0.03075673803687096</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.0197260994464159</v>
+        <v>0.02058907225728035</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.006166414357721806</v>
+        <v>0.03945566713809967</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.04723115637898445</v>
+        <v>0.03046231344342232</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.02717016823589802</v>
+        <v>0.02272837236523628</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.0174848809838295</v>
+        <v>0.02051210217177868</v>
       </c>
       <c r="BB13" t="n">
-        <v>0.02711106091737747</v>
+        <v>0.009258716367185116</v>
       </c>
       <c r="BC13" t="n">
-        <v>0.005717973224818707</v>
+        <v>0.02102089859545231</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04457918927073479</v>
+        <v>0.01634127274155617</v>
       </c>
       <c r="BE13" t="n">
-        <v>0.03156516328454018</v>
+        <v>0.03303714841604233</v>
       </c>
       <c r="BF13" t="n">
-        <v>0.01109658740460873</v>
+        <v>0.01331040356308222</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.003094489686191082</v>
+        <v>0.008989290334284306</v>
       </c>
       <c r="BH13" t="n">
-        <v>0.01299979910254478</v>
+        <v>0.02162719704210758</v>
       </c>
       <c r="BI13" t="n">
-        <v>0.01326513849198818</v>
+        <v>0.01820073276758194</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.01760829798877239</v>
+        <v>0.02933373302221298</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.01326418295502663</v>
+        <v>0.002162150107324123</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.0117441825568676</v>
+        <v>0.003508398775011301</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.03347194194793701</v>
+        <v>0.02487041056156158</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.02453075721859932</v>
+        <v>0.004733139649033546</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.003050999715924263</v>
+        <v>0.01050165481865406</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.02557476609945297</v>
+        <v>0.01499882899224758</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.0061080870218575</v>
+        <v>0.001042807358317077</v>
       </c>
       <c r="BR13" t="n">
-        <v>0.005128496326506138</v>
+        <v>0.02073255740106106</v>
       </c>
       <c r="BS13" t="n">
-        <v>0.004424754530191422</v>
+        <v>0.00542854331433773</v>
       </c>
       <c r="BT13" t="n">
-        <v>0.004249121528118849</v>
+        <v>0.008373535238206387</v>
       </c>
       <c r="BU13" t="n">
-        <v>0.005444563459604979</v>
+        <v>0.01419973373413086</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.05170222744345665</v>
+        <v>0.05956109613180161</v>
       </c>
       <c r="BW13" t="n">
-        <v>0.02180704846978188</v>
+        <v>0.01206858642399311</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.01429760456085205</v>
+        <v>0.05559257790446281</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.003892067121341825</v>
+        <v>0.03931049257516861</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.02139140665531158</v>
+        <v>0.03705956041812897</v>
       </c>
       <c r="CA13" t="n">
-        <v>0.002118462696671486</v>
+        <v>0.000195452943444252</v>
       </c>
       <c r="CB13" t="n">
-        <v>0.005531114526093006</v>
+        <v>0.002563346643000841</v>
       </c>
       <c r="CC13" t="n">
-        <v>0.0151279317215085</v>
+        <v>0.01112218573689461</v>
       </c>
       <c r="CD13" t="n">
-        <v>0.002097834832966328</v>
+        <v>0.01408167649060488</v>
       </c>
       <c r="CE13" t="n">
-        <v>0.02345090359449387</v>
+        <v>0.01795893535017967</v>
       </c>
       <c r="CF13" t="n">
-        <v>0.01752123422920704</v>
+        <v>0.003720455337315798</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.007537618279457092</v>
+        <v>0.004125289153307676</v>
       </c>
       <c r="CH13" t="n">
-        <v>0.002682421123608947</v>
+        <v>0.007521290332078934</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.01318739727139473</v>
+        <v>0.01359376311302185</v>
       </c>
       <c r="CJ13" t="n">
-        <v>0.01031447388231754</v>
+        <v>0.0007454326841980219</v>
       </c>
       <c r="CK13" t="n">
-        <v>0.01063832081854343</v>
+        <v>0.009111125953495502</v>
       </c>
       <c r="CL13" t="n">
-        <v>0.01244643144309521</v>
+        <v>0.004633110947906971</v>
       </c>
       <c r="CM13" t="n">
-        <v>0.02943543344736099</v>
+        <v>0.04838097840547562</v>
       </c>
       <c r="CN13" t="n">
-        <v>0.02495075576007366</v>
+        <v>0.07355205714702606</v>
       </c>
       <c r="CO13" t="n">
-        <v>6.763450801372528e-05</v>
+        <v>0.008863831870257854</v>
       </c>
       <c r="CP13" t="n">
-        <v>0.03387225046753883</v>
+        <v>0.04213092103600502</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.02005872130393982</v>
+        <v>0.02841577678918839</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.01068413723260164</v>
+        <v>0.0481838583946228</v>
       </c>
       <c r="CS13" t="n">
-        <v>0.02075297944247723</v>
+        <v>0.01092311087995768</v>
       </c>
       <c r="CT13" t="n">
-        <v>0.01393930707126856</v>
+        <v>0.001548978267237544</v>
       </c>
       <c r="CU13" t="n">
-        <v>0.01316673588007689</v>
+        <v>0.01746338978409767</v>
       </c>
       <c r="CV13" t="n">
-        <v>0.001090884557925165</v>
+        <v>0.01823604479432106</v>
       </c>
       <c r="CW13" t="n">
-        <v>0.02114607952535152</v>
+        <v>0.01494993083178997</v>
       </c>
       <c r="CX13" t="n">
-        <v>0.01801098696887493</v>
+        <v>0.005863669328391552</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.01376328524202108</v>
+        <v>0.01199002657085657</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.005151648074388504</v>
+        <v>0.007105100899934769</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.01398227736353874</v>
+        <v>0.005799845792353153</v>
       </c>
       <c r="DB13" t="n">
-        <v>0.01082671247422695</v>
+        <v>0.004143429454416037</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.01744493469595909</v>
+        <v>0.005216998048126698</v>
       </c>
       <c r="DD13" t="n">
-        <v>0.008718891069293022</v>
+        <v>0.004013681318610907</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.007609870750457048</v>
+        <v>0.01049417816102505</v>
       </c>
       <c r="DF13" t="n">
-        <v>0.0136425718665123</v>
+        <v>0.006528111174702644</v>
       </c>
       <c r="DG13" t="n">
-        <v>0.002490857616066933</v>
+        <v>0.0281788595020771</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.07262768596410751</v>
+        <v>0.009729329496622086</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.01944229565560818</v>
+        <v>0.02180682122707367</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.02697623148560524</v>
+        <v>0.002697517164051533</v>
       </c>
       <c r="DK13" t="n">
-        <v>0.02549200877547264</v>
+        <v>0.03239056095480919</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.0222218930721283</v>
+        <v>0.0227567907422781</v>
       </c>
       <c r="DM13" t="n">
-        <v>0.02109366096556187</v>
+        <v>0.0236746221780777</v>
       </c>
       <c r="DN13" t="n">
-        <v>0.003985878080129623</v>
+        <v>0.02184218727052212</v>
       </c>
       <c r="DO13" t="n">
-        <v>0.01490947883576155</v>
+        <v>0.01888234540820122</v>
       </c>
       <c r="DP13" t="n">
-        <v>0.02168704196810722</v>
+        <v>0.002002857625484467</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.01245751790702343</v>
+        <v>0.04896489530801773</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.01076187659054995</v>
+        <v>0.01856900937855244</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.006179139018058777</v>
+        <v>0.01754552870988846</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.004289291799068451</v>
+        <v>0.008119947277009487</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.0004534241743385792</v>
+        <v>0.01023803278803825</v>
       </c>
       <c r="DV13" t="n">
-        <v>0.01187722664326429</v>
+        <v>0.006432489491999149</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.001042270800098777</v>
+        <v>0.006268422119319439</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.01141374837607145</v>
+        <v>0.003608306171372533</v>
       </c>
       <c r="DY13" t="n">
-        <v>0.01521278545260429</v>
+        <v>0.03243838623166084</v>
       </c>
       <c r="DZ13" t="n">
-        <v>0.005085226148366928</v>
+        <v>0.01341990567743778</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.005064972676336765</v>
+        <v>0.002734743058681488</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.01605339720845222</v>
+        <v>0.01341737620532513</v>
       </c>
       <c r="EC13" t="n">
-        <v>0.005808945745229721</v>
+        <v>0.0082975709810853</v>
       </c>
       <c r="ED13" t="n">
-        <v>0.007352563552558422</v>
+        <v>0.01149902027100325</v>
       </c>
       <c r="EE13" t="n">
-        <v>0.0146466288715601</v>
+        <v>0.02357392944395542</v>
       </c>
       <c r="EF13" t="n">
-        <v>0.002758333925157785</v>
+        <v>0.02553640305995941</v>
       </c>
       <c r="EG13" t="n">
-        <v>0.0186653658747673</v>
+        <v>0.01281629875302315</v>
       </c>
       <c r="EH13" t="n">
-        <v>0.01272701937705278</v>
+        <v>0.002216200344264507</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.002589564304798841</v>
+        <v>0.003321117721498013</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.006479552015662193</v>
+        <v>0.00125473365187645</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.001846670173108578</v>
+        <v>0.004477633163332939</v>
       </c>
       <c r="EL13" t="n">
-        <v>0.007815811783075333</v>
+        <v>0.002776015549898148</v>
       </c>
       <c r="EM13" t="n">
-        <v>0.003730907337740064</v>
+        <v>0.003375538624823093</v>
       </c>
       <c r="EN13" t="n">
-        <v>0.006168355699628592</v>
+        <v>0.01678581163287163</v>
       </c>
       <c r="EO13" t="n">
-        <v>0.003275573253631592</v>
+        <v>0.01425690948963165</v>
       </c>
       <c r="EP13" t="n">
-        <v>0.008600316010415554</v>
+        <v>0.01204161811619997</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0.01210304256528616</v>
+        <v>0.003796264063566923</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.01283653825521469</v>
+        <v>0.0111118983477354</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.00672372430562973</v>
+        <v>0.002571652643382549</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.0202349629253149</v>
+        <v>0.01373668946325779</v>
       </c>
       <c r="EU13" t="n">
-        <v>0.024049062281847</v>
+        <v>0.002042324980720878</v>
       </c>
       <c r="EV13" t="n">
-        <v>0.04802767932415009</v>
+        <v>0.004578249994665384</v>
       </c>
       <c r="EW13" t="n">
-        <v>0.007092866115272045</v>
+        <v>0.005007864907383919</v>
       </c>
       <c r="EX13" t="n">
-        <v>0.001083589741028845</v>
+        <v>0.01994890719652176</v>
       </c>
       <c r="EY13" t="n">
-        <v>0.01474758516997099</v>
+        <v>0.02249372564256191</v>
       </c>
       <c r="EZ13" t="n">
-        <v>0.01328380592167377</v>
+        <v>0.005496904253959656</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.007584731094539165</v>
+        <v>0.01551446970552206</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.003302507568150759</v>
+        <v>0.002047892659902573</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.01169420871883631</v>
+        <v>0.008206289261579514</v>
       </c>
       <c r="FD13" t="n">
-        <v>0.01789195090532303</v>
+        <v>0.002542746718972921</v>
       </c>
       <c r="FE13" t="n">
-        <v>0.01347396522760391</v>
+        <v>0.004896505270153284</v>
       </c>
       <c r="FF13" t="n">
-        <v>0.01221395842730999</v>
+        <v>0.004546847194433212</v>
       </c>
       <c r="FG13" t="n">
-        <v>0.003166080452501774</v>
+        <v>0.01207037828862667</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.01579330861568451</v>
+        <v>0.0312379002571106</v>
       </c>
       <c r="FI13" t="n">
-        <v>0.01585171744227409</v>
+        <v>0.01225846074521542</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.01992373540997505</v>
+        <v>0.04541011899709702</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.006028510630130768</v>
+        <v>0.008740411140024662</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.002821654547005892</v>
+        <v>0.01526838075369596</v>
       </c>
       <c r="FM13" t="n">
-        <v>0.0127167385071516</v>
+        <v>0.01151378732174635</v>
       </c>
       <c r="FN13" t="n">
-        <v>0.0109943151473999</v>
+        <v>0.002812000224366784</v>
       </c>
       <c r="FO13" t="n">
-        <v>0.009124539792537689</v>
+        <v>0.0192672461271286</v>
       </c>
       <c r="FP13" t="n">
-        <v>0.01696488074958324</v>
+        <v>0.00424797460436821</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01873973198235035</v>
+        <v>0.1012041196227074</v>
       </c>
       <c r="FR13" t="n">
-        <v>0.01935651339590549</v>
+        <v>0.01237689144909382</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.002837487496435642</v>
+        <v>0.03192558139562607</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.02862977609038353</v>
+        <v>0.04156297817826271</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02254908159375191</v>
+        <v>0.02629438415169716</v>
       </c>
       <c r="FV13" t="n">
-        <v>0.01410043425858021</v>
+        <v>0.02533805184066296</v>
       </c>
       <c r="FW13" t="n">
-        <v>0.002155140973627567</v>
+        <v>0.03171307593584061</v>
       </c>
       <c r="FX13" t="n">
-        <v>0.01128438487648964</v>
+        <v>0.009840181097388268</v>
       </c>
       <c r="FY13" t="n">
-        <v>0.02315151318907738</v>
+        <v>0.0007029736880213022</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.003012014552950859</v>
+        <v>0.0007526322151534259</v>
       </c>
       <c r="GA13" t="n">
-        <v>0.01081140618771315</v>
+        <v>0.03347174078226089</v>
       </c>
       <c r="GB13" t="n">
-        <v>0.00502720894291997</v>
+        <v>0.01837706752121449</v>
       </c>
       <c r="GC13" t="n">
-        <v>0.001885336823761463</v>
+        <v>0.02851106040179729</v>
       </c>
       <c r="GD13" t="n">
-        <v>0.006052786950021982</v>
+        <v>0.01536931470036507</v>
       </c>
       <c r="GE13" t="n">
-        <v>0.05211837962269783</v>
+        <v>0.0004072403535246849</v>
       </c>
       <c r="GF13" t="n">
-        <v>0.0008123139850795269</v>
+        <v>0.0006574704311788082</v>
       </c>
       <c r="GG13" t="n">
-        <v>0.004070116207003593</v>
+        <v>0.01074469927698374</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.002358072204515338</v>
+        <v>0.02485533803701401</v>
       </c>
       <c r="B14" t="n">
-        <v>0.04519301652908325</v>
+        <v>0.1062333881855011</v>
       </c>
       <c r="C14" t="n">
-        <v>0.004394729621708393</v>
+        <v>0.002901607193052769</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02061634697020054</v>
+        <v>0.04458122327923775</v>
       </c>
       <c r="E14" t="n">
-        <v>0.009545069187879562</v>
+        <v>0.04486511275172234</v>
       </c>
       <c r="F14" t="n">
-        <v>0.005772814154624939</v>
+        <v>0.1184226647019386</v>
       </c>
       <c r="G14" t="n">
-        <v>0.003513716161251068</v>
+        <v>0.07844188064336777</v>
       </c>
       <c r="H14" t="n">
-        <v>0.002010042546316981</v>
+        <v>0.0968015193939209</v>
       </c>
       <c r="I14" t="n">
-        <v>0.002089016605168581</v>
+        <v>0.003223583800718188</v>
       </c>
       <c r="J14" t="n">
-        <v>0.003829649649560452</v>
+        <v>0.002385057508945465</v>
       </c>
       <c r="K14" t="n">
-        <v>0.03236570209264755</v>
+        <v>0.160155177116394</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0006502055912278593</v>
+        <v>0.01512216590344906</v>
       </c>
       <c r="M14" t="n">
-        <v>0.01762154325842857</v>
+        <v>0.1011393070220947</v>
       </c>
       <c r="N14" t="n">
-        <v>0.01126196980476379</v>
+        <v>0.09882472455501556</v>
       </c>
       <c r="O14" t="n">
-        <v>0.005728586111217737</v>
+        <v>0.159686416387558</v>
       </c>
       <c r="P14" t="n">
-        <v>0.003196128876879811</v>
+        <v>0.0351041704416275</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007111258804798126</v>
+        <v>0.03510860353708267</v>
       </c>
       <c r="R14" t="n">
-        <v>0.0007328984211198986</v>
+        <v>0.02153632789850235</v>
       </c>
       <c r="S14" t="n">
-        <v>0.002067269757390022</v>
+        <v>0.005300791934132576</v>
       </c>
       <c r="T14" t="n">
-        <v>0.006256969179958105</v>
+        <v>0.01795030571520329</v>
       </c>
       <c r="U14" t="n">
-        <v>0.001513654133304954</v>
+        <v>0.01895463466644287</v>
       </c>
       <c r="V14" t="n">
-        <v>0.006452227476984262</v>
+        <v>0.03570126742124557</v>
       </c>
       <c r="W14" t="n">
-        <v>0.004701576661318541</v>
+        <v>0.04098550975322723</v>
       </c>
       <c r="X14" t="n">
-        <v>0.00345646170899272</v>
+        <v>0.04777741432189941</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.003379710717126727</v>
+        <v>0.005805299617350101</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.00489895511418581</v>
+        <v>0.03263327479362488</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.002485897624865174</v>
+        <v>0.02814331836998463</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.001236291602253914</v>
+        <v>0.02068754844367504</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.001727407914586365</v>
+        <v>0.01661871001124382</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.002102994592860341</v>
+        <v>0.01213883794844151</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.0002266294322907925</v>
+        <v>0.05856777727603912</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.649235729128122e-06</v>
+        <v>0.02044185623526573</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.00180037273094058</v>
+        <v>0.06693828105926514</v>
       </c>
       <c r="AH14" t="n">
-        <v>0.000353102688677609</v>
+        <v>0.02109875902533531</v>
       </c>
       <c r="AI14" t="n">
-        <v>0.004351659212261438</v>
+        <v>0.1073121130466461</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.0002582528395578265</v>
+        <v>0.002618271159008145</v>
       </c>
       <c r="AK14" t="n">
-        <v>0.006368061061948538</v>
+        <v>0.001900867093354464</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.002275861334055662</v>
+        <v>0.008670199662446976</v>
       </c>
       <c r="AM14" t="n">
-        <v>5.456275175674818e-05</v>
+        <v>0.01502684503793716</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.004180687945336103</v>
+        <v>0.04857440292835236</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.005278751254081726</v>
+        <v>0.01003884896636009</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.006157109048217535</v>
+        <v>0.03333023563027382</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.001611470826901495</v>
+        <v>0.01434374321252108</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.003543199738487601</v>
+        <v>0.03633460029959679</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.002012870972976089</v>
+        <v>0.008388504385948181</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.000589625327847898</v>
+        <v>0.007090939208865166</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.02816320769488811</v>
+        <v>0.1535891443490982</v>
       </c>
       <c r="AV14" t="n">
-        <v>0.000505245930980891</v>
+        <v>0.01168308593332767</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.003534745192155242</v>
+        <v>0.01892137341201305</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0003250674344599247</v>
+        <v>0.04615578055381775</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.0004427229869179428</v>
+        <v>0.09558367729187012</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.002484109252691269</v>
+        <v>0.004530405625700951</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.005095392465591431</v>
+        <v>0.01033803075551987</v>
       </c>
       <c r="BB14" t="n">
-        <v>0.000525263836607337</v>
+        <v>0.01471718493849039</v>
       </c>
       <c r="BC14" t="n">
-        <v>0.0002770917490124702</v>
+        <v>0.0005049174651503563</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.006502642761915922</v>
+        <v>0.007309939712285995</v>
       </c>
       <c r="BE14" t="n">
-        <v>0.009466564282774925</v>
+        <v>0.03450249508023262</v>
       </c>
       <c r="BF14" t="n">
-        <v>0.005594672635197639</v>
+        <v>0.01677185297012329</v>
       </c>
       <c r="BG14" t="n">
-        <v>0.01332369446754456</v>
+        <v>0.03710534051060677</v>
       </c>
       <c r="BH14" t="n">
-        <v>0.001307048252783716</v>
+        <v>0.01564384438097477</v>
       </c>
       <c r="BI14" t="n">
-        <v>0.001286300714127719</v>
+        <v>0.001379827037453651</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.005344799719750881</v>
+        <v>0.1231893002986908</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.0003660556103568524</v>
+        <v>0.03191414475440979</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.004482337739318609</v>
+        <v>0.001486535649746656</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.00801701657474041</v>
+        <v>0.05583050101995468</v>
       </c>
       <c r="BN14" t="n">
-        <v>0.002826443174853921</v>
+        <v>0.007613757625222206</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.0005527305183932185</v>
+        <v>0.03819286078214645</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.006181838922202587</v>
+        <v>0.04655587300658226</v>
       </c>
       <c r="BQ14" t="n">
-        <v>0.003852311056107283</v>
+        <v>0.03665772452950478</v>
       </c>
       <c r="BR14" t="n">
-        <v>0.001361681846901774</v>
+        <v>0.06323373317718506</v>
       </c>
       <c r="BS14" t="n">
-        <v>0.002026309492066503</v>
+        <v>0.0443921759724617</v>
       </c>
       <c r="BT14" t="n">
-        <v>0.001684439601376653</v>
+        <v>0.03605446964502335</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.001588342012837529</v>
+        <v>0.01264573447406292</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.01544628199189901</v>
+        <v>0.09749531745910645</v>
       </c>
       <c r="BW14" t="n">
-        <v>0.004026705864816904</v>
+        <v>0.01146531198173761</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.001949121593497694</v>
+        <v>0.05357515811920166</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.0004117278731428087</v>
+        <v>0.01878972537815571</v>
       </c>
       <c r="BZ14" t="n">
-        <v>0.00568440742790699</v>
+        <v>0.06609348207712173</v>
       </c>
       <c r="CA14" t="n">
-        <v>0.003422705456614494</v>
+        <v>0.01340493001043797</v>
       </c>
       <c r="CB14" t="n">
-        <v>0.001169334980659187</v>
+        <v>0.0022828234359622</v>
       </c>
       <c r="CC14" t="n">
-        <v>0.0002859613159671426</v>
+        <v>0.04192500561475754</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.0004892206052318215</v>
+        <v>0.005102259106934071</v>
       </c>
       <c r="CE14" t="n">
-        <v>0.007556325290352106</v>
+        <v>0.04058695957064629</v>
       </c>
       <c r="CF14" t="n">
-        <v>0.002519540721550584</v>
+        <v>0.002331104595214128</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.002646306063979864</v>
+        <v>0.0160352848470211</v>
       </c>
       <c r="CH14" t="n">
-        <v>0.001717986189760268</v>
+        <v>0.008483310230076313</v>
       </c>
       <c r="CI14" t="n">
-        <v>0.001579961972311139</v>
+        <v>0.01770994998514652</v>
       </c>
       <c r="CJ14" t="n">
-        <v>0.001542418613098562</v>
+        <v>0.009006520733237267</v>
       </c>
       <c r="CK14" t="n">
-        <v>0.001639616675674915</v>
+        <v>0.008298099972307682</v>
       </c>
       <c r="CL14" t="n">
-        <v>0.001618520356714725</v>
+        <v>0.002318489598110318</v>
       </c>
       <c r="CM14" t="n">
-        <v>0.009313393384218216</v>
+        <v>0.05465948209166527</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.001035006018355489</v>
+        <v>0.1044844388961792</v>
       </c>
       <c r="CO14" t="n">
-        <v>0.00118982105050236</v>
+        <v>0.0530661903321743</v>
       </c>
       <c r="CP14" t="n">
-        <v>0.004368024412542582</v>
+        <v>0.05941006541252136</v>
       </c>
       <c r="CQ14" t="n">
-        <v>0.004631674848496914</v>
+        <v>0.04487789422273636</v>
       </c>
       <c r="CR14" t="n">
-        <v>0.01109731756150723</v>
+        <v>0.01528549939393997</v>
       </c>
       <c r="CS14" t="n">
-        <v>0.00450505455955863</v>
+        <v>0.05443267524242401</v>
       </c>
       <c r="CT14" t="n">
-        <v>0.003140865126624703</v>
+        <v>0.06728243827819824</v>
       </c>
       <c r="CU14" t="n">
-        <v>0.004724707920104265</v>
+        <v>0.008845399133861065</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.0002019125386141241</v>
+        <v>0.00457743788138032</v>
       </c>
       <c r="CW14" t="n">
-        <v>0.006920638959854841</v>
+        <v>0.0330190435051918</v>
       </c>
       <c r="CX14" t="n">
-        <v>0.003056071233004332</v>
+        <v>0.0004347015637904406</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.004189737141132355</v>
+        <v>0.02948565036058426</v>
       </c>
       <c r="CZ14" t="n">
-        <v>0.001675832783803344</v>
+        <v>0.01689820177853107</v>
       </c>
       <c r="DA14" t="n">
-        <v>0.001350408187136054</v>
+        <v>0.01810035668313503</v>
       </c>
       <c r="DB14" t="n">
-        <v>0.001742023276165128</v>
+        <v>0.000400543212890625</v>
       </c>
       <c r="DC14" t="n">
-        <v>0.002626793691888452</v>
+        <v>0.006608227267861366</v>
       </c>
       <c r="DD14" t="n">
-        <v>0.001187085174024105</v>
+        <v>9.43115446716547e-05</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.003959824331104755</v>
+        <v>0.01139640156179667</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.01083394419401884</v>
+        <v>0.01242936216294765</v>
       </c>
       <c r="DG14" t="n">
-        <v>0.001643328578211367</v>
+        <v>0.03163518011569977</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01045149099081755</v>
+        <v>0.0006252210587263107</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.001797748962417245</v>
+        <v>0.0155989695340395</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0.002384244231507182</v>
+        <v>0.009508363902568817</v>
       </c>
       <c r="DK14" t="n">
-        <v>0.002422656631097198</v>
+        <v>0.02113125845789909</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.001308617298491299</v>
+        <v>0.1295603960752487</v>
       </c>
       <c r="DM14" t="n">
-        <v>0.002716596936807036</v>
+        <v>0.01562847755849361</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.005022190045565367</v>
+        <v>0.02429594472050667</v>
       </c>
       <c r="DO14" t="n">
-        <v>0.003116497071459889</v>
+        <v>0.03923318907618523</v>
       </c>
       <c r="DP14" t="n">
-        <v>0.001034805784001946</v>
+        <v>0.006022569723427296</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.002973497845232487</v>
+        <v>0.01157995034009218</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.002085627289488912</v>
+        <v>0.03259840607643127</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.002929333131760359</v>
+        <v>0.01230427250266075</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.001922483323141932</v>
+        <v>0.01305516250431538</v>
       </c>
       <c r="DU14" t="n">
-        <v>0.002710998989641666</v>
+        <v>0.07031442224979401</v>
       </c>
       <c r="DV14" t="n">
-        <v>0.001496804994530976</v>
+        <v>0.02244788967072964</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.0001658318506088108</v>
+        <v>0.0215471014380455</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.002744293538853526</v>
+        <v>0.02692974545061588</v>
       </c>
       <c r="DY14" t="n">
-        <v>0.004052429459989071</v>
+        <v>0.007200069259852171</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0.001053379266522825</v>
+        <v>0.002522891387343407</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.005694754887372255</v>
+        <v>0.0236683189868927</v>
       </c>
       <c r="EB14" t="n">
-        <v>0.0001260707213077694</v>
+        <v>0.0124048562720418</v>
       </c>
       <c r="EC14" t="n">
-        <v>0.003552204463630915</v>
+        <v>0.009405268356204033</v>
       </c>
       <c r="ED14" t="n">
-        <v>0.001280946773476899</v>
+        <v>0.05969836935400963</v>
       </c>
       <c r="EE14" t="n">
-        <v>0.00393104599788785</v>
+        <v>0.05520189553499222</v>
       </c>
       <c r="EF14" t="n">
-        <v>0.005381423979997635</v>
+        <v>0.0119518768042326</v>
       </c>
       <c r="EG14" t="n">
-        <v>0.006616978906095028</v>
+        <v>0.0111894691362977</v>
       </c>
       <c r="EH14" t="n">
-        <v>0.004005718510597944</v>
+        <v>0.01494130305945873</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.002836177591234446</v>
+        <v>0.008568890392780304</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.002028055721893907</v>
+        <v>0.01321811135858297</v>
       </c>
       <c r="EK14" t="n">
-        <v>0.00111375586129725</v>
+        <v>0.01833624206483364</v>
       </c>
       <c r="EL14" t="n">
-        <v>0.001889899373054504</v>
+        <v>0.003239307086914778</v>
       </c>
       <c r="EM14" t="n">
-        <v>0.0007925838581286371</v>
+        <v>0.007458968088030815</v>
       </c>
       <c r="EN14" t="n">
-        <v>0.0004042948712594807</v>
+        <v>0.01970576494932175</v>
       </c>
       <c r="EO14" t="n">
-        <v>0.001496068201959133</v>
+        <v>0.009748234413564205</v>
       </c>
       <c r="EP14" t="n">
-        <v>0.004327090457081795</v>
+        <v>0.01364483125507832</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0.002100758021697402</v>
+        <v>0.01885745488107204</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.003511213697493076</v>
+        <v>0.003458865219727159</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.002297418424859643</v>
+        <v>0.0466134287416935</v>
       </c>
       <c r="ET14" t="n">
-        <v>0.001638241927139461</v>
+        <v>0.002360514365136623</v>
       </c>
       <c r="EU14" t="n">
-        <v>0.004281843546777964</v>
+        <v>0.01871779561042786</v>
       </c>
       <c r="EV14" t="n">
-        <v>0.00117468973621726</v>
+        <v>0.01160957850515842</v>
       </c>
       <c r="EW14" t="n">
-        <v>0.001543662510812283</v>
+        <v>0.05493924766778946</v>
       </c>
       <c r="EX14" t="n">
-        <v>0.001138758379966021</v>
+        <v>0.001090246252715588</v>
       </c>
       <c r="EY14" t="n">
-        <v>0.006944842170923948</v>
+        <v>0.04459083825349808</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0.002329354407265782</v>
+        <v>0.001217883662320673</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.003240364603698254</v>
+        <v>0.03113367035984993</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.0008262525661848485</v>
+        <v>0.004852195270359516</v>
       </c>
       <c r="FC14" t="n">
-        <v>0.001625071279704571</v>
+        <v>0.02722000703215599</v>
       </c>
       <c r="FD14" t="n">
-        <v>0.002044411143288016</v>
+        <v>0.02013238146901131</v>
       </c>
       <c r="FE14" t="n">
-        <v>0.00190382928121835</v>
+        <v>0.01355711929500103</v>
       </c>
       <c r="FF14" t="n">
-        <v>0.002086432883515954</v>
+        <v>0.00943469163030386</v>
       </c>
       <c r="FG14" t="n">
-        <v>0.002448851941153407</v>
+        <v>0.01239743549376726</v>
       </c>
       <c r="FH14" t="n">
-        <v>0.001511680311523378</v>
+        <v>0.01445790939033031</v>
       </c>
       <c r="FI14" t="n">
-        <v>0.001422689761966467</v>
+        <v>0.02678640931844711</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.004429338034242392</v>
+        <v>0.04726731032133102</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.004772622138261795</v>
+        <v>0.009246621280908585</v>
       </c>
       <c r="FL14" t="n">
-        <v>0.003454443998634815</v>
+        <v>0.02976242266595364</v>
       </c>
       <c r="FM14" t="n">
-        <v>0.001444476773031056</v>
+        <v>0.00538370106369257</v>
       </c>
       <c r="FN14" t="n">
-        <v>0.001529344124719501</v>
+        <v>0.0542420968413353</v>
       </c>
       <c r="FO14" t="n">
-        <v>0.0005203075706958771</v>
+        <v>0.05060621351003647</v>
       </c>
       <c r="FP14" t="n">
-        <v>0.004889121279120445</v>
+        <v>0.03755877912044525</v>
       </c>
       <c r="FQ14" t="n">
-        <v>0.002276194049045444</v>
+        <v>0.02124545723199844</v>
       </c>
       <c r="FR14" t="n">
-        <v>0.007912082597613335</v>
+        <v>0.06211766973137856</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.0006347137386910617</v>
+        <v>0.01677023246884346</v>
       </c>
       <c r="FT14" t="n">
-        <v>0.008354900404810905</v>
+        <v>0.06790046393871307</v>
       </c>
       <c r="FU14" t="n">
-        <v>0.0007438568864017725</v>
+        <v>0.01858197525143623</v>
       </c>
       <c r="FV14" t="n">
-        <v>0.002860329346731305</v>
+        <v>0.03213795274496078</v>
       </c>
       <c r="FW14" t="n">
-        <v>0.001584090990945697</v>
+        <v>0.1438654214143753</v>
       </c>
       <c r="FX14" t="n">
-        <v>0.004692681133747101</v>
+        <v>0.004563923925161362</v>
       </c>
       <c r="FY14" t="n">
-        <v>0.00494852289557457</v>
+        <v>0.0001812293194234371</v>
       </c>
       <c r="FZ14" t="n">
-        <v>9.347433660877869e-06</v>
+        <v>0.01479511056095362</v>
       </c>
       <c r="GA14" t="n">
-        <v>0.001626380369998515</v>
+        <v>0.02217602357268333</v>
       </c>
       <c r="GB14" t="n">
-        <v>0.001066774944774806</v>
+        <v>0.01944304257631302</v>
       </c>
       <c r="GC14" t="n">
-        <v>0.002008714713156223</v>
+        <v>0.01334641501307487</v>
       </c>
       <c r="GD14" t="n">
-        <v>0.003383556380867958</v>
+        <v>0.05688530951738358</v>
       </c>
       <c r="GE14" t="n">
-        <v>0.006340105086565018</v>
+        <v>0.06246214359998703</v>
       </c>
       <c r="GF14" t="n">
-        <v>0.002066040877252817</v>
+        <v>0.00999606866389513</v>
       </c>
       <c r="GG14" t="n">
-        <v>0.004599385429173708</v>
+        <v>0.008903962559998035</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.07610310614109039</v>
+        <v>0.08984729647636414</v>
       </c>
       <c r="B15" t="n">
-        <v>0.411668062210083</v>
+        <v>0.7885388731956482</v>
       </c>
       <c r="C15" t="n">
-        <v>0.158510223031044</v>
+        <v>0.2375502288341522</v>
       </c>
       <c r="D15" t="n">
-        <v>0.05049798637628555</v>
+        <v>0.1503854095935822</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1321723312139511</v>
+        <v>0.2242917865514755</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09109190106391907</v>
+        <v>0.08239521086215973</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05906286463141441</v>
+        <v>0.1486689150333405</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0915796309709549</v>
+        <v>0.1309545785188675</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0001880638301372528</v>
+        <v>0.05958897992968559</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1433568894863129</v>
+        <v>0.1422261297702789</v>
       </c>
       <c r="K15" t="n">
-        <v>0.382185697555542</v>
+        <v>0.8324722647666931</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0941464826464653</v>
+        <v>0.2249647676944733</v>
       </c>
       <c r="M15" t="n">
-        <v>0.054460808634758</v>
+        <v>0.3154048919677734</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0194612592458725</v>
+        <v>0.3011319935321808</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01062044501304626</v>
+        <v>0.2738910913467407</v>
       </c>
       <c r="P15" t="n">
-        <v>0.003081373870372772</v>
+        <v>0.1256293505430222</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.1155020743608475</v>
+        <v>0.1436002105474472</v>
       </c>
       <c r="R15" t="n">
-        <v>0.04253998026251793</v>
+        <v>0.00905974954366684</v>
       </c>
       <c r="S15" t="n">
-        <v>0.07169656455516815</v>
+        <v>0.07052417099475861</v>
       </c>
       <c r="T15" t="n">
-        <v>0.06086963042616844</v>
+        <v>0.09772177785634995</v>
       </c>
       <c r="U15" t="n">
-        <v>0.08174596726894379</v>
+        <v>0.03635858371853828</v>
       </c>
       <c r="V15" t="n">
-        <v>0.06742234528064728</v>
+        <v>0.03530112653970718</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02817211300134659</v>
+        <v>0.07350754737854004</v>
       </c>
       <c r="X15" t="n">
-        <v>0.01899260655045509</v>
+        <v>0.03121469169855118</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.007404321804642677</v>
+        <v>0.02085095271468163</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.04890120774507523</v>
+        <v>0.03694803640246391</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.02935429289937019</v>
+        <v>0.2007229924201965</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.08036722987890244</v>
+        <v>0.06781172007322311</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.067853644490242</v>
+        <v>0.02547221817076206</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.02381036803126335</v>
+        <v>0.1238936483860016</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.0259773712605238</v>
+        <v>0.1491069048643112</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.05029798671603203</v>
+        <v>0.04046065732836723</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.003953221254050732</v>
+        <v>0.02156385406851768</v>
       </c>
       <c r="AH15" t="n">
-        <v>0.02497844584286213</v>
+        <v>0.08575940877199173</v>
       </c>
       <c r="AI15" t="n">
-        <v>0.01932291314005852</v>
+        <v>0.03543447703123093</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.03376981243491173</v>
+        <v>0.1007097288966179</v>
       </c>
       <c r="AK15" t="n">
-        <v>0.01476699020713568</v>
+        <v>0.08816731721162796</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.03874154016375542</v>
+        <v>0.3394765257835388</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.0165469367057085</v>
+        <v>0.06625219434499741</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.04408201202750206</v>
+        <v>0.03165791928768158</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.01957880891859531</v>
+        <v>0.2685364186763763</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.07605625689029694</v>
+        <v>0.01139986142516136</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0460878387093544</v>
+        <v>0.04346535727381706</v>
       </c>
       <c r="AR15" t="n">
-        <v>0.02649686299264431</v>
+        <v>0.02082053385674953</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.02522652968764305</v>
+        <v>0.01815649680793285</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.1064468100667</v>
+        <v>0.10361198335886</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2120381593704224</v>
+        <v>0.4773233532905579</v>
       </c>
       <c r="AV15" t="n">
-        <v>0.0854422003030777</v>
+        <v>0.06237606331706047</v>
       </c>
       <c r="AW15" t="n">
-        <v>0.03814927488565445</v>
+        <v>0.02290987595915794</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.07543283700942993</v>
+        <v>0.003644015872851014</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.05569338425993919</v>
+        <v>0.1104674711823463</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.02627405524253845</v>
+        <v>0.04604757949709892</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.03308914601802826</v>
+        <v>0.03394188731908798</v>
       </c>
       <c r="BB15" t="n">
-        <v>0.05925072729587555</v>
+        <v>0.02749582566320896</v>
       </c>
       <c r="BC15" t="n">
-        <v>0.1482377648353577</v>
+        <v>0.1036574468016624</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.09953807294368744</v>
+        <v>0.09005073457956314</v>
       </c>
       <c r="BE15" t="n">
-        <v>0.03630518540740013</v>
+        <v>0.1142981722950935</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.01499730814248323</v>
+        <v>0.08686923235654831</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2729237675666809</v>
+        <v>0.3080984354019165</v>
       </c>
       <c r="BH15" t="n">
-        <v>0.009466017596423626</v>
+        <v>0.1015610620379448</v>
       </c>
       <c r="BI15" t="n">
-        <v>0.04752553626894951</v>
+        <v>0.01440920773893595</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.2065271586179733</v>
+        <v>0.1087407320737839</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.01278456300497055</v>
+        <v>0.1229678392410278</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.07824257016181946</v>
+        <v>0.09573575109243393</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.01348275691270828</v>
+        <v>0.1453769505023956</v>
       </c>
       <c r="BN15" t="n">
-        <v>0.07708752155303955</v>
+        <v>0.06197446957230568</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.02313582971692085</v>
+        <v>0.03209362179040909</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.09627660363912582</v>
+        <v>0.04918446391820908</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.03746278211474419</v>
+        <v>0.007592483423650265</v>
       </c>
       <c r="BR15" t="n">
-        <v>0.05454527586698532</v>
+        <v>0.0844080001115799</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.01376903243362904</v>
+        <v>0.08210373669862747</v>
       </c>
       <c r="BT15" t="n">
-        <v>0.05671530961990356</v>
+        <v>0.09042759239673615</v>
       </c>
       <c r="BU15" t="n">
-        <v>0.08282661437988281</v>
+        <v>0.09950681775808334</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.08930687606334686</v>
+        <v>0.4177460670471191</v>
       </c>
       <c r="BW15" t="n">
-        <v>0.004144832957535982</v>
+        <v>0.005861889570951462</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.01505659054964781</v>
+        <v>0.07007742673158646</v>
       </c>
       <c r="BY15" t="n">
-        <v>0.061689592897892</v>
+        <v>0.05305711925029755</v>
       </c>
       <c r="BZ15" t="n">
-        <v>0.0362836942076683</v>
+        <v>0.04293582588434219</v>
       </c>
       <c r="CA15" t="n">
-        <v>0.04479794204235077</v>
+        <v>0.04200325161218643</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.08149918913841248</v>
+        <v>0.02896992117166519</v>
       </c>
       <c r="CC15" t="n">
-        <v>0.07752534002065659</v>
+        <v>0.0967157855629921</v>
       </c>
       <c r="CD15" t="n">
-        <v>0.04493556916713715</v>
+        <v>0.07598081976175308</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.06856624037027359</v>
+        <v>0.2524089515209198</v>
       </c>
       <c r="CF15" t="n">
-        <v>0.03671246021986008</v>
+        <v>0.07634449005126953</v>
       </c>
       <c r="CG15" t="n">
-        <v>0.02637576684355736</v>
+        <v>0.04265135154128075</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05144701153039932</v>
+        <v>0.007422443944960833</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.02238438650965691</v>
+        <v>0.06001919880509377</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0.01307603437453508</v>
+        <v>0.009102554991841316</v>
       </c>
       <c r="CK15" t="n">
-        <v>0.02246538177132607</v>
+        <v>0.02516301721334457</v>
       </c>
       <c r="CL15" t="n">
-        <v>0.04525324329733849</v>
+        <v>0.004607431590557098</v>
       </c>
       <c r="CM15" t="n">
-        <v>0.000278085470199585</v>
+        <v>0.0439981073141098</v>
       </c>
       <c r="CN15" t="n">
-        <v>0.01381478831171989</v>
+        <v>0.2407783567905426</v>
       </c>
       <c r="CO15" t="n">
-        <v>0.02965095080435276</v>
+        <v>0.03091806918382645</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.04174362123012543</v>
+        <v>0.07964346557855606</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.0477890707552433</v>
+        <v>0.1708972752094269</v>
       </c>
       <c r="CR15" t="n">
-        <v>0.07056698203086853</v>
+        <v>0.05644089728593826</v>
       </c>
       <c r="CS15" t="n">
-        <v>0.05273233726620674</v>
+        <v>0.1133342087268829</v>
       </c>
       <c r="CT15" t="n">
-        <v>0.03825761750340462</v>
+        <v>0.1829686611890793</v>
       </c>
       <c r="CU15" t="n">
-        <v>0.0563976988196373</v>
+        <v>0.07189792394638062</v>
       </c>
       <c r="CV15" t="n">
-        <v>0.04335435107350349</v>
+        <v>0.06802500784397125</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.06432358175516129</v>
+        <v>0.2468522787094116</v>
       </c>
       <c r="CX15" t="n">
-        <v>0.01968980208039284</v>
+        <v>0.05563231557607651</v>
       </c>
       <c r="CY15" t="n">
-        <v>0.03668865561485291</v>
+        <v>0.05531415343284607</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03489523753523827</v>
+        <v>0.02412024140357971</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.009588389657437801</v>
+        <v>0.06168124079704285</v>
       </c>
       <c r="DB15" t="n">
-        <v>0.0006664907559752464</v>
+        <v>0.01163000334054232</v>
       </c>
       <c r="DC15" t="n">
-        <v>0.01417835708707571</v>
+        <v>0.04124438390135765</v>
       </c>
       <c r="DD15" t="n">
-        <v>0.04538939520716667</v>
+        <v>0.0303233377635479</v>
       </c>
       <c r="DE15" t="n">
-        <v>0.04914849996566772</v>
+        <v>0.01091220043599606</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.2341235280036926</v>
+        <v>0.140029713511467</v>
       </c>
       <c r="DG15" t="n">
-        <v>0.03667566925287247</v>
+        <v>0.2047505080699921</v>
       </c>
       <c r="DH15" t="n">
-        <v>0.1098794266581535</v>
+        <v>0.04540003091096878</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.0229358896613121</v>
+        <v>0.003549715504050255</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.1593420058488846</v>
+        <v>0.4365721642971039</v>
       </c>
       <c r="DK15" t="n">
-        <v>0.1550595015287399</v>
+        <v>0.03239573538303375</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.01108607184141874</v>
+        <v>0.02984823659062386</v>
       </c>
       <c r="DM15" t="n">
-        <v>0.04061049595475197</v>
+        <v>0.06828589737415314</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.07970203459262848</v>
+        <v>0.07015343010425568</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.03451824933290482</v>
+        <v>0.1406413018703461</v>
       </c>
       <c r="DP15" t="n">
-        <v>0.1747804135084152</v>
+        <v>0.03976145386695862</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0.0463133417069912</v>
+        <v>0.01893356442451477</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1042510792613029</v>
+        <v>0.002505977638065815</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.05251546204090118</v>
+        <v>0.1068755388259888</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.01166925020515919</v>
+        <v>0.0102085517719388</v>
       </c>
       <c r="DU15" t="n">
-        <v>0.01832926832139492</v>
+        <v>0.05802128463983536</v>
       </c>
       <c r="DV15" t="n">
-        <v>0.007298606913536787</v>
+        <v>0.1912345439195633</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.002431796863675117</v>
+        <v>0.00233151763677597</v>
       </c>
       <c r="DX15" t="n">
-        <v>0.001995776314288378</v>
+        <v>0.01135575771331787</v>
       </c>
       <c r="DY15" t="n">
-        <v>0.07830838859081268</v>
+        <v>0.0440019816160202</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.05465792864561081</v>
+        <v>0.006340651772916317</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01149700582027435</v>
+        <v>0.01695308648049831</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.09885059297084808</v>
+        <v>0.2897043824195862</v>
       </c>
       <c r="EC15" t="n">
-        <v>0.03239524364471436</v>
+        <v>0.0272216685116291</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.06551336497068405</v>
+        <v>0.0886538103222847</v>
       </c>
       <c r="EE15" t="n">
-        <v>0.02815594524145126</v>
+        <v>0.00409531407058239</v>
       </c>
       <c r="EF15" t="n">
-        <v>0.06073470786213875</v>
+        <v>0.06392291933298111</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.07120942324399948</v>
+        <v>0.2519206702709198</v>
       </c>
       <c r="EH15" t="n">
-        <v>0.018047159537673</v>
+        <v>0.02806676179170609</v>
       </c>
       <c r="EI15" t="n">
-        <v>3.074854612350464e-05</v>
+        <v>0.04323727265000343</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03597139939665794</v>
+        <v>0.02369724772870541</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.03376695886254311</v>
+        <v>0.04204127565026283</v>
       </c>
       <c r="EL15" t="n">
-        <v>0.01296351291239262</v>
+        <v>0.02309376001358032</v>
       </c>
       <c r="EM15" t="n">
-        <v>0.04085635393857956</v>
+        <v>0.05146178603172302</v>
       </c>
       <c r="EN15" t="n">
-        <v>0.05996063724160194</v>
+        <v>0.06393977999687195</v>
       </c>
       <c r="EO15" t="n">
-        <v>0.03065993264317513</v>
+        <v>0.008888185024261475</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.04738239198923111</v>
+        <v>0.2202398031949997</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0.02103868871927261</v>
+        <v>0.03182563930749893</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.004497559741139412</v>
+        <v>0.0885649174451828</v>
       </c>
       <c r="ES15" t="n">
-        <v>0.004488762933760881</v>
+        <v>0.09823023527860641</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.03980752825737</v>
+        <v>0.01315910369157791</v>
       </c>
       <c r="EU15" t="n">
-        <v>0.04051487147808075</v>
+        <v>0.06616353243589401</v>
       </c>
       <c r="EV15" t="n">
-        <v>0.08164753019809723</v>
+        <v>0.1354900151491165</v>
       </c>
       <c r="EW15" t="n">
-        <v>0.03132126480340958</v>
+        <v>0.01191619317978621</v>
       </c>
       <c r="EX15" t="n">
-        <v>0.03440189361572266</v>
+        <v>0.07569620758295059</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.08316176384687424</v>
+        <v>0.2880139052867889</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0.03805418685078621</v>
+        <v>0.0676497295498848</v>
       </c>
       <c r="FA15" t="n">
-        <v>0.03479516506195068</v>
+        <v>0.03645271435379982</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.02558166161179543</v>
+        <v>0.01114815846085548</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.01704508997499943</v>
+        <v>0.05595852434635162</v>
       </c>
       <c r="FD15" t="n">
-        <v>0.01610545441508293</v>
+        <v>0.003197647165507078</v>
       </c>
       <c r="FE15" t="n">
-        <v>0.01112247258424759</v>
+        <v>0.04461751133203506</v>
       </c>
       <c r="FF15" t="n">
-        <v>0.06072255223989487</v>
+        <v>0.03062429837882519</v>
       </c>
       <c r="FG15" t="n">
-        <v>0.0001864507794380188</v>
+        <v>0.0587298646569252</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.04629730060696602</v>
+        <v>0.09898668527603149</v>
       </c>
       <c r="FI15" t="n">
-        <v>0.02618619613349438</v>
+        <v>0.1557356864213943</v>
       </c>
       <c r="FJ15" t="n">
-        <v>0.02680531144142151</v>
+        <v>0.01702506095170975</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.04384745657444</v>
+        <v>0.08387820422649384</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.05748160183429718</v>
+        <v>0.007959247566759586</v>
       </c>
       <c r="FM15" t="n">
-        <v>0.03548800572752953</v>
+        <v>0.01625457778573036</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.01223508361726999</v>
+        <v>0.02924387156963348</v>
       </c>
       <c r="FO15" t="n">
-        <v>0.05262100324034691</v>
+        <v>0.280714362859726</v>
       </c>
       <c r="FP15" t="n">
-        <v>0.1425653845071793</v>
+        <v>0.03342117369174957</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.04731027409434319</v>
+        <v>0.2365243434906006</v>
       </c>
       <c r="FR15" t="n">
-        <v>0.162313848733902</v>
+        <v>0.04791194945573807</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.03387156128883362</v>
+        <v>0.1759515106678009</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.09987379610538483</v>
+        <v>0.02072919718921185</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.07140262424945831</v>
+        <v>0.1543325483798981</v>
       </c>
       <c r="FV15" t="n">
-        <v>0.03311662748456001</v>
+        <v>0.1687681674957275</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.001610347419045866</v>
+        <v>0.263926237821579</v>
       </c>
       <c r="FX15" t="n">
-        <v>0.04791879281401634</v>
+        <v>0.1245554313063622</v>
       </c>
       <c r="FY15" t="n">
-        <v>0.06547407060861588</v>
+        <v>0.07657261192798615</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.06162799522280693</v>
+        <v>0.2063716053962708</v>
       </c>
       <c r="GA15" t="n">
-        <v>0.04432064667344093</v>
+        <v>0.1128855794668198</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.01907679252326488</v>
+        <v>0.0526244044303894</v>
       </c>
       <c r="GC15" t="n">
-        <v>0.1077161729335785</v>
+        <v>0.1689919829368591</v>
       </c>
       <c r="GD15" t="n">
-        <v>0.08685251325368881</v>
+        <v>0.03277899324893951</v>
       </c>
       <c r="GE15" t="n">
-        <v>0.07511383295059204</v>
+        <v>0.0237262025475502</v>
       </c>
       <c r="GF15" t="n">
-        <v>0.03598324209451675</v>
+        <v>0.1430694460868835</v>
       </c>
       <c r="GG15" t="n">
-        <v>0.02884509414434433</v>
+        <v>0.02337388135492802</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.001139481901191175</v>
+        <v>0.1264732331037521</v>
       </c>
       <c r="B16" t="n">
-        <v>0.002857709769159555</v>
+        <v>0.02259986102581024</v>
       </c>
       <c r="C16" t="n">
-        <v>0.006328504998236895</v>
+        <v>0.3912931680679321</v>
       </c>
       <c r="D16" t="n">
-        <v>0.001315808854997158</v>
+        <v>0.1488132923841476</v>
       </c>
       <c r="E16" t="n">
-        <v>0.000590263691265136</v>
+        <v>0.01072841137647629</v>
       </c>
       <c r="F16" t="n">
-        <v>0.002348438138142228</v>
+        <v>0.131215512752533</v>
       </c>
       <c r="G16" t="n">
-        <v>0.002258795546367764</v>
+        <v>0.006459586322307587</v>
       </c>
       <c r="H16" t="n">
-        <v>0.002767425961792469</v>
+        <v>0.1840973198413849</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0001445988600607961</v>
+        <v>0.1057046130299568</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00328315794467926</v>
+        <v>0.0632074847817421</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00422661891207099</v>
+        <v>0.003946095705032349</v>
       </c>
       <c r="L16" t="n">
-        <v>0.005178845953196287</v>
+        <v>0.3574815690517426</v>
       </c>
       <c r="M16" t="n">
-        <v>0.003803297644481063</v>
+        <v>0.1408314555883408</v>
       </c>
       <c r="N16" t="n">
-        <v>0.006039747968316078</v>
+        <v>0.08940582722425461</v>
       </c>
       <c r="O16" t="n">
-        <v>0.004470083396881819</v>
+        <v>0.1114820763468742</v>
       </c>
       <c r="P16" t="n">
-        <v>0.0003507584915496409</v>
+        <v>0.03494332730770111</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.005474230274558067</v>
+        <v>0.201177641749382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.0010785604827106</v>
+        <v>0.07229812443256378</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0008591098012402654</v>
+        <v>0.001544829457998276</v>
       </c>
       <c r="T16" t="n">
-        <v>0.002186422701925039</v>
+        <v>0.04430270567536354</v>
       </c>
       <c r="U16" t="n">
-        <v>0.002424300648272038</v>
+        <v>0.04918956384062767</v>
       </c>
       <c r="V16" t="n">
-        <v>0.0004865070804953575</v>
+        <v>0.0940563827753067</v>
       </c>
       <c r="W16" t="n">
-        <v>0.00129056884907186</v>
+        <v>0.04095941036939621</v>
       </c>
       <c r="X16" t="n">
-        <v>0.001866094069555402</v>
+        <v>0.07834111154079437</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.001707161543890834</v>
+        <v>0.03693455830216408</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.00357361719943583</v>
+        <v>0.009349631145596504</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.002694885479286313</v>
+        <v>0.02877174876630306</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.002223832299932837</v>
+        <v>0.01826400682330132</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.0003320817777421325</v>
+        <v>0.02468568459153175</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.001434496603906155</v>
+        <v>0.06760136038064957</v>
       </c>
       <c r="AE16" t="n">
-        <v>0.00925887655466795</v>
+        <v>0.1268853098154068</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.002430655062198639</v>
+        <v>0.1153889372944832</v>
       </c>
       <c r="AG16" t="n">
-        <v>0.002324088243767619</v>
+        <v>0.03064142540097237</v>
       </c>
       <c r="AH16" t="n">
-        <v>0.001003646291792393</v>
+        <v>0.02857212908565998</v>
       </c>
       <c r="AI16" t="n">
-        <v>0.001057847053743899</v>
+        <v>0.05081263184547424</v>
       </c>
       <c r="AJ16" t="n">
-        <v>8.964953303802758e-05</v>
+        <v>0.08307626098394394</v>
       </c>
       <c r="AK16" t="n">
-        <v>0.001610641251318157</v>
+        <v>0.0040859030559659</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.002002483932301402</v>
+        <v>0.01060333382338285</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.0007059124764055014</v>
+        <v>0.04735705256462097</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.002025575144216418</v>
+        <v>0.07518427073955536</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0009801943087950349</v>
+        <v>0.06644334644079208</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.00196816585958004</v>
+        <v>0.09587685763835907</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0009829192422330379</v>
+        <v>0.0488290935754776</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.0005581841105595231</v>
+        <v>0.03420713543891907</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.002078225836157799</v>
+        <v>0.0003727152943611145</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.0006398570258170366</v>
+        <v>0.06085637956857681</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.0008041856926865876</v>
+        <v>0.009984632954001427</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.005868732929229736</v>
+        <v>0.2649102509021759</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.003989233169704676</v>
+        <v>0.1921025812625885</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.002014990197494626</v>
+        <v>0.08843894302845001</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.0001381347537972033</v>
+        <v>0.17674320936203</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.003113452345132828</v>
+        <v>0.118675634264946</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.005904115736484528</v>
+        <v>0.07892473042011261</v>
       </c>
       <c r="BB16" t="n">
-        <v>0.0004246221506036818</v>
+        <v>0.03781269118189812</v>
       </c>
       <c r="BC16" t="n">
-        <v>0.004829248413443565</v>
+        <v>0.1609267592430115</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.000541092362254858</v>
+        <v>0.02493644319474697</v>
       </c>
       <c r="BE16" t="n">
-        <v>0.00156808621250093</v>
+        <v>0.03756918758153915</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.004373959265649319</v>
+        <v>0.1903347820043564</v>
       </c>
       <c r="BG16" t="n">
-        <v>0.00583646772429347</v>
+        <v>0.1098699495196342</v>
       </c>
       <c r="BH16" t="n">
-        <v>0.00178917683660984</v>
+        <v>0.121620237827301</v>
       </c>
       <c r="BI16" t="n">
-        <v>0.003463700413703918</v>
+        <v>0.05783019959926605</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.008675619959831238</v>
+        <v>0.09552015364170074</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.002777445130050182</v>
+        <v>0.03841382265090942</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.004049390554428101</v>
+        <v>0.004766862839460373</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.002607694827020168</v>
+        <v>0.04529167339205742</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.003977896180003881</v>
+        <v>0.07635128498077393</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.002320768777281046</v>
+        <v>0.004712052643299103</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.000771196442656219</v>
+        <v>0.09402705729007721</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.000400435266783461</v>
+        <v>0.0310223288834095</v>
       </c>
       <c r="BR16" t="n">
-        <v>0.0004756775742862374</v>
+        <v>0.01867813989520073</v>
       </c>
       <c r="BS16" t="n">
-        <v>0.0006770298350602388</v>
+        <v>0.004273630678653717</v>
       </c>
       <c r="BT16" t="n">
-        <v>0.002367500681430101</v>
+        <v>0.02001200243830681</v>
       </c>
       <c r="BU16" t="n">
-        <v>0.005122066475450993</v>
+        <v>0.0004844171926379204</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.001073775696568191</v>
+        <v>0.05673851817846298</v>
       </c>
       <c r="BW16" t="n">
-        <v>0.003817953867837787</v>
+        <v>0.1322646588087082</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.002719912212342024</v>
+        <v>0.2657169103622437</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.005336274392902851</v>
+        <v>0.005950581282377243</v>
       </c>
       <c r="BZ16" t="n">
-        <v>0.003378811525180936</v>
+        <v>0.04144791513681412</v>
       </c>
       <c r="CA16" t="n">
-        <v>0.001058854511938989</v>
+        <v>0.07528039813041687</v>
       </c>
       <c r="CB16" t="n">
-        <v>0.003277676180005074</v>
+        <v>0.01392468251287937</v>
       </c>
       <c r="CC16" t="n">
-        <v>0.00132658495567739</v>
+        <v>0.02002756297588348</v>
       </c>
       <c r="CD16" t="n">
-        <v>0.002124086720868945</v>
+        <v>0.001628921367228031</v>
       </c>
       <c r="CE16" t="n">
-        <v>0.0003015128895640373</v>
+        <v>0.05009029060602188</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.001620222115889192</v>
+        <v>0.09000113606452942</v>
       </c>
       <c r="CG16" t="n">
-        <v>0.000585192465223372</v>
+        <v>0.03295241668820381</v>
       </c>
       <c r="CH16" t="n">
-        <v>0.001198149286210537</v>
+        <v>0.00300801545381546</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.0006052872631698847</v>
+        <v>0.01692923530936241</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0.0005177103448659182</v>
+        <v>0.005880275741219521</v>
       </c>
       <c r="CK16" t="n">
-        <v>0.000465901248389855</v>
+        <v>0.02270487323403358</v>
       </c>
       <c r="CL16" t="n">
-        <v>0.001269791158847511</v>
+        <v>0.02480301633477211</v>
       </c>
       <c r="CM16" t="n">
-        <v>0.007196408696472645</v>
+        <v>0.009285600855946541</v>
       </c>
       <c r="CN16" t="n">
-        <v>0.003430298296734691</v>
+        <v>0.08957810699939728</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.003542062826454639</v>
+        <v>0.006719344295561314</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.0009046654449775815</v>
+        <v>0.01774034649133682</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.001348644262179732</v>
+        <v>0.1640722751617432</v>
       </c>
       <c r="CR16" t="n">
-        <v>0.002324431668967009</v>
+        <v>0.02749391086399555</v>
       </c>
       <c r="CS16" t="n">
-        <v>0.001659573405049741</v>
+        <v>0.01897221244871616</v>
       </c>
       <c r="CT16" t="n">
-        <v>0.002329934621229768</v>
+        <v>0.01547891646623611</v>
       </c>
       <c r="CU16" t="n">
-        <v>0.0001136527935159393</v>
+        <v>0.0540461540222168</v>
       </c>
       <c r="CV16" t="n">
-        <v>0.002239231020212173</v>
+        <v>0.01429271884262562</v>
       </c>
       <c r="CW16" t="n">
-        <v>6.124319043010473e-07</v>
+        <v>0.01430725306272507</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.0004734410904347897</v>
+        <v>0.0833984762430191</v>
       </c>
       <c r="CY16" t="n">
-        <v>8.94937984412536e-05</v>
+        <v>0.03469435498118401</v>
       </c>
       <c r="CZ16" t="n">
-        <v>0.0003974561113864183</v>
+        <v>0.01210589148104191</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.0009788796305656433</v>
+        <v>0.02998081222176552</v>
       </c>
       <c r="DB16" t="n">
-        <v>0.0003939619055017829</v>
+        <v>0.01984462700784206</v>
       </c>
       <c r="DC16" t="n">
-        <v>0.0001937608176376671</v>
+        <v>0.008938083425164223</v>
       </c>
       <c r="DD16" t="n">
-        <v>0.0006487902137450874</v>
+        <v>0.03357040882110596</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.001354671781882644</v>
+        <v>0.02510897442698479</v>
       </c>
       <c r="DF16" t="n">
-        <v>0.01194736082106829</v>
+        <v>0.008910035714507103</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.002542086876928806</v>
+        <v>0.1850228011608124</v>
       </c>
       <c r="DH16" t="n">
-        <v>0.007140039931982756</v>
+        <v>0.0323416143655777</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.00675049377605319</v>
+        <v>0.1241007000207901</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0.005452899262309074</v>
+        <v>0.04583361744880676</v>
       </c>
       <c r="DK16" t="n">
-        <v>0.01065034791827202</v>
+        <v>0.07876181602478027</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.00222668657079339</v>
+        <v>0.03623955324292183</v>
       </c>
       <c r="DM16" t="n">
-        <v>0.001032709376886487</v>
+        <v>0.1575317978858948</v>
       </c>
       <c r="DN16" t="n">
-        <v>2.988288179039955e-05</v>
+        <v>0.0406029038131237</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.001540764234960079</v>
+        <v>0.008399669080972672</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.003539487486705184</v>
+        <v>0.01409556623548269</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.003248354652896523</v>
+        <v>0.02454218454658985</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.001129753072746098</v>
+        <v>0.04807018861174583</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.001858373056165874</v>
+        <v>0.0537029355764389</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.003782011801376939</v>
+        <v>0.06930897384881973</v>
       </c>
       <c r="DU16" t="n">
-        <v>0.0009568245150148869</v>
+        <v>0.01077007036656141</v>
       </c>
       <c r="DV16" t="n">
-        <v>6.15035678492859e-05</v>
+        <v>0.04957809299230576</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.0009781979024410248</v>
+        <v>0.08196604251861572</v>
       </c>
       <c r="DX16" t="n">
-        <v>0.005161233711987734</v>
+        <v>0.003122292924672365</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.001172608695924282</v>
+        <v>0.02162934839725494</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.000196336506633088</v>
+        <v>0.0112405214458704</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.004703357815742493</v>
+        <v>0.07077848166227341</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.004072303418070078</v>
+        <v>0.07708199322223663</v>
       </c>
       <c r="EC16" t="n">
-        <v>0.001724935951642692</v>
+        <v>0.05548838526010513</v>
       </c>
       <c r="ED16" t="n">
-        <v>0.001565777929499745</v>
+        <v>0.02042357996106148</v>
       </c>
       <c r="EE16" t="n">
-        <v>0.002977951429784298</v>
+        <v>0.0005711093544960022</v>
       </c>
       <c r="EF16" t="n">
-        <v>0.001906497636809945</v>
+        <v>0.04473805800080299</v>
       </c>
       <c r="EG16" t="n">
-        <v>0.002343512838706374</v>
+        <v>0.02735641412436962</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0005043933051638305</v>
+        <v>0.08014644682407379</v>
       </c>
       <c r="EI16" t="n">
-        <v>0.003349015954881907</v>
+        <v>0.003123331815004349</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.001392957754433155</v>
+        <v>0.02829941175878048</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.002298578387126327</v>
+        <v>0.0007040780037641525</v>
       </c>
       <c r="EL16" t="n">
-        <v>0.001144787762314081</v>
+        <v>0.01706209778785706</v>
       </c>
       <c r="EM16" t="n">
-        <v>0.0003302289405837655</v>
+        <v>0.03248962759971619</v>
       </c>
       <c r="EN16" t="n">
-        <v>0.001624029944650829</v>
+        <v>0.0006274892948567867</v>
       </c>
       <c r="EO16" t="n">
-        <v>0.001831091940402985</v>
+        <v>0.0407201461493969</v>
       </c>
       <c r="EP16" t="n">
-        <v>3.72596550732851e-05</v>
+        <v>0.05708173662424088</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.0007219138205982745</v>
+        <v>0.02992499247193336</v>
       </c>
       <c r="ER16" t="n">
-        <v>0.0002829807344824076</v>
+        <v>0.02846315130591393</v>
       </c>
       <c r="ES16" t="n">
-        <v>0.002892695832997561</v>
+        <v>0.05492831766605377</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.005921930074691772</v>
+        <v>0.1082282662391663</v>
       </c>
       <c r="EU16" t="n">
-        <v>8.634317782707512e-05</v>
+        <v>0.004345317836850882</v>
       </c>
       <c r="EV16" t="n">
-        <v>0.003099956549704075</v>
+        <v>0.0407305471599102</v>
       </c>
       <c r="EW16" t="n">
-        <v>4.484769306145608e-05</v>
+        <v>0.01265075616538525</v>
       </c>
       <c r="EX16" t="n">
-        <v>0.00268099969252944</v>
+        <v>3.42121347784996e-06</v>
       </c>
       <c r="EY16" t="n">
-        <v>0.0006173327565193176</v>
+        <v>0.05556689575314522</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0007125696283765137</v>
+        <v>0.08646067976951599</v>
       </c>
       <c r="FA16" t="n">
-        <v>0.0005744864465668797</v>
+        <v>0.0401245579123497</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.000547314528375864</v>
+        <v>0.01214470341801643</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.0004221514100208879</v>
+        <v>0.04419213533401489</v>
       </c>
       <c r="FD16" t="n">
-        <v>4.276477557141334e-05</v>
+        <v>0.01612326130270958</v>
       </c>
       <c r="FE16" t="n">
-        <v>0.0007817933801561594</v>
+        <v>0.003021758049726486</v>
       </c>
       <c r="FF16" t="n">
-        <v>0.000940116704441607</v>
+        <v>0.02843673340976238</v>
       </c>
       <c r="FG16" t="n">
-        <v>0.0004505813703872263</v>
+        <v>0.02682296931743622</v>
       </c>
       <c r="FH16" t="n">
-        <v>0.006541823036968708</v>
+        <v>0.02182720601558685</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.0006574990111403167</v>
+        <v>0.1396051943302155</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.001909299287945032</v>
+        <v>0.06447555124759674</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.000821208581328392</v>
+        <v>0.07486343383789062</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.002719905925914645</v>
+        <v>0.09998157620429993</v>
       </c>
       <c r="FM16" t="n">
-        <v>0.0006340299732983112</v>
+        <v>0.01726214773952961</v>
       </c>
       <c r="FN16" t="n">
-        <v>0.001318468945100904</v>
+        <v>0.04679081588983536</v>
       </c>
       <c r="FO16" t="n">
-        <v>0.001431444543413818</v>
+        <v>0.01940857246518135</v>
       </c>
       <c r="FP16" t="n">
-        <v>0.007803010754287243</v>
+        <v>0.01307729631662369</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.008561997674405575</v>
+        <v>0.0343465581536293</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.01394707895815372</v>
+        <v>0.04359464347362518</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.0005478115053847432</v>
+        <v>0.1060061454772949</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.01053434237837791</v>
+        <v>0.02833684720098972</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.002045581350103021</v>
+        <v>0.08103844523429871</v>
       </c>
       <c r="FV16" t="n">
-        <v>0.002570054493844509</v>
+        <v>0.0898413360118866</v>
       </c>
       <c r="FW16" t="n">
-        <v>0.0002606128109619021</v>
+        <v>0.1220217198133469</v>
       </c>
       <c r="FX16" t="n">
-        <v>0.002416766248643398</v>
+        <v>0.07572165131568909</v>
       </c>
       <c r="FY16" t="n">
-        <v>0.0007230557966977358</v>
+        <v>0.001571916975080967</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.0001294855610467494</v>
+        <v>0.1498092263936996</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.003197837388142943</v>
+        <v>0.09479422867298126</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.002365388441830873</v>
+        <v>0.05907762795686722</v>
       </c>
       <c r="GC16" t="n">
-        <v>0.004374533891677856</v>
+        <v>0.01424002554267645</v>
       </c>
       <c r="GD16" t="n">
-        <v>0.00242526619695127</v>
+        <v>0.02255981788039207</v>
       </c>
       <c r="GE16" t="n">
-        <v>0.003522973274812102</v>
+        <v>0.03241125121712685</v>
       </c>
       <c r="GF16" t="n">
-        <v>0.004297186620533466</v>
+        <v>0.07427804917097092</v>
       </c>
       <c r="GG16" t="n">
-        <v>0.0003743542183656245</v>
+        <v>0.03510767221450806</v>
       </c>
     </row>
     <row r="17">
